--- a/Outputs/Recycling_Plot_Data/Repeal/08_Recycled_Content_Ratio_data_Repeal.xlsx
+++ b/Outputs/Recycling_Plot_Data/Repeal/08_Recycled_Content_Ratio_data_Repeal.xlsx
@@ -421,7 +421,7 @@
         </is>
       </c>
       <c r="G2">
-        <v>0.678550401397562</v>
+        <v>0.6780851423604122</v>
       </c>
     </row>
     <row r="3">
@@ -454,7 +454,7 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.678550401397562</v>
+        <v>0.6780851423604122</v>
       </c>
     </row>
     <row r="4">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="G4">
-        <v>0.8066492432493432</v>
+        <v>0.7979819624072101</v>
       </c>
     </row>
     <row r="5">
@@ -520,7 +520,7 @@
         </is>
       </c>
       <c r="G5">
-        <v>0.8066492432493432</v>
+        <v>0.7979819624072101</v>
       </c>
     </row>
     <row r="6">
@@ -553,7 +553,7 @@
         </is>
       </c>
       <c r="G6">
-        <v>1.092324607672388</v>
+        <v>1.082126150733171</v>
       </c>
     </row>
     <row r="7">
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="G7">
-        <v>1.092324607672388</v>
+        <v>1.082126150733171</v>
       </c>
     </row>
     <row r="8">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="G8">
-        <v>1.416007385300069</v>
+        <v>1.40288136979463</v>
       </c>
     </row>
     <row r="9">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="G9">
-        <v>1.416007385300069</v>
+        <v>1.40288136979463</v>
       </c>
     </row>
     <row r="10">
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="G10">
-        <v>1.794125772785953</v>
+        <v>1.777114044375011</v>
       </c>
     </row>
     <row r="11">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="G11">
-        <v>1.794125772785953</v>
+        <v>1.777114044375011</v>
       </c>
     </row>
     <row r="12">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="G12">
-        <v>2.248481262086216</v>
+        <v>2.225722380621859</v>
       </c>
     </row>
     <row r="13">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="G13">
-        <v>2.248481262086216</v>
+        <v>2.225722380621859</v>
       </c>
     </row>
     <row r="14">
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="G14">
-        <v>2.821705946758411</v>
+        <v>2.791749903313669</v>
       </c>
     </row>
     <row r="15">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="G15">
-        <v>2.821705946758411</v>
+        <v>2.791749903313669</v>
       </c>
     </row>
     <row r="16">
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="G16">
-        <v>3.25289053503255</v>
+        <v>3.214977224913449</v>
       </c>
     </row>
     <row r="17">
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="G17">
-        <v>3.25289053503255</v>
+        <v>3.214977224913449</v>
       </c>
     </row>
     <row r="18">
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="G18">
-        <v>3.931130164446334</v>
+        <v>3.881417959427569</v>
       </c>
     </row>
     <row r="19">
@@ -982,7 +982,7 @@
         </is>
       </c>
       <c r="G19">
-        <v>3.931130164446334</v>
+        <v>3.881417959427569</v>
       </c>
     </row>
     <row r="20">
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="G20">
-        <v>4.857089869531427</v>
+        <v>4.789237697424389</v>
       </c>
     </row>
     <row r="21">
@@ -1048,7 +1048,7 @@
         </is>
       </c>
       <c r="G21">
-        <v>4.857089869531427</v>
+        <v>4.789237697424389</v>
       </c>
     </row>
     <row r="22">
@@ -1081,7 +1081,7 @@
         </is>
       </c>
       <c r="G22">
-        <v>6.298418573699843</v>
+        <v>6.200292021743948</v>
       </c>
     </row>
     <row r="23">
@@ -1114,7 +1114,7 @@
         </is>
       </c>
       <c r="G23">
-        <v>6.298418573699843</v>
+        <v>6.200292021743948</v>
       </c>
     </row>
     <row r="24">
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="G24">
-        <v>6.568023020223163</v>
+        <v>6.553472333486202</v>
       </c>
     </row>
     <row r="25">
@@ -1180,7 +1180,7 @@
         </is>
       </c>
       <c r="G25">
-        <v>8.202412246656507</v>
+        <v>8.059474607275334</v>
       </c>
     </row>
     <row r="26">
@@ -1213,7 +1213,7 @@
         </is>
       </c>
       <c r="G26">
-        <v>6.339691611865686</v>
+        <v>6.329910634375138</v>
       </c>
     </row>
     <row r="27">
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="G27">
-        <v>10.46663226540654</v>
+        <v>10.27944580533306</v>
       </c>
     </row>
     <row r="28">
@@ -1279,7 +1279,7 @@
         </is>
       </c>
       <c r="G28">
-        <v>6.269109801373637</v>
+        <v>6.230029581391157</v>
       </c>
     </row>
     <row r="29">
@@ -1312,7 +1312,7 @@
         </is>
       </c>
       <c r="G29">
-        <v>14.07668338582182</v>
+        <v>13.50104535928962</v>
       </c>
     </row>
     <row r="30">
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="G30">
-        <v>5.882927412834932</v>
+        <v>5.84694659594471</v>
       </c>
     </row>
     <row r="31">
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c r="G31">
-        <v>16.39564289413168</v>
+        <v>15.75205347556104</v>
       </c>
     </row>
     <row r="32">
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="G32">
-        <v>5.635589125358054</v>
+        <v>5.605076631150654</v>
       </c>
     </row>
     <row r="33">
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="G33">
-        <v>19.05973280528345</v>
+        <v>18.40193506882056</v>
       </c>
     </row>
     <row r="34">
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="G34">
-        <v>5.381738901988111</v>
+        <v>5.359023155938347</v>
       </c>
     </row>
     <row r="35">
@@ -1510,7 +1510,7 @@
         </is>
       </c>
       <c r="G35">
-        <v>21.63886153674822</v>
+        <v>21.04870265796465</v>
       </c>
     </row>
     <row r="36">
@@ -1543,7 +1543,7 @@
         </is>
       </c>
       <c r="G36">
-        <v>5.139878693601409</v>
+        <v>5.125134326136516</v>
       </c>
     </row>
     <row r="37">
@@ -1576,7 +1576,7 @@
         </is>
       </c>
       <c r="G37">
-        <v>24.42729487247241</v>
+        <v>23.95776793905343</v>
       </c>
     </row>
     <row r="38">
@@ -1609,7 +1609,7 @@
         </is>
       </c>
       <c r="G38">
-        <v>4.928553188568903</v>
+        <v>4.920299738147429</v>
       </c>
     </row>
     <row r="39">
@@ -1642,7 +1642,7 @@
         </is>
       </c>
       <c r="G39">
-        <v>27.56261678761782</v>
+        <v>27.22530063048109</v>
       </c>
     </row>
     <row r="40">
@@ -1675,7 +1675,7 @@
         </is>
       </c>
       <c r="G40">
-        <v>4.745753534635353</v>
+        <v>4.741826900750426</v>
       </c>
     </row>
     <row r="41">
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="G41">
-        <v>31.13574471804534</v>
+        <v>30.90833228981088</v>
       </c>
     </row>
     <row r="42">
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="G42">
-        <v>4.575450473658126</v>
+        <v>4.574160694590696</v>
       </c>
     </row>
     <row r="43">
@@ -1774,7 +1774,7 @@
         </is>
       </c>
       <c r="G43">
-        <v>35.04928512813891</v>
+        <v>34.89855778883003</v>
       </c>
     </row>
     <row r="44">
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="G44">
-        <v>4.43153040231579</v>
+        <v>4.431923957968758</v>
       </c>
     </row>
     <row r="45">
@@ -1840,7 +1840,7 @@
         </is>
       </c>
       <c r="G45">
-        <v>39.50001870651256</v>
+        <v>39.3977593298256</v>
       </c>
     </row>
     <row r="46">
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="G46">
-        <v>4.301631943977405</v>
+        <v>4.303284820216586</v>
       </c>
     </row>
     <row r="47">
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="G47">
-        <v>44.09993131319845</v>
+        <v>44.02929233036105</v>
       </c>
     </row>
     <row r="48">
@@ -1939,7 +1939,7 @@
         </is>
       </c>
       <c r="G48">
-        <v>4.182315874800094</v>
+        <v>4.185036714523538</v>
       </c>
     </row>
     <row r="49">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="G49">
-        <v>48.70312454381093</v>
+        <v>48.65423156064291</v>
       </c>
     </row>
     <row r="50">
@@ -2005,7 +2005,7 @@
         </is>
       </c>
       <c r="G50">
-        <v>4.073026540833304</v>
+        <v>4.076655126772783</v>
       </c>
     </row>
     <row r="51">
@@ -2038,7 +2038,7 @@
         </is>
       </c>
       <c r="G51">
-        <v>53.06741318748869</v>
+        <v>53.03307838184124</v>
       </c>
     </row>
     <row r="52">
@@ -2071,7 +2071,7 @@
         </is>
       </c>
       <c r="G52">
-        <v>0.7045123723737181</v>
+        <v>0.7040292226245707</v>
       </c>
     </row>
     <row r="53">
@@ -2104,7 +2104,7 @@
         </is>
       </c>
       <c r="G53">
-        <v>0.7045123723737181</v>
+        <v>0.7040292226245707</v>
       </c>
     </row>
     <row r="54">
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="G54">
-        <v>0.8779881296719685</v>
+        <v>0.8685475658962922</v>
       </c>
     </row>
     <row r="55">
@@ -2170,7 +2170,7 @@
         </is>
       </c>
       <c r="G55">
-        <v>0.8779881296719685</v>
+        <v>0.8685475658962922</v>
       </c>
     </row>
     <row r="56">
@@ -2203,7 +2203,7 @@
         </is>
       </c>
       <c r="G56">
-        <v>1.230386686315928</v>
+        <v>1.218873498778856</v>
       </c>
     </row>
     <row r="57">
@@ -2236,7 +2236,7 @@
         </is>
       </c>
       <c r="G57">
-        <v>1.230386686315928</v>
+        <v>1.218873498778856</v>
       </c>
     </row>
     <row r="58">
@@ -2269,7 +2269,7 @@
         </is>
       </c>
       <c r="G58">
-        <v>1.644012195388687</v>
+        <v>1.628713087827859</v>
       </c>
     </row>
     <row r="59">
@@ -2302,7 +2302,7 @@
         </is>
       </c>
       <c r="G59">
-        <v>1.644012195388687</v>
+        <v>1.628713087827859</v>
       </c>
     </row>
     <row r="60">
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="G60">
-        <v>2.13690009566249</v>
+        <v>2.11651689041768</v>
       </c>
     </row>
     <row r="61">
@@ -2368,7 +2368,7 @@
         </is>
       </c>
       <c r="G61">
-        <v>2.13690009566249</v>
+        <v>2.11651689041768</v>
       </c>
     </row>
     <row r="62">
@@ -2401,7 +2401,7 @@
         </is>
       </c>
       <c r="G62">
-        <v>2.73157715344072</v>
+        <v>2.7036871429419</v>
       </c>
     </row>
     <row r="63">
@@ -2434,7 +2434,7 @@
         </is>
       </c>
       <c r="G63">
-        <v>2.73157715344072</v>
+        <v>2.7036871429419</v>
       </c>
     </row>
     <row r="64">
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="G64">
-        <v>3.504779200199949</v>
+        <v>3.467162079297369</v>
       </c>
     </row>
     <row r="65">
@@ -2500,7 +2500,7 @@
         </is>
       </c>
       <c r="G65">
-        <v>3.504779200199949</v>
+        <v>3.467162079297369</v>
       </c>
     </row>
     <row r="66">
@@ -2533,7 +2533,7 @@
         </is>
       </c>
       <c r="G66">
-        <v>4.146536681878042</v>
+        <v>4.0975087421026</v>
       </c>
     </row>
     <row r="67">
@@ -2566,7 +2566,7 @@
         </is>
       </c>
       <c r="G67">
-        <v>4.146536681878042</v>
+        <v>4.0975087421026</v>
       </c>
     </row>
     <row r="68">
@@ -2599,7 +2599,7 @@
         </is>
       </c>
       <c r="G68">
-        <v>5.133210645560393</v>
+        <v>5.067074830261418</v>
       </c>
     </row>
     <row r="69">
@@ -2632,7 +2632,7 @@
         </is>
       </c>
       <c r="G69">
-        <v>5.133210645560393</v>
+        <v>5.067074830261418</v>
       </c>
     </row>
     <row r="70">
@@ -2665,7 +2665,7 @@
         </is>
       </c>
       <c r="G70">
-        <v>6.484508530999245</v>
+        <v>6.391776061789177</v>
       </c>
     </row>
     <row r="71">
@@ -2698,7 +2698,7 @@
         </is>
       </c>
       <c r="G71">
-        <v>6.484508530999245</v>
+        <v>6.391776061789177</v>
       </c>
     </row>
     <row r="72">
@@ -2731,7 +2731,7 @@
         </is>
       </c>
       <c r="G72">
-        <v>8.554814502364501</v>
+        <v>8.417707021902423</v>
       </c>
     </row>
     <row r="73">
@@ -2764,7 +2764,7 @@
         </is>
       </c>
       <c r="G73">
-        <v>8.554814502364501</v>
+        <v>8.417707021902423</v>
       </c>
     </row>
     <row r="74">
@@ -2797,7 +2797,7 @@
         </is>
       </c>
       <c r="G74">
-        <v>9.000300863352008</v>
+        <v>8.9746294387313</v>
       </c>
     </row>
     <row r="75">
@@ -2830,7 +2830,7 @@
         </is>
       </c>
       <c r="G75">
-        <v>11.29334895401028</v>
+        <v>11.09018901291618</v>
       </c>
     </row>
     <row r="76">
@@ -2863,7 +2863,7 @@
         </is>
       </c>
       <c r="G76">
-        <v>8.783531647443638</v>
+        <v>8.762775341183067</v>
       </c>
     </row>
     <row r="77">
@@ -2896,7 +2896,7 @@
         </is>
       </c>
       <c r="G77">
-        <v>14.58542430783554</v>
+        <v>14.31398277963033</v>
       </c>
     </row>
     <row r="78">
@@ -2929,7 +2929,7 @@
         </is>
       </c>
       <c r="G78">
-        <v>8.769659872229802</v>
+        <v>8.696479328796633</v>
       </c>
     </row>
     <row r="79">
@@ -2962,7 +2962,7 @@
         </is>
       </c>
       <c r="G79">
-        <v>19.82309841634784</v>
+        <v>18.97633873952574</v>
       </c>
     </row>
     <row r="80">
@@ -2995,7 +2995,7 @@
         </is>
       </c>
       <c r="G80">
-        <v>8.338685501951677</v>
+        <v>8.265578715520196</v>
       </c>
     </row>
     <row r="81">
@@ -3028,7 +3028,7 @@
         </is>
       </c>
       <c r="G81">
-        <v>23.43906291632119</v>
+        <v>22.46502317505583</v>
       </c>
     </row>
     <row r="82">
@@ -3061,7 +3061,7 @@
         </is>
       </c>
       <c r="G82">
-        <v>7.824805042143081</v>
+        <v>7.758114982370665</v>
       </c>
     </row>
     <row r="83">
@@ -3094,7 +3094,7 @@
         </is>
       </c>
       <c r="G83">
-        <v>26.76149743378571</v>
+        <v>25.76503006181695</v>
       </c>
     </row>
     <row r="84">
@@ -3127,7 +3127,7 @@
         </is>
       </c>
       <c r="G84">
-        <v>7.279775473710355</v>
+        <v>7.225554678950346</v>
       </c>
     </row>
     <row r="85">
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c r="G85">
-        <v>29.69892711736891</v>
+        <v>28.80417484193693</v>
       </c>
     </row>
     <row r="86">
@@ -3193,7 +3193,7 @@
         </is>
       </c>
       <c r="G86">
-        <v>6.747570962876397</v>
+        <v>6.708734925018205</v>
       </c>
     </row>
     <row r="87">
@@ -3226,7 +3226,7 @@
         </is>
       </c>
       <c r="G87">
-        <v>32.66258147102161</v>
+        <v>31.95055246574195</v>
       </c>
     </row>
     <row r="88">
@@ -3259,7 +3259,7 @@
         </is>
       </c>
       <c r="G88">
-        <v>6.271798104748047</v>
+        <v>6.247319117653356</v>
       </c>
     </row>
     <row r="89">
@@ -3292,7 +3292,7 @@
         </is>
       </c>
       <c r="G89">
-        <v>35.87004945127007</v>
+        <v>35.35910215761792</v>
       </c>
     </row>
     <row r="90">
@@ -3325,7 +3325,7 @@
         </is>
       </c>
       <c r="G90">
-        <v>5.861372200287538</v>
+        <v>5.847486515129811</v>
       </c>
     </row>
     <row r="91">
@@ -3358,7 +3358,7 @@
         </is>
       </c>
       <c r="G91">
-        <v>39.48269503645371</v>
+        <v>39.13918209280204</v>
       </c>
     </row>
     <row r="92">
@@ -3391,7 +3391,7 @@
         </is>
       </c>
       <c r="G92">
-        <v>5.494687227808699</v>
+        <v>5.487553473548779</v>
       </c>
     </row>
     <row r="93">
@@ -3424,7 +3424,7 @@
         </is>
       </c>
       <c r="G93">
-        <v>43.37856633348044</v>
+        <v>43.15188678059388</v>
       </c>
     </row>
     <row r="94">
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="G94">
-        <v>5.180426648505716</v>
+        <v>5.177417212216031</v>
       </c>
     </row>
     <row r="95">
@@ -3490,7 +3490,7 @@
         </is>
       </c>
       <c r="G95">
-        <v>47.76148420157172</v>
+        <v>47.60857937119452</v>
       </c>
     </row>
     <row r="96">
@@ -3523,7 +3523,7 @@
         </is>
       </c>
       <c r="G96">
-        <v>4.900246746263242</v>
+        <v>4.899935150017501</v>
       </c>
     </row>
     <row r="97">
@@ -3556,7 +3556,7 @@
         </is>
       </c>
       <c r="G97">
-        <v>52.14311188249802</v>
+        <v>52.03808863532864</v>
       </c>
     </row>
     <row r="98">
@@ -3589,7 +3589,7 @@
         </is>
       </c>
       <c r="G98">
-        <v>4.647105311459809</v>
+        <v>4.648750758961938</v>
       </c>
     </row>
     <row r="99">
@@ -3622,7 +3622,7 @@
         </is>
       </c>
       <c r="G99">
-        <v>56.3538541452235</v>
+        <v>56.2817264331812</v>
       </c>
     </row>
     <row r="100">
@@ -3655,7 +3655,7 @@
         </is>
       </c>
       <c r="G100">
-        <v>4.420331627365178</v>
+        <v>4.423438076494774</v>
       </c>
     </row>
     <row r="101">
@@ -3688,7 +3688,7 @@
         </is>
       </c>
       <c r="G101">
-        <v>60.15482831407365</v>
+        <v>60.10515492391663</v>
       </c>
     </row>
     <row r="102">
@@ -3721,7 +3721,7 @@
         </is>
       </c>
       <c r="G102">
-        <v>0.7607182005909324</v>
+        <v>0.7601617789820817</v>
       </c>
     </row>
     <row r="103">
@@ -3754,7 +3754,7 @@
         </is>
       </c>
       <c r="G103">
-        <v>0.7607182005909324</v>
+        <v>0.7601617789820817</v>
       </c>
     </row>
     <row r="104">
@@ -3787,7 +3787,7 @@
         </is>
       </c>
       <c r="G104">
-        <v>0.9522839240334419</v>
+        <v>0.9423093425378035</v>
       </c>
     </row>
     <row r="105">
@@ -3820,7 +3820,7 @@
         </is>
       </c>
       <c r="G105">
-        <v>0.9522839240334419</v>
+        <v>0.9423093425378035</v>
       </c>
     </row>
     <row r="106">
@@ -3853,7 +3853,7 @@
         </is>
       </c>
       <c r="G106">
-        <v>1.353129073683465</v>
+        <v>1.340755969636724</v>
       </c>
     </row>
     <row r="107">
@@ -3886,7 +3886,7 @@
         </is>
       </c>
       <c r="G107">
-        <v>1.353129073683465</v>
+        <v>1.340755969636724</v>
       </c>
     </row>
     <row r="108">
@@ -3919,7 +3919,7 @@
         </is>
       </c>
       <c r="G108">
-        <v>1.838824974405591</v>
+        <v>1.822062040653551</v>
       </c>
     </row>
     <row r="109">
@@ -3952,7 +3952,7 @@
         </is>
       </c>
       <c r="G109">
-        <v>1.838824974405591</v>
+        <v>1.822062040653551</v>
       </c>
     </row>
     <row r="110">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="G110">
-        <v>2.437531497692002</v>
+        <v>2.414692059842958</v>
       </c>
     </row>
     <row r="111">
@@ -4018,7 +4018,7 @@
         </is>
       </c>
       <c r="G111">
-        <v>2.437531497692002</v>
+        <v>2.414692059842958</v>
       </c>
     </row>
     <row r="112">
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c r="G112">
-        <v>3.188922256944341</v>
+        <v>3.156837470367571</v>
       </c>
     </row>
     <row r="113">
@@ -4084,7 +4084,7 @@
         </is>
       </c>
       <c r="G113">
-        <v>3.188922256944341</v>
+        <v>3.156837470367571</v>
       </c>
     </row>
     <row r="114">
@@ -4117,7 +4117,7 @@
         </is>
       </c>
       <c r="G114">
-        <v>4.175095602728176</v>
+        <v>4.130820793003583</v>
       </c>
     </row>
     <row r="115">
@@ -4150,7 +4150,7 @@
         </is>
       </c>
       <c r="G115">
-        <v>4.175095602728176</v>
+        <v>4.130820793003583</v>
       </c>
     </row>
     <row r="116">
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="G116">
-        <v>5.010590909432119</v>
+        <v>4.951827918629021</v>
       </c>
     </row>
     <row r="117">
@@ -4216,7 +4216,7 @@
         </is>
       </c>
       <c r="G117">
-        <v>5.010590909432119</v>
+        <v>4.951827918629021</v>
       </c>
     </row>
     <row r="118">
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="G118">
-        <v>6.285459607483862</v>
+        <v>6.204839080384664</v>
       </c>
     </row>
     <row r="119">
@@ -4282,7 +4282,7 @@
         </is>
       </c>
       <c r="G119">
-        <v>6.285459607483862</v>
+        <v>6.204839080384664</v>
       </c>
     </row>
     <row r="120">
@@ -4315,7 +4315,7 @@
         </is>
       </c>
       <c r="G120">
-        <v>8.050192073660867</v>
+        <v>7.935094384078235</v>
       </c>
     </row>
     <row r="121">
@@ -4348,7 +4348,7 @@
         </is>
       </c>
       <c r="G121">
-        <v>8.050192073660867</v>
+        <v>7.935094384078235</v>
       </c>
     </row>
     <row r="122">
@@ -4381,7 +4381,7 @@
         </is>
       </c>
       <c r="G122">
-        <v>10.46536477672392</v>
+        <v>10.29685612504705</v>
       </c>
     </row>
     <row r="123">
@@ -4414,7 +4414,7 @@
         </is>
       </c>
       <c r="G123">
-        <v>10.46536477672392</v>
+        <v>10.29685612504705</v>
       </c>
     </row>
     <row r="124">
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="G124">
-        <v>13.65477073986755</v>
+        <v>13.40681008345821</v>
       </c>
     </row>
     <row r="125">
@@ -4480,7 +4480,7 @@
         </is>
       </c>
       <c r="G125">
-        <v>13.65477073986755</v>
+        <v>13.40681008345821</v>
       </c>
     </row>
     <row r="126">
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="G126">
-        <v>15.75931225750605</v>
+        <v>15.74268278800208</v>
       </c>
     </row>
     <row r="127">
@@ -4546,7 +4546,7 @@
         </is>
       </c>
       <c r="G127">
-        <v>17.41685712057426</v>
+        <v>17.088187492256</v>
       </c>
     </row>
     <row r="128">
@@ -4579,7 +4579,7 @@
         </is>
       </c>
       <c r="G128">
-        <v>15.79583557929759</v>
+        <v>15.73391986188437</v>
       </c>
     </row>
     <row r="129">
@@ -4612,7 +4612,7 @@
         </is>
       </c>
       <c r="G129">
-        <v>23.40355152377628</v>
+        <v>22.38096763225461</v>
       </c>
     </row>
     <row r="130">
@@ -4645,7 +4645,7 @@
         </is>
       </c>
       <c r="G130">
-        <v>14.94162423036545</v>
+        <v>14.87845030180027</v>
       </c>
     </row>
     <row r="131">
@@ -4678,7 +4678,7 @@
         </is>
       </c>
       <c r="G131">
-        <v>26.88802088171896</v>
+        <v>25.73047917049552</v>
       </c>
     </row>
     <row r="132">
@@ -4711,7 +4711,7 @@
         </is>
       </c>
       <c r="G132">
-        <v>14.24409776264411</v>
+        <v>14.18438373560027</v>
       </c>
     </row>
     <row r="133">
@@ -4744,7 +4744,7 @@
         </is>
       </c>
       <c r="G133">
-        <v>30.27157971021305</v>
+        <v>29.0869968668164</v>
       </c>
     </row>
     <row r="134">
@@ -4777,7 +4777,7 @@
         </is>
       </c>
       <c r="G134">
-        <v>13.45902446227108</v>
+        <v>13.40907109875598</v>
       </c>
     </row>
     <row r="135">
@@ -4810,7 +4810,7 @@
         </is>
       </c>
       <c r="G135">
-        <v>33.0593709091422</v>
+        <v>31.99572039296879</v>
       </c>
     </row>
     <row r="136">
@@ -4843,7 +4843,7 @@
         </is>
       </c>
       <c r="G136">
-        <v>12.68210112576414</v>
+        <v>12.64552105936054</v>
       </c>
     </row>
     <row r="137">
@@ -4876,7 +4876,7 @@
         </is>
       </c>
       <c r="G137">
-        <v>35.7405860226602</v>
+        <v>34.89442054259061</v>
       </c>
     </row>
     <row r="138">
@@ -4909,7 +4909,7 @@
         </is>
       </c>
       <c r="G138">
-        <v>11.9932259346639</v>
+        <v>11.97011918177676</v>
       </c>
     </row>
     <row r="139">
@@ -4942,7 +4942,7 @@
         </is>
       </c>
       <c r="G139">
-        <v>38.57472525746721</v>
+        <v>37.96808440024127</v>
       </c>
     </row>
     <row r="140">
@@ -4975,7 +4975,7 @@
         </is>
       </c>
       <c r="G140">
-        <v>11.39608462029988</v>
+        <v>11.38344704427656</v>
       </c>
     </row>
     <row r="141">
@@ -5008,7 +5008,7 @@
         </is>
       </c>
       <c r="G141">
-        <v>41.74368905509428</v>
+        <v>41.33653053781499</v>
       </c>
     </row>
     <row r="142">
@@ -5041,7 +5041,7 @@
         </is>
       </c>
       <c r="G142">
-        <v>10.85629295192884</v>
+        <v>10.85075955861169</v>
       </c>
     </row>
     <row r="143">
@@ -5074,7 +5074,7 @@
         </is>
       </c>
       <c r="G143">
-        <v>45.12957863121383</v>
+        <v>44.86153076440966</v>
       </c>
     </row>
     <row r="144">
@@ -5107,7 +5107,7 @@
         </is>
       </c>
       <c r="G144">
-        <v>10.40007938729971</v>
+        <v>10.39935645318499</v>
       </c>
     </row>
     <row r="145">
@@ -5140,7 +5140,7 @@
         </is>
       </c>
       <c r="G145">
-        <v>48.95483681834711</v>
+        <v>48.77452405338148</v>
       </c>
     </row>
     <row r="146">
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="G146">
-        <v>10.0019177724098</v>
+        <v>10.00481814992133</v>
       </c>
     </row>
     <row r="147">
@@ -5206,7 +5206,7 @@
         </is>
       </c>
       <c r="G147">
-        <v>52.73469862331195</v>
+        <v>52.61113491935404</v>
       </c>
     </row>
     <row r="148">
@@ -5239,7 +5239,7 @@
         </is>
       </c>
       <c r="G148">
-        <v>9.64682423547749</v>
+        <v>9.652755537190691</v>
       </c>
     </row>
     <row r="149">
@@ -5272,7 +5272,7 @@
         </is>
       </c>
       <c r="G149">
-        <v>56.31995672140631</v>
+        <v>56.23529023874336</v>
       </c>
     </row>
     <row r="150">
@@ -5305,7 +5305,7 @@
         </is>
       </c>
       <c r="G150">
-        <v>9.334935058561991</v>
+        <v>9.343411087311724</v>
       </c>
     </row>
     <row r="151">
@@ -5338,7 +5338,7 @@
         </is>
       </c>
       <c r="G151">
-        <v>59.62527202075331</v>
+        <v>59.56724069739862</v>
       </c>
     </row>
     <row r="152">
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="G152">
-        <v>0.7898008962378448</v>
+        <v>0.7892230996361821</v>
       </c>
     </row>
     <row r="153">
@@ -5404,7 +5404,7 @@
         </is>
       </c>
       <c r="G153">
-        <v>0.7898008962378448</v>
+        <v>0.7892230996361821</v>
       </c>
     </row>
     <row r="154">
@@ -5437,7 +5437,7 @@
         </is>
       </c>
       <c r="G154">
-        <v>1.036407023350686</v>
+        <v>1.025543709679333</v>
       </c>
     </row>
     <row r="155">
@@ -5470,7 +5470,7 @@
         </is>
       </c>
       <c r="G155">
-        <v>1.036407023350686</v>
+        <v>1.025543709679333</v>
       </c>
     </row>
     <row r="156">
@@ -5503,7 +5503,7 @@
         </is>
       </c>
       <c r="G156">
-        <v>1.524124956875401</v>
+        <v>1.510159360676202</v>
       </c>
     </row>
     <row r="157">
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c r="G157">
-        <v>1.524124956875401</v>
+        <v>1.510159360676202</v>
       </c>
     </row>
     <row r="158">
@@ -5569,7 +5569,7 @@
         </is>
       </c>
       <c r="G158">
-        <v>2.135145995119714</v>
+        <v>2.115613284084782</v>
       </c>
     </row>
     <row r="159">
@@ -5602,7 +5602,7 @@
         </is>
       </c>
       <c r="G159">
-        <v>2.135145995119714</v>
+        <v>2.115613284084782</v>
       </c>
     </row>
     <row r="160">
@@ -5635,7 +5635,7 @@
         </is>
       </c>
       <c r="G160">
-        <v>2.904228382420921</v>
+        <v>2.876873448364529</v>
       </c>
     </row>
     <row r="161">
@@ -5668,7 +5668,7 @@
         </is>
       </c>
       <c r="G161">
-        <v>2.904228382420921</v>
+        <v>2.876873448364529</v>
       </c>
     </row>
     <row r="162">
@@ -5701,7 +5701,7 @@
         </is>
       </c>
       <c r="G162">
-        <v>3.876570556041197</v>
+        <v>3.837276245800538</v>
       </c>
     </row>
     <row r="163">
@@ -5734,7 +5734,7 @@
         </is>
       </c>
       <c r="G163">
-        <v>3.876570556041197</v>
+        <v>3.837276245800538</v>
       </c>
     </row>
     <row r="164">
@@ -5767,7 +5767,7 @@
         </is>
       </c>
       <c r="G164">
-        <v>5.190997929042657</v>
+        <v>5.135440357982378</v>
       </c>
     </row>
     <row r="165">
@@ -5800,7 +5800,7 @@
         </is>
       </c>
       <c r="G165">
-        <v>5.190997929042657</v>
+        <v>5.135440357982378</v>
       </c>
     </row>
     <row r="166">
@@ -5833,7 +5833,7 @@
         </is>
       </c>
       <c r="G166">
-        <v>6.397195897754669</v>
+        <v>6.321273849787495</v>
       </c>
     </row>
     <row r="167">
@@ -5866,7 +5866,7 @@
         </is>
       </c>
       <c r="G167">
-        <v>6.397195897754669</v>
+        <v>6.321273849787495</v>
       </c>
     </row>
     <row r="168">
@@ -5899,7 +5899,7 @@
         </is>
       </c>
       <c r="G168">
-        <v>8.226259987547715</v>
+        <v>8.119121766103246</v>
       </c>
     </row>
     <row r="169">
@@ -5932,7 +5932,7 @@
         </is>
       </c>
       <c r="G169">
-        <v>8.226259987547715</v>
+        <v>8.119121766103246</v>
       </c>
     </row>
     <row r="170">
@@ -5965,7 +5965,7 @@
         </is>
       </c>
       <c r="G170">
-        <v>10.78067917292112</v>
+        <v>10.62357786217093</v>
       </c>
     </row>
     <row r="171">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="G171">
-        <v>10.78067917292112</v>
+        <v>10.62357786217093</v>
       </c>
     </row>
     <row r="172">
@@ -6031,7 +6031,7 @@
         </is>
       </c>
       <c r="G172">
-        <v>14.27251963122736</v>
+        <v>14.03737839040344</v>
       </c>
     </row>
     <row r="173">
@@ -6064,7 +6064,7 @@
         </is>
       </c>
       <c r="G173">
-        <v>14.27251963122736</v>
+        <v>14.03737839040344</v>
       </c>
     </row>
     <row r="174">
@@ -6097,7 +6097,7 @@
         </is>
       </c>
       <c r="G174">
-        <v>18.89819236269502</v>
+        <v>18.54609760304042</v>
       </c>
     </row>
     <row r="175">
@@ -6130,7 +6130,7 @@
         </is>
       </c>
       <c r="G175">
-        <v>18.89819236269502</v>
+        <v>18.54609760304042</v>
       </c>
     </row>
     <row r="176">
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="G176">
-        <v>21.99655766749998</v>
+        <v>21.95765520512719</v>
       </c>
     </row>
     <row r="177">
@@ -6196,7 +6196,7 @@
         </is>
       </c>
       <c r="G177">
-        <v>24.42895456287432</v>
+        <v>23.95280447163976</v>
       </c>
     </row>
     <row r="178">
@@ -6229,7 +6229,7 @@
         </is>
       </c>
       <c r="G178">
-        <v>22.28614291309746</v>
+        <v>22.15801024438909</v>
       </c>
     </row>
     <row r="179">
@@ -6262,7 +6262,7 @@
         </is>
       </c>
       <c r="G179">
-        <v>33.20514641444181</v>
+        <v>31.70294557570564</v>
       </c>
     </row>
     <row r="180">
@@ -6295,7 +6295,7 @@
         </is>
       </c>
       <c r="G180">
-        <v>21.39905920884812</v>
+        <v>21.25725614256192</v>
       </c>
     </row>
     <row r="181">
@@ -6328,7 +6328,7 @@
         </is>
       </c>
       <c r="G181">
-        <v>38.79126263182641</v>
+        <v>37.04215084111503</v>
       </c>
     </row>
     <row r="182">
@@ -6361,7 +6361,7 @@
         </is>
       </c>
       <c r="G182">
-        <v>20.02005989760769</v>
+        <v>19.87643579541383</v>
       </c>
     </row>
     <row r="183">
@@ -6394,7 +6394,7 @@
         </is>
       </c>
       <c r="G183">
-        <v>42.96792755174048</v>
+        <v>41.17650746146379</v>
       </c>
     </row>
     <row r="184">
@@ -6427,7 +6427,7 @@
         </is>
       </c>
       <c r="G184">
-        <v>18.45660385875385</v>
+        <v>18.32708157411775</v>
       </c>
     </row>
     <row r="185">
@@ -6460,7 +6460,7 @@
         </is>
       </c>
       <c r="G185">
-        <v>45.93399436215196</v>
+        <v>44.32416326572221</v>
       </c>
     </row>
     <row r="186">
@@ -6493,7 +6493,7 @@
         </is>
       </c>
       <c r="G186">
-        <v>16.8901839972393</v>
+        <v>16.78795767519208</v>
       </c>
     </row>
     <row r="187">
@@ -6526,7 +6526,7 @@
         </is>
       </c>
       <c r="G187">
-        <v>48.41446757035663</v>
+        <v>47.13330043297209</v>
       </c>
     </row>
     <row r="188">
@@ -6559,7 +6559,7 @@
         </is>
       </c>
       <c r="G188">
-        <v>15.48029163772849</v>
+        <v>15.40996855991398</v>
       </c>
     </row>
     <row r="189">
@@ -6592,7 +6592,7 @@
         </is>
       </c>
       <c r="G189">
-        <v>50.85041369551791</v>
+        <v>49.93237294238607</v>
       </c>
     </row>
     <row r="190">
@@ -6625,7 +6625,7 @@
         </is>
       </c>
       <c r="G190">
-        <v>14.26562711986447</v>
+        <v>14.2223287761949</v>
       </c>
     </row>
     <row r="191">
@@ -6658,7 +6658,7 @@
         </is>
       </c>
       <c r="G191">
-        <v>53.58109694517369</v>
+        <v>52.96585939273785</v>
       </c>
     </row>
     <row r="192">
@@ -6691,7 +6691,7 @@
         </is>
       </c>
       <c r="G192">
-        <v>13.20181293371447</v>
+        <v>13.17733591701875</v>
       </c>
     </row>
     <row r="193">
@@ -6724,7 +6724,7 @@
         </is>
       </c>
       <c r="G193">
-        <v>56.48626436898299</v>
+        <v>56.08216248898309</v>
       </c>
     </row>
     <row r="194">
@@ -6757,7 +6757,7 @@
         </is>
       </c>
       <c r="G194">
-        <v>12.30000355455411</v>
+        <v>12.28764939762666</v>
       </c>
     </row>
     <row r="195">
@@ -6790,7 +6790,7 @@
         </is>
       </c>
       <c r="G195">
-        <v>59.80972326964391</v>
+        <v>59.53862964727939</v>
       </c>
     </row>
     <row r="196">
@@ -6823,7 +6823,7 @@
         </is>
       </c>
       <c r="G196">
-        <v>11.51765451004899</v>
+        <v>11.51340272884409</v>
       </c>
     </row>
     <row r="197">
@@ -6856,7 +6856,7 @@
         </is>
       </c>
       <c r="G197">
-        <v>62.9474299854208</v>
+        <v>62.76200781548399</v>
       </c>
     </row>
     <row r="198">
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="G198">
-        <v>10.82657030962825</v>
+        <v>10.82822387984282</v>
       </c>
     </row>
     <row r="199">
@@ -6922,7 +6922,7 @@
         </is>
       </c>
       <c r="G199">
-        <v>65.73272466229389</v>
+        <v>65.60590394642527</v>
       </c>
     </row>
     <row r="200">
@@ -6955,7 +6955,7 @@
         </is>
       </c>
       <c r="G200">
-        <v>10.22244236805062</v>
+        <v>10.22852049822737</v>
       </c>
     </row>
     <row r="201">
@@ -6988,7 +6988,7 @@
         </is>
       </c>
       <c r="G201">
-        <v>68.10689383453422</v>
+        <v>68.0206612280267</v>
       </c>
     </row>
     <row r="202">
@@ -7021,7 +7021,7 @@
         </is>
       </c>
       <c r="G202">
-        <v>0.295432860322181</v>
+        <v>0.2952292961548024</v>
       </c>
     </row>
     <row r="203">
@@ -7054,7 +7054,7 @@
         </is>
       </c>
       <c r="G203">
-        <v>0.3118457970067467</v>
+        <v>0.311630923718958</v>
       </c>
     </row>
     <row r="204">
@@ -7087,7 +7087,7 @@
         </is>
       </c>
       <c r="G204">
-        <v>0.475379704562547</v>
+        <v>0.4690370857277862</v>
       </c>
     </row>
     <row r="205">
@@ -7120,7 +7120,7 @@
         </is>
       </c>
       <c r="G205">
-        <v>0.5017896881493553</v>
+        <v>0.4950947016015519</v>
       </c>
     </row>
     <row r="206">
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="G206">
-        <v>0.74848397214645</v>
+        <v>0.7409532443316537</v>
       </c>
     </row>
     <row r="207">
@@ -7186,7 +7186,7 @@
         </is>
       </c>
       <c r="G207">
-        <v>0.7900664150434753</v>
+        <v>0.7821173134611898</v>
       </c>
     </row>
     <row r="208">
@@ -7219,7 +7219,7 @@
         </is>
       </c>
       <c r="G208">
-        <v>1.059466725054776</v>
+        <v>1.049910184149904</v>
       </c>
     </row>
     <row r="209">
@@ -7252,7 +7252,7 @@
         </is>
       </c>
       <c r="G209">
-        <v>1.11832598755782</v>
+        <v>1.108238527713788</v>
       </c>
     </row>
     <row r="210">
@@ -7285,7 +7285,7 @@
         </is>
       </c>
       <c r="G210">
-        <v>1.428188545531923</v>
+        <v>1.416035958230084</v>
       </c>
     </row>
     <row r="211">
@@ -7318,7 +7318,7 @@
         </is>
       </c>
       <c r="G211">
-        <v>1.50753235361703</v>
+        <v>1.4947046225762</v>
       </c>
     </row>
     <row r="212">
@@ -7351,7 +7351,7 @@
         </is>
       </c>
       <c r="G212">
-        <v>1.853541513500507</v>
+        <v>1.837823185878504</v>
       </c>
     </row>
     <row r="213">
@@ -7384,7 +7384,7 @@
         </is>
       </c>
       <c r="G213">
-        <v>1.956516042028314</v>
+        <v>1.939924473982866</v>
       </c>
     </row>
     <row r="214">
@@ -7417,7 +7417,7 @@
         </is>
       </c>
       <c r="G214">
-        <v>2.392660217798988</v>
+        <v>2.37217226143327</v>
       </c>
     </row>
     <row r="215">
@@ -7450,7 +7450,7 @@
         </is>
       </c>
       <c r="G215">
-        <v>2.525585785454488</v>
+        <v>2.503959609290674</v>
       </c>
     </row>
     <row r="216">
@@ -7483,7 +7483,7 @@
         </is>
       </c>
       <c r="G216">
-        <v>2.920305682458435</v>
+        <v>2.89387405207294</v>
       </c>
     </row>
     <row r="217">
@@ -7516,7 +7516,7 @@
         </is>
       </c>
       <c r="G217">
-        <v>3.082544887039459</v>
+        <v>3.054644832743659</v>
       </c>
     </row>
     <row r="218">
@@ -7549,7 +7549,7 @@
         </is>
       </c>
       <c r="G218">
-        <v>3.669381563008118</v>
+        <v>3.63385508292381</v>
       </c>
     </row>
     <row r="219">
@@ -7582,7 +7582,7 @@
         </is>
       </c>
       <c r="G219">
-        <v>3.873236094286345</v>
+        <v>3.835735920864022</v>
       </c>
     </row>
     <row r="220">
@@ -7615,7 +7615,7 @@
         </is>
       </c>
       <c r="G220">
-        <v>4.565783472166334</v>
+        <v>4.517824410698892</v>
       </c>
     </row>
     <row r="221">
@@ -7648,7 +7648,7 @@
         </is>
       </c>
       <c r="G221">
-        <v>4.819438109508907</v>
+        <v>4.768814655737721</v>
       </c>
     </row>
     <row r="222">
@@ -7681,7 +7681,7 @@
         </is>
       </c>
       <c r="G222">
-        <v>6.187959809051659</v>
+        <v>6.117124935862905</v>
       </c>
     </row>
     <row r="223">
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="G223">
-        <v>6.187959809051659</v>
+        <v>6.117124935862905</v>
       </c>
     </row>
     <row r="224">
@@ -7747,7 +7747,7 @@
         </is>
       </c>
       <c r="G224">
-        <v>6.306656871861175</v>
+        <v>6.321635700919888</v>
       </c>
     </row>
     <row r="225">
@@ -7780,7 +7780,7 @@
         </is>
       </c>
       <c r="G225">
-        <v>7.876462122200893</v>
+        <v>7.774785136565031</v>
       </c>
     </row>
     <row r="226">
@@ -7813,7 +7813,7 @@
         </is>
       </c>
       <c r="G226">
-        <v>5.925987015938373</v>
+        <v>5.945139391844929</v>
       </c>
     </row>
     <row r="227">
@@ -7846,7 +7846,7 @@
         </is>
       </c>
       <c r="G227">
-        <v>9.784773002658016</v>
+        <v>9.655716078650299</v>
       </c>
     </row>
     <row r="228">
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="G228">
-        <v>5.601089349922847</v>
+        <v>5.624707100094046</v>
       </c>
     </row>
     <row r="229">
@@ -7912,7 +7912,7 @@
         </is>
       </c>
       <c r="G229">
-        <v>12.57882206780231</v>
+        <v>12.19128151380629</v>
       </c>
     </row>
     <row r="230">
@@ -7945,7 +7945,7 @@
         </is>
       </c>
       <c r="G230">
-        <v>5.344678205897538</v>
+        <v>5.36804958849702</v>
       </c>
     </row>
     <row r="231">
@@ -7978,7 +7978,7 @@
         </is>
       </c>
       <c r="G231">
-        <v>14.89860322143914</v>
+        <v>14.46483293610887</v>
       </c>
     </row>
     <row r="232">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="G232">
-        <v>5.177677194292053</v>
+        <v>5.198728387350182</v>
       </c>
     </row>
     <row r="233">
@@ -8044,7 +8044,7 @@
         </is>
       </c>
       <c r="G233">
-        <v>17.51517736311497</v>
+        <v>17.07188336307036</v>
       </c>
     </row>
     <row r="234">
@@ -8077,7 +8077,7 @@
         </is>
       </c>
       <c r="G234">
-        <v>4.988721102067261</v>
+        <v>5.00541534150462</v>
       </c>
     </row>
     <row r="235">
@@ -8110,7 +8110,7 @@
         </is>
       </c>
       <c r="G235">
-        <v>20.06377468216118</v>
+        <v>19.66490849157652</v>
       </c>
     </row>
     <row r="236">
@@ -8143,7 +8143,7 @@
         </is>
       </c>
       <c r="G236">
-        <v>4.789163848227199</v>
+        <v>4.80091219981513</v>
       </c>
     </row>
     <row r="237">
@@ -8176,7 +8176,7 @@
         </is>
       </c>
       <c r="G237">
-        <v>22.76682983252904</v>
+        <v>22.44841602539632</v>
       </c>
     </row>
     <row r="238">
@@ -8209,7 +8209,7 @@
         </is>
       </c>
       <c r="G238">
-        <v>4.59750352802629</v>
+        <v>4.605165290999079</v>
       </c>
     </row>
     <row r="239">
@@ -8242,7 +8242,7 @@
         </is>
       </c>
       <c r="G239">
-        <v>25.71878671685506</v>
+        <v>25.4890776924146</v>
       </c>
     </row>
     <row r="240">
@@ -8275,7 +8275,7 @@
         </is>
       </c>
       <c r="G240">
-        <v>4.421645665269913</v>
+        <v>4.426630424187309</v>
       </c>
     </row>
     <row r="241">
@@ -8308,7 +8308,7 @@
         </is>
       </c>
       <c r="G241">
-        <v>29.01825100943636</v>
+        <v>28.86267678798626</v>
       </c>
     </row>
     <row r="242">
@@ -8341,7 +8341,7 @@
         </is>
       </c>
       <c r="G242">
-        <v>4.25268746016835</v>
+        <v>4.256279050589031</v>
       </c>
     </row>
     <row r="243">
@@ -8374,7 +8374,7 @@
         </is>
       </c>
       <c r="G243">
-        <v>32.58716936865326</v>
+        <v>32.48360163570752</v>
       </c>
     </row>
     <row r="244">
@@ -8407,7 +8407,7 @@
         </is>
       </c>
       <c r="G244">
-        <v>4.104406078706487</v>
+        <v>4.107496568745158</v>
       </c>
     </row>
     <row r="245">
@@ -8440,7 +8440,7 @@
         </is>
       </c>
       <c r="G245">
-        <v>36.59624016007235</v>
+        <v>36.52574672722631</v>
       </c>
     </row>
     <row r="246">
@@ -8473,7 +8473,7 @@
         </is>
       </c>
       <c r="G246">
-        <v>3.973605870842785</v>
+        <v>3.976748136050456</v>
       </c>
     </row>
     <row r="247">
@@ -8506,7 +8506,7 @@
         </is>
       </c>
       <c r="G247">
-        <v>40.75074828995886</v>
+        <v>40.70201274742362</v>
       </c>
     </row>
     <row r="248">
@@ -8539,7 +8539,7 @@
         </is>
       </c>
       <c r="G248">
-        <v>3.86205788978834</v>
+        <v>3.865550165568842</v>
       </c>
     </row>
     <row r="249">
@@ -8572,7 +8572,7 @@
         </is>
       </c>
       <c r="G249">
-        <v>44.98921929085875</v>
+        <v>44.95545140530164</v>
       </c>
     </row>
     <row r="250">
@@ -8605,7 +8605,7 @@
         </is>
       </c>
       <c r="G250">
-        <v>3.769528855975905</v>
+        <v>3.773491341827794</v>
       </c>
     </row>
     <row r="251">
@@ -8638,7 +8638,7 @@
         </is>
       </c>
       <c r="G251">
-        <v>49.13051074793176</v>
+        <v>49.10658644543338</v>
       </c>
     </row>
     <row r="252">
@@ -8671,7 +8671,7 @@
         </is>
       </c>
       <c r="G252">
-        <v>0.2929298037429034</v>
+        <v>0.2927280275162023</v>
       </c>
     </row>
     <row r="253">
@@ -8704,7 +8704,7 @@
         </is>
       </c>
       <c r="G253">
-        <v>0.3092036817286204</v>
+        <v>0.3089906957115467</v>
       </c>
     </row>
     <row r="254">
@@ -8737,7 +8737,7 @@
         </is>
       </c>
       <c r="G254">
-        <v>0.4661124316449251</v>
+        <v>0.4598950176556959</v>
       </c>
     </row>
     <row r="255">
@@ -8770,7 +8770,7 @@
         </is>
       </c>
       <c r="G255">
-        <v>0.4920075667363099</v>
+        <v>0.4854447408587902</v>
       </c>
     </row>
     <row r="256">
@@ -8803,7 +8803,7 @@
         </is>
       </c>
       <c r="G256">
-        <v>0.7280840229518519</v>
+        <v>0.7207644545602913</v>
       </c>
     </row>
     <row r="257">
@@ -8836,7 +8836,7 @@
         </is>
       </c>
       <c r="G257">
-        <v>0.768533135338066</v>
+        <v>0.7608069242580854</v>
       </c>
     </row>
     <row r="258">
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="G258">
-        <v>1.022968027374306</v>
+        <v>1.013753055961216</v>
       </c>
     </row>
     <row r="259">
@@ -8902,7 +8902,7 @@
         </is>
       </c>
       <c r="G259">
-        <v>1.079799584450657</v>
+        <v>1.070072670181283</v>
       </c>
     </row>
     <row r="260">
@@ -8935,7 +8935,7 @@
         </is>
       </c>
       <c r="G260">
-        <v>1.37097689523429</v>
+        <v>1.359334155182921</v>
       </c>
     </row>
     <row r="261">
@@ -8968,7 +8968,7 @@
         </is>
       </c>
       <c r="G261">
-        <v>1.447142278302862</v>
+        <v>1.43485271935975</v>
       </c>
     </row>
     <row r="262">
@@ -9001,7 +9001,7 @@
         </is>
       </c>
       <c r="G262">
-        <v>1.772974940041353</v>
+        <v>1.757982282569809</v>
       </c>
     </row>
     <row r="263">
@@ -9034,7 +9034,7 @@
         </is>
       </c>
       <c r="G263">
-        <v>1.871473547821429</v>
+        <v>1.855647964934799</v>
       </c>
     </row>
     <row r="264">
@@ -9067,7 +9067,7 @@
         </is>
       </c>
       <c r="G264">
-        <v>2.27840497485922</v>
+        <v>2.258965377500274</v>
       </c>
     </row>
     <row r="265">
@@ -9100,7 +9100,7 @@
         </is>
       </c>
       <c r="G265">
-        <v>2.404983029018065</v>
+        <v>2.384463454028067</v>
       </c>
     </row>
     <row r="266">
@@ -9133,7 +9133,7 @@
         </is>
       </c>
       <c r="G266">
-        <v>2.761804000041364</v>
+        <v>2.736922758024696</v>
       </c>
     </row>
     <row r="267">
@@ -9166,7 +9166,7 @@
         </is>
       </c>
       <c r="G267">
-        <v>2.915237555599218</v>
+        <v>2.888974022359399</v>
       </c>
     </row>
     <row r="268">
@@ -9199,7 +9199,7 @@
         </is>
       </c>
       <c r="G268">
-        <v>3.450320661361087</v>
+        <v>3.417114334905348</v>
       </c>
     </row>
     <row r="269">
@@ -9232,7 +9232,7 @@
         </is>
       </c>
       <c r="G269">
-        <v>3.642005142547814</v>
+        <v>3.606954020177867</v>
       </c>
     </row>
     <row r="270">
@@ -9265,7 +9265,7 @@
         </is>
       </c>
       <c r="G270">
-        <v>4.273505070474704</v>
+        <v>4.228955404209927</v>
       </c>
     </row>
     <row r="271">
@@ -9298,7 +9298,7 @@
         </is>
       </c>
       <c r="G271">
-        <v>4.510922018834409</v>
+        <v>4.463897371110478</v>
       </c>
     </row>
     <row r="272">
@@ -9331,7 +9331,7 @@
         </is>
       </c>
       <c r="G272">
-        <v>5.77298093863362</v>
+        <v>5.707505584896177</v>
       </c>
     </row>
     <row r="273">
@@ -9364,7 +9364,7 @@
         </is>
       </c>
       <c r="G273">
-        <v>5.77298093863362</v>
+        <v>5.707505584896177</v>
       </c>
     </row>
     <row r="274">
@@ -9397,7 +9397,7 @@
         </is>
       </c>
       <c r="G274">
-        <v>5.843288230573793</v>
+        <v>5.857510769560665</v>
       </c>
     </row>
     <row r="275">
@@ -9430,7 +9430,7 @@
         </is>
       </c>
       <c r="G275">
-        <v>7.332469135263276</v>
+        <v>7.238711901830798</v>
       </c>
     </row>
     <row r="276">
@@ -9463,7 +9463,7 @@
         </is>
       </c>
       <c r="G276">
-        <v>5.476164001817605</v>
+        <v>5.494325247083015</v>
       </c>
     </row>
     <row r="277">
@@ -9496,7 +9496,7 @@
         </is>
       </c>
       <c r="G277">
-        <v>9.094570270290863</v>
+        <v>8.976109061469549</v>
       </c>
     </row>
     <row r="278">
@@ -9529,7 +9529,7 @@
         </is>
       </c>
       <c r="G278">
-        <v>5.166931108239496</v>
+        <v>5.189585865144116</v>
       </c>
     </row>
     <row r="279">
@@ -9562,7 +9562,7 @@
         </is>
       </c>
       <c r="G279">
-        <v>11.68158257699518</v>
+        <v>11.32612184848599</v>
       </c>
     </row>
     <row r="280">
@@ -9595,7 +9595,7 @@
         </is>
       </c>
       <c r="G280">
-        <v>4.911121334125668</v>
+        <v>4.933564939123503</v>
       </c>
     </row>
     <row r="281">
@@ -9628,7 +9628,7 @@
         </is>
       </c>
       <c r="G281">
-        <v>13.80777059203894</v>
+        <v>13.41204206285844</v>
       </c>
     </row>
     <row r="282">
@@ -9661,7 +9661,7 @@
         </is>
       </c>
       <c r="G282">
-        <v>4.76434457839119</v>
+        <v>4.78472770100735</v>
       </c>
     </row>
     <row r="283">
@@ -9694,7 +9694,7 @@
         </is>
       </c>
       <c r="G283">
-        <v>16.29893231303306</v>
+        <v>15.89467479023067</v>
       </c>
     </row>
     <row r="284">
@@ -9727,7 +9727,7 @@
         </is>
       </c>
       <c r="G284">
-        <v>4.59775669795347</v>
+        <v>4.614080965078807</v>
       </c>
     </row>
     <row r="285">
@@ -9760,7 +9760,7 @@
         </is>
       </c>
       <c r="G285">
-        <v>18.76311740390178</v>
+        <v>18.39953687626324</v>
       </c>
     </row>
     <row r="286">
@@ -9793,7 +9793,7 @@
         </is>
       </c>
       <c r="G286">
-        <v>4.42219405378004</v>
+        <v>4.433802848388659</v>
       </c>
     </row>
     <row r="287">
@@ -9826,7 +9826,7 @@
         </is>
       </c>
       <c r="G287">
-        <v>21.41387986069695</v>
+        <v>21.12369353860958</v>
       </c>
     </row>
     <row r="288">
@@ -9859,7 +9859,7 @@
         </is>
       </c>
       <c r="G288">
-        <v>4.253726739990149</v>
+        <v>4.261358492712802</v>
       </c>
     </row>
     <row r="289">
@@ -9892,7 +9892,7 @@
         </is>
       </c>
       <c r="G289">
-        <v>24.33782872022509</v>
+        <v>24.12842390793164</v>
       </c>
     </row>
     <row r="290">
@@ -9925,7 +9925,7 @@
         </is>
       </c>
       <c r="G290">
-        <v>4.098995883493121</v>
+        <v>4.103971607952764</v>
       </c>
     </row>
     <row r="291">
@@ -9958,7 +9958,7 @@
         </is>
       </c>
       <c r="G291">
-        <v>27.62322360610587</v>
+        <v>27.48128152408327</v>
       </c>
     </row>
     <row r="292">
@@ -9991,7 +9991,7 @@
         </is>
       </c>
       <c r="G292">
-        <v>3.949567071454919</v>
+        <v>3.9531282614294</v>
       </c>
     </row>
     <row r="293">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="G293">
-        <v>31.19514684526869</v>
+        <v>31.10052690812301</v>
       </c>
     </row>
     <row r="294">
@@ -10057,7 +10057,7 @@
         </is>
       </c>
       <c r="G294">
-        <v>3.8188006680082</v>
+        <v>3.821824239791061</v>
       </c>
     </row>
     <row r="295">
@@ -10090,7 +10090,7 @@
         </is>
       </c>
       <c r="G295">
-        <v>35.22579773790735</v>
+        <v>35.16127845566829</v>
       </c>
     </row>
     <row r="296">
@@ -10123,7 +10123,7 @@
         </is>
       </c>
       <c r="G296">
-        <v>3.703747636802806</v>
+        <v>3.706779821583519</v>
       </c>
     </row>
     <row r="297">
@@ -10156,7 +10156,7 @@
         </is>
       </c>
       <c r="G297">
-        <v>39.43275059824736</v>
+        <v>39.38806887209225</v>
       </c>
     </row>
     <row r="298">
@@ -10189,7 +10189,7 @@
         </is>
       </c>
       <c r="G298">
-        <v>3.605877366609214</v>
+        <v>3.609213973671528</v>
       </c>
     </row>
     <row r="299">
@@ -10222,7 +10222,7 @@
         </is>
       </c>
       <c r="G299">
-        <v>43.75261998249629</v>
+        <v>43.72158474734443</v>
       </c>
     </row>
     <row r="300">
@@ -10255,7 +10255,7 @@
         </is>
       </c>
       <c r="G300">
-        <v>3.525176696747726</v>
+        <v>3.528940880532474</v>
       </c>
     </row>
     <row r="301">
@@ -10288,7 +10288,7 @@
         </is>
       </c>
       <c r="G301">
-        <v>48.00253268538068</v>
+        <v>47.98039412309156</v>
       </c>
     </row>
     <row r="302">
@@ -10321,7 +10321,7 @@
         </is>
       </c>
       <c r="G302">
-        <v>0.3295283857001211</v>
+        <v>0.3292864697502012</v>
       </c>
     </row>
     <row r="303">
@@ -10354,7 +10354,7 @@
         </is>
       </c>
       <c r="G303">
-        <v>0.3478355182390166</v>
+        <v>0.3475801625141013</v>
       </c>
     </row>
     <row r="304">
@@ -10387,7 +10387,7 @@
         </is>
       </c>
       <c r="G304">
-        <v>0.5520886476496339</v>
+        <v>0.5448549370760647</v>
       </c>
     </row>
     <row r="305">
@@ -10420,7 +10420,7 @@
         </is>
       </c>
       <c r="G305">
-        <v>0.5827602391857243</v>
+        <v>0.5751246558025127</v>
       </c>
     </row>
     <row r="306">
@@ -10453,7 +10453,7 @@
         </is>
       </c>
       <c r="G306">
-        <v>0.8994278711822026</v>
+        <v>0.8903886981449273</v>
       </c>
     </row>
     <row r="307">
@@ -10486,7 +10486,7 @@
         </is>
       </c>
       <c r="G307">
-        <v>0.9493960862478801</v>
+        <v>0.9398547369307564</v>
       </c>
     </row>
     <row r="308">
@@ -10519,7 +10519,7 @@
         </is>
       </c>
       <c r="G308">
-        <v>1.320303895164894</v>
+        <v>1.308243069912405</v>
       </c>
     </row>
     <row r="309">
@@ -10552,7 +10552,7 @@
         </is>
       </c>
       <c r="G309">
-        <v>1.393654111562943</v>
+        <v>1.380923240463094</v>
       </c>
     </row>
     <row r="310">
@@ -10585,7 +10585,7 @@
         </is>
       </c>
       <c r="G310">
-        <v>1.843279407637193</v>
+        <v>1.827176855353008</v>
       </c>
     </row>
     <row r="311">
@@ -10618,7 +10618,7 @@
         </is>
       </c>
       <c r="G311">
-        <v>1.945683819172594</v>
+        <v>1.928686680650398</v>
       </c>
     </row>
     <row r="312">
@@ -10651,7 +10651,7 @@
         </is>
       </c>
       <c r="G312">
-        <v>2.47066694644957</v>
+        <v>2.448834859041311</v>
       </c>
     </row>
     <row r="313">
@@ -10684,7 +10684,7 @@
         </is>
       </c>
       <c r="G313">
-        <v>2.607926221252323</v>
+        <v>2.584881240099161</v>
       </c>
     </row>
     <row r="314">
@@ -10717,7 +10717,7 @@
         </is>
       </c>
       <c r="G314">
-        <v>3.299091158394274</v>
+        <v>3.269278974133922</v>
       </c>
     </row>
     <row r="315">
@@ -10750,7 +10750,7 @@
         </is>
       </c>
       <c r="G315">
-        <v>3.482374000527289</v>
+        <v>3.450905583808028</v>
       </c>
     </row>
     <row r="316">
@@ -10783,7 +10783,7 @@
         </is>
       </c>
       <c r="G316">
-        <v>4.163880858075983</v>
+        <v>4.12348862897497</v>
       </c>
     </row>
     <row r="317">
@@ -10816,7 +10816,7 @@
         </is>
       </c>
       <c r="G317">
-        <v>4.395207572413535</v>
+        <v>4.35257133058469</v>
       </c>
     </row>
     <row r="318">
@@ -10849,7 +10849,7 @@
         </is>
       </c>
       <c r="G318">
-        <v>5.390118334230968</v>
+        <v>5.333181928619577</v>
       </c>
     </row>
     <row r="319">
@@ -10882,7 +10882,7 @@
         </is>
       </c>
       <c r="G319">
-        <v>5.689569352799353</v>
+        <v>5.629469813542885</v>
       </c>
     </row>
     <row r="320">
@@ -10915,7 +10915,7 @@
         </is>
       </c>
       <c r="G320">
-        <v>6.904030641248658</v>
+        <v>6.823504363322784</v>
       </c>
     </row>
     <row r="321">
@@ -10948,7 +10948,7 @@
         </is>
       </c>
       <c r="G321">
-        <v>7.287587899095806</v>
+        <v>7.202587939062938</v>
       </c>
     </row>
     <row r="322">
@@ -10981,7 +10981,7 @@
         </is>
       </c>
       <c r="G322">
-        <v>9.351303398398866</v>
+        <v>9.230563526462774</v>
       </c>
     </row>
     <row r="323">
@@ -11014,7 +11014,7 @@
         </is>
       </c>
       <c r="G323">
-        <v>9.351303398398866</v>
+        <v>9.230563526462774</v>
       </c>
     </row>
     <row r="324">
@@ -11047,7 +11047,7 @@
         </is>
       </c>
       <c r="G324">
-        <v>11.91072973537804</v>
+        <v>11.7361147971967</v>
       </c>
     </row>
     <row r="325">
@@ -11080,7 +11080,7 @@
         </is>
       </c>
       <c r="G325">
-        <v>11.91072973537804</v>
+        <v>11.7361147971967</v>
       </c>
     </row>
     <row r="326">
@@ -11113,7 +11113,7 @@
         </is>
       </c>
       <c r="G326">
-        <v>13.38100080812751</v>
+        <v>13.41597717803341</v>
       </c>
     </row>
     <row r="327">
@@ -11146,7 +11146,7 @@
         </is>
       </c>
       <c r="G327">
-        <v>14.78859778264657</v>
+        <v>14.56278586726197</v>
       </c>
     </row>
     <row r="328">
@@ -11179,7 +11179,7 @@
         </is>
       </c>
       <c r="G328">
-        <v>12.89123187458063</v>
+        <v>12.94892870945182</v>
       </c>
     </row>
     <row r="329">
@@ -11212,7 +11212,7 @@
         </is>
       </c>
       <c r="G329">
-        <v>19.1009036462033</v>
+        <v>18.42021065703163</v>
       </c>
     </row>
     <row r="330">
@@ -11245,7 +11245,7 @@
         </is>
       </c>
       <c r="G330">
-        <v>12.44683635452157</v>
+        <v>12.50544485392479</v>
       </c>
     </row>
     <row r="331">
@@ -11278,7 +11278,7 @@
         </is>
       </c>
       <c r="G331">
-        <v>22.40009581999206</v>
+        <v>21.62808519906394</v>
       </c>
     </row>
     <row r="332">
@@ -11311,7 +11311,7 @@
         </is>
       </c>
       <c r="G332">
-        <v>12.07023376189104</v>
+        <v>12.12388441740704</v>
       </c>
     </row>
     <row r="333">
@@ -11344,7 +11344,7 @@
         </is>
       </c>
       <c r="G333">
-        <v>25.65391728033235</v>
+        <v>24.86378984121693</v>
       </c>
     </row>
     <row r="334">
@@ -11377,7 +11377,7 @@
         </is>
       </c>
       <c r="G334">
-        <v>11.60257895273374</v>
+        <v>11.6456520020482</v>
       </c>
     </row>
     <row r="335">
@@ -11410,7 +11410,7 @@
         </is>
       </c>
       <c r="G335">
-        <v>28.50232262953195</v>
+        <v>27.79081606034199</v>
       </c>
     </row>
     <row r="336">
@@ -11443,7 +11443,7 @@
         </is>
       </c>
       <c r="G336">
-        <v>11.09744810961964</v>
+        <v>11.12803655559762</v>
       </c>
     </row>
     <row r="337">
@@ -11476,7 +11476,7 @@
         </is>
       </c>
       <c r="G337">
-        <v>31.27845977392408</v>
+        <v>30.71067721264987</v>
       </c>
     </row>
     <row r="338">
@@ -11509,7 +11509,7 @@
         </is>
       </c>
       <c r="G338">
-        <v>10.61624647400238</v>
+        <v>10.63629931104626</v>
       </c>
     </row>
     <row r="339">
@@ -11542,7 +11542,7 @@
         </is>
       </c>
       <c r="G339">
-        <v>34.15043022768154</v>
+        <v>33.74186362478192</v>
       </c>
     </row>
     <row r="340">
@@ -11575,7 +11575,7 @@
         </is>
       </c>
       <c r="G340">
-        <v>10.17614886072955</v>
+        <v>10.18917135562661</v>
       </c>
     </row>
     <row r="341">
@@ -11608,7 +11608,7 @@
         </is>
       </c>
       <c r="G341">
-        <v>37.28062312354245</v>
+        <v>37.00527615158919</v>
       </c>
     </row>
     <row r="342">
@@ -11641,7 +11641,7 @@
         </is>
       </c>
       <c r="G342">
-        <v>9.758563608169684</v>
+        <v>9.767845673858909</v>
       </c>
     </row>
     <row r="343">
@@ -11674,7 +11674,7 @@
         </is>
       </c>
       <c r="G343">
-        <v>40.57287443356753</v>
+        <v>40.39084238633473</v>
       </c>
     </row>
     <row r="344">
@@ -11707,7 +11707,7 @@
         </is>
       </c>
       <c r="G344">
-        <v>9.39000030093796</v>
+        <v>9.397870018107435</v>
       </c>
     </row>
     <row r="345">
@@ -11740,7 +11740,7 @@
         </is>
       </c>
       <c r="G345">
-        <v>44.20795204284926</v>
+        <v>44.08510304293223</v>
       </c>
     </row>
     <row r="346">
@@ -11773,7 +11773,7 @@
         </is>
       </c>
       <c r="G346">
-        <v>9.067507387494192</v>
+        <v>9.075413965874738</v>
       </c>
     </row>
     <row r="347">
@@ -11806,7 +11806,7 @@
         </is>
       </c>
       <c r="G347">
-        <v>47.81693260382459</v>
+        <v>47.73264737639808</v>
       </c>
     </row>
     <row r="348">
@@ -11839,7 +11839,7 @@
         </is>
       </c>
       <c r="G348">
-        <v>8.792306782705326</v>
+        <v>8.801042557808083</v>
       </c>
     </row>
     <row r="349">
@@ -11872,7 +11872,7 @@
         </is>
       </c>
       <c r="G349">
-        <v>51.34118843828276</v>
+        <v>51.28340756657948</v>
       </c>
     </row>
     <row r="350">
@@ -11905,7 +11905,7 @@
         </is>
       </c>
       <c r="G350">
-        <v>8.563758200486012</v>
+        <v>8.573651583359009</v>
       </c>
     </row>
     <row r="351">
@@ -11938,7 +11938,7 @@
         </is>
       </c>
       <c r="G351">
-        <v>54.71078891907156</v>
+        <v>54.67103897143273</v>
       </c>
     </row>
     <row r="352">
@@ -11971,7 +11971,7 @@
         </is>
       </c>
       <c r="G352">
-        <v>0.3267526141120825</v>
+        <v>0.3265128074224641</v>
       </c>
     </row>
     <row r="353">
@@ -12004,7 +12004,7 @@
         </is>
       </c>
       <c r="G353">
-        <v>0.3449055371183093</v>
+        <v>0.3446524078348233</v>
       </c>
     </row>
     <row r="354">
@@ -12037,7 +12037,7 @@
         </is>
       </c>
       <c r="G354">
-        <v>0.5414108966847557</v>
+        <v>0.5343188429594328</v>
       </c>
     </row>
     <row r="355">
@@ -12070,7 +12070,7 @@
         </is>
       </c>
       <c r="G355">
-        <v>0.5714892798339086</v>
+        <v>0.5640032231238458</v>
       </c>
     </row>
     <row r="356">
@@ -12103,7 +12103,7 @@
         </is>
       </c>
       <c r="G356">
-        <v>0.8751285327394911</v>
+        <v>0.8663402779138962</v>
       </c>
     </row>
     <row r="357">
@@ -12136,7 +12136,7 @@
         </is>
       </c>
       <c r="G357">
-        <v>0.9237467845583514</v>
+        <v>0.9144702933535568</v>
       </c>
     </row>
     <row r="358">
@@ -12169,7 +12169,7 @@
         </is>
       </c>
       <c r="G358">
-        <v>1.275251829128424</v>
+        <v>1.263617070972868</v>
       </c>
     </row>
     <row r="359">
@@ -12202,7 +12202,7 @@
         </is>
       </c>
       <c r="G359">
-        <v>1.346099152968891</v>
+        <v>1.333818019360249</v>
       </c>
     </row>
     <row r="360">
@@ -12235,7 +12235,7 @@
         </is>
       </c>
       <c r="G360">
-        <v>1.77020638798991</v>
+        <v>1.754770176051827</v>
       </c>
     </row>
     <row r="361">
@@ -12268,7 +12268,7 @@
         </is>
       </c>
       <c r="G361">
-        <v>1.868551187322682</v>
+        <v>1.852257408054705</v>
       </c>
     </row>
     <row r="362">
@@ -12301,7 +12301,7 @@
         </is>
       </c>
       <c r="G362">
-        <v>2.364552676843203</v>
+        <v>2.34371156337527</v>
       </c>
     </row>
     <row r="363">
@@ -12334,7 +12334,7 @@
         </is>
       </c>
       <c r="G363">
-        <v>2.495916714445602</v>
+        <v>2.473917761340561</v>
       </c>
     </row>
     <row r="364">
@@ -12367,7 +12367,7 @@
         </is>
       </c>
       <c r="G364">
-        <v>3.14354388201462</v>
+        <v>3.1152289221849</v>
       </c>
     </row>
     <row r="365">
@@ -12400,7 +12400,7 @@
         </is>
       </c>
       <c r="G365">
-        <v>3.31818520879321</v>
+        <v>3.288297195639616</v>
       </c>
     </row>
     <row r="366">
@@ -12433,7 +12433,7 @@
         </is>
       </c>
       <c r="G366">
-        <v>3.940450363895703</v>
+        <v>3.902382834531418</v>
       </c>
     </row>
     <row r="367">
@@ -12466,7 +12466,7 @@
         </is>
       </c>
       <c r="G367">
-        <v>4.159364273001017</v>
+        <v>4.119181880894273</v>
       </c>
     </row>
     <row r="368">
@@ -12499,7 +12499,7 @@
         </is>
       </c>
       <c r="G368">
-        <v>5.071774570965296</v>
+        <v>5.018483029036076</v>
       </c>
     </row>
     <row r="369">
@@ -12532,7 +12532,7 @@
         </is>
       </c>
       <c r="G369">
-        <v>5.353539824907809</v>
+        <v>5.2972876417603</v>
       </c>
     </row>
     <row r="370">
@@ -12565,7 +12565,7 @@
         </is>
       </c>
       <c r="G370">
-        <v>6.466664524514555</v>
+        <v>6.39174219872958</v>
       </c>
     </row>
     <row r="371">
@@ -12598,7 +12598,7 @@
         </is>
       </c>
       <c r="G371">
-        <v>6.825923664765368</v>
+        <v>6.746838987547894</v>
       </c>
     </row>
     <row r="372">
@@ -12631,7 +12631,7 @@
         </is>
       </c>
       <c r="G372">
-        <v>8.729204112581227</v>
+        <v>8.617410594384866</v>
       </c>
     </row>
     <row r="373">
@@ -12664,7 +12664,7 @@
         </is>
       </c>
       <c r="G373">
-        <v>8.729204112581227</v>
+        <v>8.617410594384866</v>
       </c>
     </row>
     <row r="374">
@@ -12697,7 +12697,7 @@
         </is>
       </c>
       <c r="G374">
-        <v>11.09231450847162</v>
+        <v>10.9310535702294</v>
       </c>
     </row>
     <row r="375">
@@ -12730,7 +12730,7 @@
         </is>
       </c>
       <c r="G375">
-        <v>11.09231450847162</v>
+        <v>10.9310535702294</v>
       </c>
     </row>
     <row r="376">
@@ -12763,7 +12763,7 @@
         </is>
       </c>
       <c r="G376">
-        <v>12.37844535888716</v>
+        <v>12.4119037436147</v>
       </c>
     </row>
     <row r="377">
@@ -12796,7 +12796,7 @@
         </is>
       </c>
       <c r="G377">
-        <v>13.7474715294748</v>
+        <v>13.53986544453288</v>
       </c>
     </row>
     <row r="378">
@@ -12829,7 +12829,7 @@
         </is>
       </c>
       <c r="G378">
-        <v>11.90357548172632</v>
+        <v>11.95890800898863</v>
       </c>
     </row>
     <row r="379">
@@ -12862,7 +12862,7 @@
         </is>
       </c>
       <c r="G379">
-        <v>17.73658922460711</v>
+        <v>17.11122224611759</v>
       </c>
     </row>
     <row r="380">
@@ -12895,7 +12895,7 @@
         </is>
       </c>
       <c r="G380">
-        <v>11.44801928617419</v>
+        <v>11.50430963524353</v>
       </c>
     </row>
     <row r="381">
@@ -12928,7 +12928,7 @@
         </is>
       </c>
       <c r="G381">
-        <v>20.75405031135491</v>
+        <v>20.04849326588458</v>
       </c>
     </row>
     <row r="382">
@@ -12961,7 +12961,7 @@
         </is>
       </c>
       <c r="G382">
-        <v>11.11642063377181</v>
+        <v>11.16842665409194</v>
       </c>
     </row>
     <row r="383">
@@ -12994,7 +12994,7 @@
         </is>
       </c>
       <c r="G383">
-        <v>23.86094511833507</v>
+        <v>23.13907529196048</v>
       </c>
     </row>
     <row r="384">
@@ -13027,7 +13027,7 @@
         </is>
       </c>
       <c r="G384">
-        <v>10.70201478096181</v>
+        <v>10.74425487920755</v>
       </c>
     </row>
     <row r="385">
@@ -13060,7 +13060,7 @@
         </is>
       </c>
       <c r="G385">
-        <v>26.63801223053413</v>
+        <v>25.98825725031164</v>
       </c>
     </row>
     <row r="386">
@@ -13093,7 +13093,7 @@
         </is>
       </c>
       <c r="G386">
-        <v>10.2551908772189</v>
+        <v>10.28558461556624</v>
       </c>
     </row>
     <row r="387">
@@ -13126,7 +13126,7 @@
         </is>
       </c>
       <c r="G387">
-        <v>29.40018861720855</v>
+        <v>28.88182494479973</v>
       </c>
     </row>
     <row r="388">
@@ -13159,7 +13159,7 @@
         </is>
       </c>
       <c r="G388">
-        <v>9.830112898233585</v>
+        <v>9.850266041544065</v>
       </c>
     </row>
     <row r="389">
@@ -13192,7 +13192,7 @@
         </is>
       </c>
       <c r="G389">
-        <v>32.29622721916585</v>
+        <v>31.92321103002072</v>
       </c>
     </row>
     <row r="390">
@@ -13225,7 +13225,7 @@
         </is>
       </c>
       <c r="G390">
-        <v>9.440913898782402</v>
+        <v>9.454072343709475</v>
       </c>
     </row>
     <row r="391">
@@ -13258,7 +13258,7 @@
         </is>
       </c>
       <c r="G391">
-        <v>35.46707863831342</v>
+        <v>35.21560280544144</v>
       </c>
     </row>
     <row r="392">
@@ -13291,7 +13291,7 @@
         </is>
       </c>
       <c r="G392">
-        <v>9.069786359941437</v>
+        <v>9.079121484187286</v>
       </c>
     </row>
     <row r="393">
@@ -13324,7 +13324,7 @@
         </is>
       </c>
       <c r="G393">
-        <v>38.81589147864737</v>
+        <v>38.64954658272307</v>
       </c>
     </row>
     <row r="394">
@@ -13357,7 +13357,7 @@
         </is>
       </c>
       <c r="G394">
-        <v>8.742760477476653</v>
+        <v>8.750565297098472</v>
       </c>
     </row>
     <row r="395">
@@ -13390,7 +13390,7 @@
         </is>
       </c>
       <c r="G395">
-        <v>42.52374869735254</v>
+        <v>42.41140909012696</v>
       </c>
     </row>
     <row r="396">
@@ -13423,7 +13423,7 @@
         </is>
       </c>
       <c r="G396">
-        <v>8.457259860530423</v>
+        <v>8.464972921758541</v>
       </c>
     </row>
     <row r="397">
@@ -13456,7 +13456,7 @@
         </is>
       </c>
       <c r="G397">
-        <v>46.23517771894338</v>
+        <v>46.158077510105</v>
       </c>
     </row>
     <row r="398">
@@ -13489,7 +13489,7 @@
         </is>
       </c>
       <c r="G398">
-        <v>8.214068772329584</v>
+        <v>8.222480153101918</v>
       </c>
     </row>
     <row r="399">
@@ -13522,7 +13522,7 @@
         </is>
       </c>
       <c r="G399">
-        <v>49.8873603726403</v>
+        <v>49.83449203178036</v>
       </c>
     </row>
     <row r="400">
@@ -13555,7 +13555,7 @@
         </is>
       </c>
       <c r="G400">
-        <v>8.01333053339741</v>
+        <v>8.022778528327505</v>
       </c>
     </row>
     <row r="401">
@@ -13588,7 +13588,7 @@
         </is>
       </c>
       <c r="G401">
-        <v>53.40764808575982</v>
+        <v>53.37118106653111</v>
       </c>
     </row>
     <row r="402">
@@ -13654,7 +13654,7 @@
         </is>
       </c>
       <c r="G403">
-        <v>0.3299272917827096</v>
+        <v>0.3299550423828091</v>
       </c>
     </row>
     <row r="404">
@@ -13720,7 +13720,7 @@
         </is>
       </c>
       <c r="G405">
-        <v>0.5015297382650249</v>
+        <v>0.4948535356949978</v>
       </c>
     </row>
     <row r="406">
@@ -13786,7 +13786,7 @@
         </is>
       </c>
       <c r="G407">
-        <v>0.7616529233975217</v>
+        <v>0.753761589124459</v>
       </c>
     </row>
     <row r="408">
@@ -13852,7 +13852,7 @@
         </is>
       </c>
       <c r="G409">
-        <v>1.059193270732959</v>
+        <v>1.049228307686498</v>
       </c>
     </row>
     <row r="410">
@@ -13918,7 +13918,7 @@
         </is>
       </c>
       <c r="G411">
-        <v>1.412142249442524</v>
+        <v>1.399500001326464</v>
       </c>
     </row>
     <row r="412">
@@ -13984,7 +13984,7 @@
         </is>
       </c>
       <c r="G413">
-        <v>1.825019386607998</v>
+        <v>1.808636351996635</v>
       </c>
     </row>
     <row r="414">
@@ -14050,7 +14050,7 @@
         </is>
       </c>
       <c r="G415">
-        <v>2.353642848391182</v>
+        <v>2.332299699907427</v>
       </c>
     </row>
     <row r="416">
@@ -14116,7 +14116,7 @@
         </is>
       </c>
       <c r="G417">
-        <v>2.852205918467449</v>
+        <v>2.824817911340774</v>
       </c>
     </row>
     <row r="418">
@@ -14182,7 +14182,7 @@
         </is>
       </c>
       <c r="G419">
-        <v>3.566790106144984</v>
+        <v>3.530072770038457</v>
       </c>
     </row>
     <row r="420">
@@ -14248,7 +14248,7 @@
         </is>
       </c>
       <c r="G421">
-        <v>4.436655304387472</v>
+        <v>4.387137597383138</v>
       </c>
     </row>
     <row r="422">
@@ -14281,7 +14281,7 @@
         </is>
       </c>
       <c r="G422">
-        <v>5.710464592335288</v>
+        <v>5.641211526833376</v>
       </c>
     </row>
     <row r="423">
@@ -14314,7 +14314,7 @@
         </is>
       </c>
       <c r="G423">
-        <v>5.710464592335288</v>
+        <v>5.641211526833376</v>
       </c>
     </row>
     <row r="424">
@@ -14347,7 +14347,7 @@
         </is>
       </c>
       <c r="G424">
-        <v>5.840884029189191</v>
+        <v>5.850601717712401</v>
       </c>
     </row>
     <row r="425">
@@ -14380,7 +14380,7 @@
         </is>
       </c>
       <c r="G425">
-        <v>7.295100944079573</v>
+        <v>7.195796594431231</v>
       </c>
     </row>
     <row r="426">
@@ -14413,7 +14413,7 @@
         </is>
       </c>
       <c r="G426">
-        <v>5.505642686660331</v>
+        <v>5.519576602499745</v>
       </c>
     </row>
     <row r="427">
@@ -14446,7 +14446,7 @@
         </is>
       </c>
       <c r="G427">
-        <v>9.09160895997317</v>
+        <v>8.965401157648936</v>
       </c>
     </row>
     <row r="428">
@@ -14479,7 +14479,7 @@
         </is>
       </c>
       <c r="G428">
-        <v>5.222190849498949</v>
+        <v>5.236218126515933</v>
       </c>
     </row>
     <row r="429">
@@ -14512,7 +14512,7 @@
         </is>
       </c>
       <c r="G429">
-        <v>11.72957538794135</v>
+        <v>11.3508219380217</v>
       </c>
     </row>
     <row r="430">
@@ -14545,7 +14545,7 @@
         </is>
       </c>
       <c r="G430">
-        <v>4.970472994374156</v>
+        <v>4.984661765423469</v>
       </c>
     </row>
     <row r="431">
@@ -14578,7 +14578,7 @@
         </is>
       </c>
       <c r="G431">
-        <v>13.85784032214887</v>
+        <v>13.43398413623322</v>
       </c>
     </row>
     <row r="432">
@@ -14611,7 +14611,7 @@
         </is>
       </c>
       <c r="G432">
-        <v>4.807749007537482</v>
+        <v>4.820768091105183</v>
       </c>
     </row>
     <row r="433">
@@ -14644,7 +14644,7 @@
         </is>
       </c>
       <c r="G433">
-        <v>16.2668883109633</v>
+        <v>15.83370041750186</v>
       </c>
     </row>
     <row r="434">
@@ -14677,7 +14677,7 @@
         </is>
       </c>
       <c r="G434">
-        <v>4.628614288936708</v>
+        <v>4.639164009914959</v>
       </c>
     </row>
     <row r="435">
@@ -14710,7 +14710,7 @@
         </is>
       </c>
       <c r="G435">
-        <v>18.61934481496943</v>
+        <v>18.22974635094755</v>
       </c>
     </row>
     <row r="436">
@@ -14743,7 +14743,7 @@
         </is>
       </c>
       <c r="G436">
-        <v>4.446532576780895</v>
+        <v>4.454207482104322</v>
       </c>
     </row>
     <row r="437">
@@ -14776,7 +14776,7 @@
         </is>
       </c>
       <c r="G437">
-        <v>21.14272696003668</v>
+        <v>20.83187942409156</v>
       </c>
     </row>
     <row r="438">
@@ -14809,7 +14809,7 @@
         </is>
       </c>
       <c r="G438">
-        <v>4.277214950870881</v>
+        <v>4.282474859232104</v>
       </c>
     </row>
     <row r="439">
@@ -14842,7 +14842,7 @@
         </is>
       </c>
       <c r="G439">
-        <v>23.93272590025586</v>
+        <v>23.70860778796182</v>
       </c>
     </row>
     <row r="440">
@@ -14875,7 +14875,7 @@
         </is>
       </c>
       <c r="G440">
-        <v>4.124979639122073</v>
+        <v>4.128629103235474</v>
       </c>
     </row>
     <row r="441">
@@ -14908,7 +14908,7 @@
         </is>
       </c>
       <c r="G441">
-        <v>27.07804533374172</v>
+        <v>26.92633295166621</v>
       </c>
     </row>
     <row r="442">
@@ -14941,7 +14941,7 @@
         </is>
       </c>
       <c r="G442">
-        <v>3.979095079250525</v>
+        <v>3.981927240565126</v>
       </c>
     </row>
     <row r="443">
@@ -14974,7 +14974,7 @@
         </is>
       </c>
       <c r="G443">
-        <v>30.49865024920927</v>
+        <v>30.39767806633019</v>
       </c>
     </row>
     <row r="444">
@@ -15007,7 +15007,7 @@
         </is>
       </c>
       <c r="G444">
-        <v>3.852145888664432</v>
+        <v>3.85475868600831</v>
       </c>
     </row>
     <row r="445">
@@ -15040,7 +15040,7 @@
         </is>
       </c>
       <c r="G445">
-        <v>34.35626235047143</v>
+        <v>34.28751764403407</v>
       </c>
     </row>
     <row r="446">
@@ -15073,7 +15073,7 @@
         </is>
       </c>
       <c r="G446">
-        <v>3.739820859235333</v>
+        <v>3.742613672240835</v>
       </c>
     </row>
     <row r="447">
@@ -15106,7 +15106,7 @@
         </is>
       </c>
       <c r="G447">
-        <v>38.36387810176014</v>
+        <v>38.31630626999881</v>
       </c>
     </row>
     <row r="448">
@@ -15139,7 +15139,7 @@
         </is>
       </c>
       <c r="G448">
-        <v>3.643249763445735</v>
+        <v>3.646445660921244</v>
       </c>
     </row>
     <row r="449">
@@ -15172,7 +15172,7 @@
         </is>
       </c>
       <c r="G449">
-        <v>42.45246203491532</v>
+        <v>42.41944578900456</v>
       </c>
     </row>
     <row r="450">
@@ -15205,7 +15205,7 @@
         </is>
       </c>
       <c r="G450">
-        <v>3.562464461264107</v>
+        <v>3.566146373296406</v>
       </c>
     </row>
     <row r="451">
@@ -15238,7 +15238,7 @@
         </is>
       </c>
       <c r="G451">
-        <v>46.44530205836991</v>
+        <v>46.42185904308168</v>
       </c>
     </row>
     <row r="452">
@@ -15304,7 +15304,7 @@
         </is>
       </c>
       <c r="G453">
-        <v>0.3294525007221907</v>
+        <v>0.3294802219794807</v>
       </c>
     </row>
     <row r="454">
@@ -15370,7 +15370,7 @@
         </is>
       </c>
       <c r="G455">
-        <v>0.4998694924593177</v>
+        <v>0.4932156520137487</v>
       </c>
     </row>
     <row r="456">
@@ -15436,7 +15436,7 @@
         </is>
       </c>
       <c r="G457">
-        <v>0.7581324834252301</v>
+        <v>0.7502786350111098</v>
       </c>
     </row>
     <row r="458">
@@ -15502,7 +15502,7 @@
         </is>
       </c>
       <c r="G459">
-        <v>1.053009671070268</v>
+        <v>1.043105015731367</v>
       </c>
     </row>
     <row r="460">
@@ -15568,7 +15568,7 @@
         </is>
       </c>
       <c r="G461">
-        <v>1.402615210209727</v>
+        <v>1.390062248753906</v>
       </c>
     </row>
     <row r="462">
@@ -15634,7 +15634,7 @@
         </is>
       </c>
       <c r="G463">
-        <v>1.811679503224659</v>
+        <v>1.795423612311349</v>
       </c>
     </row>
     <row r="464">
@@ -15700,7 +15700,7 @@
         </is>
       </c>
       <c r="G465">
-        <v>2.334721055414729</v>
+        <v>2.313561661508297</v>
       </c>
     </row>
     <row r="466">
@@ -15766,7 +15766,7 @@
         </is>
       </c>
       <c r="G467">
-        <v>2.826231198565247</v>
+        <v>2.799112694502192</v>
       </c>
     </row>
     <row r="468">
@@ -15832,7 +15832,7 @@
         </is>
       </c>
       <c r="G469">
-        <v>3.531117225233121</v>
+        <v>3.494801619855694</v>
       </c>
     </row>
     <row r="470">
@@ -15898,7 +15898,7 @@
         </is>
       </c>
       <c r="G471">
-        <v>4.389074202485944</v>
+        <v>4.340146232420311</v>
       </c>
     </row>
     <row r="472">
@@ -15931,7 +15931,7 @@
         </is>
       </c>
       <c r="G472">
-        <v>5.646315864848741</v>
+        <v>5.577940531101348</v>
       </c>
     </row>
     <row r="473">
@@ -15964,7 +15964,7 @@
         </is>
       </c>
       <c r="G473">
-        <v>5.646315864848741</v>
+        <v>5.577940531101348</v>
       </c>
     </row>
     <row r="474">
@@ -15997,7 +15997,7 @@
         </is>
       </c>
       <c r="G474">
-        <v>5.746012300508974</v>
+        <v>5.755317482015188</v>
       </c>
     </row>
     <row r="475">
@@ -16030,7 +16030,7 @@
         </is>
       </c>
       <c r="G475">
-        <v>7.210752014026537</v>
+        <v>7.112745134312513</v>
       </c>
     </row>
     <row r="476">
@@ -16063,7 +16063,7 @@
         </is>
       </c>
       <c r="G476">
-        <v>5.409283932011264</v>
+        <v>5.422679788425627</v>
       </c>
     </row>
     <row r="477">
@@ -16096,7 +16096,7 @@
         </is>
       </c>
       <c r="G477">
-        <v>8.984386337922315</v>
+        <v>8.859913525099689</v>
       </c>
     </row>
     <row r="478">
@@ -16129,7 +16129,7 @@
         </is>
       </c>
       <c r="G478">
-        <v>5.125688600670484</v>
+        <v>5.138644319912265</v>
       </c>
     </row>
     <row r="479">
@@ -16162,7 +16162,7 @@
         </is>
       </c>
       <c r="G479">
-        <v>11.58999916245667</v>
+        <v>11.21649940463062</v>
       </c>
     </row>
     <row r="480">
@@ -16195,7 +16195,7 @@
         </is>
       </c>
       <c r="G480">
-        <v>4.867797031323535</v>
+        <v>4.880755204177803</v>
       </c>
     </row>
     <row r="481">
@@ -16228,7 +16228,7 @@
         </is>
       </c>
       <c r="G481">
-        <v>13.68828993768479</v>
+        <v>13.2706846734732</v>
       </c>
     </row>
     <row r="482">
@@ -16261,7 +16261,7 @@
         </is>
       </c>
       <c r="G482">
-        <v>4.699104379571763</v>
+        <v>4.710801908995105</v>
       </c>
     </row>
     <row r="483">
@@ -16294,7 +16294,7 @@
         </is>
       </c>
       <c r="G483">
-        <v>16.07881624972095</v>
+        <v>15.65204231803156</v>
       </c>
     </row>
     <row r="484">
@@ -16327,7 +16327,7 @@
         </is>
       </c>
       <c r="G484">
-        <v>4.51259784588902</v>
+        <v>4.521888536935636</v>
       </c>
     </row>
     <row r="485">
@@ -16360,7 +16360,7 @@
         </is>
       </c>
       <c r="G485">
-        <v>18.41939294885659</v>
+        <v>18.03558856154841</v>
       </c>
     </row>
     <row r="486">
@@ -16393,7 +16393,7 @@
         </is>
       </c>
       <c r="G486">
-        <v>4.32251410613134</v>
+        <v>4.329143831819032</v>
       </c>
     </row>
     <row r="487">
@@ -16426,7 +16426,7 @@
         </is>
       </c>
       <c r="G487">
-        <v>20.93582593517953</v>
+        <v>20.62961056534196</v>
       </c>
     </row>
     <row r="488">
@@ -16459,7 +16459,7 @@
         </is>
       </c>
       <c r="G488">
-        <v>4.145179652177187</v>
+        <v>4.149674936057993</v>
       </c>
     </row>
     <row r="489">
@@ -16492,7 +16492,7 @@
         </is>
       </c>
       <c r="G489">
-        <v>23.72233694879998</v>
+        <v>23.50154854612315</v>
       </c>
     </row>
     <row r="490">
@@ -16525,7 +16525,7 @@
         </is>
       </c>
       <c r="G490">
-        <v>3.985643900219618</v>
+        <v>3.988777808426062</v>
       </c>
     </row>
     <row r="491">
@@ -16558,7 +16558,7 @@
         </is>
       </c>
       <c r="G491">
-        <v>26.86596588473819</v>
+        <v>26.71648767798955</v>
       </c>
     </row>
     <row r="492">
@@ -16591,7 +16591,7 @@
         </is>
       </c>
       <c r="G492">
-        <v>3.83363393480378</v>
+        <v>3.836120792895407</v>
       </c>
     </row>
     <row r="493">
@@ -16624,7 +16624,7 @@
         </is>
       </c>
       <c r="G493">
-        <v>30.28725261411457</v>
+        <v>30.18774622490661</v>
       </c>
     </row>
     <row r="494">
@@ -16657,7 +16657,7 @@
         </is>
       </c>
       <c r="G494">
-        <v>3.700988433554631</v>
+        <v>3.70335213610346</v>
       </c>
     </row>
     <row r="495">
@@ -16690,7 +16690,7 @@
         </is>
       </c>
       <c r="G495">
-        <v>34.14812475982358</v>
+        <v>34.08035874189561</v>
       </c>
     </row>
     <row r="496">
@@ -16723,7 +16723,7 @@
         </is>
       </c>
       <c r="G496">
-        <v>3.583558292288267</v>
+        <v>3.586147934512283</v>
       </c>
     </row>
     <row r="497">
@@ -16756,7 +16756,7 @@
         </is>
       </c>
       <c r="G497">
-        <v>38.16356944623382</v>
+        <v>38.11666211363002</v>
       </c>
     </row>
     <row r="498">
@@ -16789,7 +16789,7 @@
         </is>
       </c>
       <c r="G498">
-        <v>3.482247765113974</v>
+        <v>3.485256899797526</v>
       </c>
     </row>
     <row r="499">
@@ -16822,7 +16822,7 @@
         </is>
       </c>
       <c r="G499">
-        <v>42.26439493438187</v>
+        <v>42.23182729081034</v>
       </c>
     </row>
     <row r="500">
@@ -16855,7 +16855,7 @@
         </is>
       </c>
       <c r="G500">
-        <v>3.39723614635704</v>
+        <v>3.400731331217682</v>
       </c>
     </row>
     <row r="501">
@@ -16888,7 +16888,7 @@
         </is>
       </c>
       <c r="G501">
-        <v>46.27360916510361</v>
+        <v>46.25046038127897</v>
       </c>
     </row>
     <row r="502">
@@ -16954,7 +16954,7 @@
         </is>
       </c>
       <c r="G503">
-        <v>0.3683669654486543</v>
+        <v>0.3683978151926927</v>
       </c>
     </row>
     <row r="504">
@@ -17020,7 +17020,7 @@
         </is>
       </c>
       <c r="G505">
-        <v>0.5842801890682948</v>
+        <v>0.5766520149203761</v>
       </c>
     </row>
     <row r="506">
@@ -17086,7 +17086,7 @@
         </is>
       </c>
       <c r="G507">
-        <v>0.919618214385124</v>
+        <v>0.9101259022032354</v>
       </c>
     </row>
     <row r="508">
@@ -17152,7 +17152,7 @@
         </is>
       </c>
       <c r="G509">
-        <v>1.328229393088739</v>
+        <v>1.315623239041714</v>
       </c>
     </row>
     <row r="510">
@@ -17218,7 +17218,7 @@
         </is>
       </c>
       <c r="G511">
-        <v>1.836397457674078</v>
+        <v>1.8196023512021</v>
       </c>
     </row>
     <row r="512">
@@ -17284,7 +17284,7 @@
         </is>
       </c>
       <c r="G513">
-        <v>2.454493306904165</v>
+        <v>2.431672323917352</v>
       </c>
     </row>
     <row r="514">
@@ -17350,7 +17350,7 @@
         </is>
       </c>
       <c r="G515">
-        <v>3.27869319707893</v>
+        <v>3.247543217519112</v>
       </c>
     </row>
     <row r="516">
@@ -17416,7 +17416,7 @@
         </is>
       </c>
       <c r="G517">
-        <v>4.113021990240127</v>
+        <v>4.071048031984064</v>
       </c>
     </row>
     <row r="518">
@@ -17482,7 +17482,7 @@
         </is>
       </c>
       <c r="G519">
-        <v>5.30520521684435</v>
+        <v>5.246204456749606</v>
       </c>
     </row>
     <row r="520">
@@ -17548,7 +17548,7 @@
         </is>
       </c>
       <c r="G521">
-        <v>6.801068041897674</v>
+        <v>6.717725898621237</v>
       </c>
     </row>
     <row r="522">
@@ -17581,7 +17581,7 @@
         </is>
       </c>
       <c r="G522">
-        <v>8.755168928740076</v>
+        <v>8.636909383782607</v>
       </c>
     </row>
     <row r="523">
@@ -17614,7 +17614,7 @@
         </is>
       </c>
       <c r="G523">
-        <v>8.755168928740076</v>
+        <v>8.636909383782607</v>
       </c>
     </row>
     <row r="524">
@@ -17647,7 +17647,7 @@
         </is>
       </c>
       <c r="G524">
-        <v>11.19773802903342</v>
+        <v>11.02682023986971</v>
       </c>
     </row>
     <row r="525">
@@ -17680,7 +17680,7 @@
         </is>
       </c>
       <c r="G525">
-        <v>11.19773802903342</v>
+        <v>11.02682023986971</v>
       </c>
     </row>
     <row r="526">
@@ -17713,7 +17713,7 @@
         </is>
       </c>
       <c r="G526">
-        <v>12.62377927281551</v>
+        <v>12.64941213227061</v>
       </c>
     </row>
     <row r="527">
@@ -17746,7 +17746,7 @@
         </is>
       </c>
       <c r="G527">
-        <v>13.95190390397207</v>
+        <v>13.73084285750937</v>
       </c>
     </row>
     <row r="528">
@@ -17779,7 +17779,7 @@
         </is>
       </c>
       <c r="G528">
-        <v>12.19551087982679</v>
+        <v>12.23406674687038</v>
       </c>
     </row>
     <row r="529">
@@ -17812,7 +17812,7 @@
         </is>
       </c>
       <c r="G529">
-        <v>18.0708845736726</v>
+        <v>17.40402600225666</v>
       </c>
     </row>
     <row r="530">
@@ -17845,7 +17845,7 @@
         </is>
       </c>
       <c r="G530">
-        <v>11.7350208670407</v>
+        <v>11.77403270387331</v>
       </c>
     </row>
     <row r="531">
@@ -17878,7 +17878,7 @@
         </is>
       </c>
       <c r="G531">
-        <v>21.12044518076019</v>
+        <v>20.36436690523736</v>
       </c>
     </row>
     <row r="532">
@@ -17911,7 +17911,7 @@
         </is>
       </c>
       <c r="G532">
-        <v>11.34854998760816</v>
+        <v>11.3839662487008</v>
       </c>
     </row>
     <row r="533">
@@ -17944,7 +17944,7 @@
         </is>
       </c>
       <c r="G533">
-        <v>24.1219932561836</v>
+        <v>23.34816063982168</v>
       </c>
     </row>
     <row r="534">
@@ -17977,7 +17977,7 @@
         </is>
       </c>
       <c r="G534">
-        <v>10.88301938586607</v>
+        <v>10.91126300572981</v>
       </c>
     </row>
     <row r="535">
@@ -18010,7 +18010,7 @@
         </is>
       </c>
       <c r="G535">
-        <v>26.7371539446039</v>
+        <v>26.04063726975734</v>
       </c>
     </row>
     <row r="536">
@@ -18043,7 +18043,7 @@
         </is>
       </c>
       <c r="G536">
-        <v>10.39819359842041</v>
+        <v>10.41836527347691</v>
       </c>
     </row>
     <row r="537">
@@ -18076,7 +18076,7 @@
         </is>
       </c>
       <c r="G537">
-        <v>29.31065448915776</v>
+        <v>28.75511739369949</v>
       </c>
     </row>
     <row r="538">
@@ -18109,7 +18109,7 @@
         </is>
       </c>
       <c r="G538">
-        <v>9.950174547622614</v>
+        <v>9.963762741249708</v>
       </c>
     </row>
     <row r="539">
@@ -18142,7 +18142,7 @@
         </is>
       </c>
       <c r="G539">
-        <v>32.01151792894348</v>
+        <v>31.61199130623163</v>
       </c>
     </row>
     <row r="540">
@@ -18175,7 +18175,7 @@
         </is>
       </c>
       <c r="G540">
-        <v>9.549088916501251</v>
+        <v>9.558370086607255</v>
       </c>
     </row>
     <row r="541">
@@ -18208,7 +18208,7 @@
         </is>
       </c>
       <c r="G541">
-        <v>34.98781499345808</v>
+        <v>34.71870707376941</v>
       </c>
     </row>
     <row r="542">
@@ -18241,7 +18241,7 @@
         </is>
       </c>
       <c r="G542">
-        <v>9.171793354995476</v>
+        <v>9.17889588780163</v>
       </c>
     </row>
     <row r="543">
@@ -18274,7 +18274,7 @@
         </is>
       </c>
       <c r="G543">
-        <v>38.13851316124125</v>
+        <v>37.96068372450856</v>
       </c>
     </row>
     <row r="544">
@@ -18307,7 +18307,7 @@
         </is>
       </c>
       <c r="G544">
-        <v>8.842035150135885</v>
+        <v>8.848530714019953</v>
       </c>
     </row>
     <row r="545">
@@ -18340,7 +18340,7 @@
         </is>
       </c>
       <c r="G545">
-        <v>41.63423399244252</v>
+        <v>41.51423455956114</v>
       </c>
     </row>
     <row r="546">
@@ -18373,7 +18373,7 @@
         </is>
       </c>
       <c r="G546">
-        <v>8.553704644307238</v>
+        <v>8.560625530770436</v>
       </c>
     </row>
     <row r="547">
@@ -18406,7 +18406,7 @@
         </is>
       </c>
       <c r="G547">
-        <v>45.11441277718693</v>
+        <v>45.03205414710039</v>
       </c>
     </row>
     <row r="548">
@@ -18439,7 +18439,7 @@
         </is>
       </c>
       <c r="G548">
-        <v>8.306261366918708</v>
+        <v>8.314187818173089</v>
       </c>
     </row>
     <row r="549">
@@ -18472,7 +18472,7 @@
         </is>
       </c>
       <c r="G549">
-        <v>48.51088953423478</v>
+        <v>48.45438299006178</v>
       </c>
     </row>
     <row r="550">
@@ -18505,7 +18505,7 @@
         </is>
       </c>
       <c r="G550">
-        <v>8.100075146101787</v>
+        <v>8.109226688261813</v>
       </c>
     </row>
     <row r="551">
@@ -18538,7 +18538,7 @@
         </is>
       </c>
       <c r="G551">
-        <v>51.75722685983499</v>
+        <v>51.71829823850311</v>
       </c>
     </row>
     <row r="552">
@@ -18604,7 +18604,7 @@
         </is>
       </c>
       <c r="G553">
-        <v>0.3678395656880682</v>
+        <v>0.3678703832662675</v>
       </c>
     </row>
     <row r="554">
@@ -18670,7 +18670,7 @@
         </is>
       </c>
       <c r="G555">
-        <v>0.5823595102122362</v>
+        <v>0.5747567060320797</v>
       </c>
     </row>
     <row r="556">
@@ -18736,7 +18736,7 @@
         </is>
       </c>
       <c r="G557">
-        <v>0.9153997803731337</v>
+        <v>0.9059521580177733</v>
       </c>
     </row>
     <row r="558">
@@ -18802,7 +18802,7 @@
         </is>
       </c>
       <c r="G559">
-        <v>1.320537558751351</v>
+        <v>1.308006908372366</v>
       </c>
     </row>
     <row r="560">
@@ -18868,7 +18868,7 @@
         </is>
       </c>
       <c r="G561">
-        <v>1.82411453263987</v>
+        <v>1.807436599288165</v>
       </c>
     </row>
     <row r="562">
@@ -18934,7 +18934,7 @@
         </is>
       </c>
       <c r="G563">
-        <v>2.436725787567779</v>
+        <v>2.414079240865233</v>
       </c>
     </row>
     <row r="564">
@@ -19000,7 +19000,7 @@
         </is>
       </c>
       <c r="G565">
-        <v>3.252601777823785</v>
+        <v>3.221715532986313</v>
       </c>
     </row>
     <row r="566">
@@ -19066,7 +19066,7 @@
         </is>
       </c>
       <c r="G567">
-        <v>4.075890803295255</v>
+        <v>4.034322902487276</v>
       </c>
     </row>
     <row r="568">
@@ -19132,7 +19132,7 @@
         </is>
       </c>
       <c r="G569">
-        <v>5.252558787932047</v>
+        <v>5.194192098901836</v>
       </c>
     </row>
     <row r="570">
@@ -19198,7 +19198,7 @@
         </is>
       </c>
       <c r="G571">
-        <v>6.728652458398897</v>
+        <v>6.646284108916308</v>
       </c>
     </row>
     <row r="572">
@@ -19231,7 +19231,7 @@
         </is>
       </c>
       <c r="G572">
-        <v>8.657270097276429</v>
+        <v>8.540481642896024</v>
       </c>
     </row>
     <row r="573">
@@ -19264,7 +19264,7 @@
         </is>
       </c>
       <c r="G573">
-        <v>8.657270097276429</v>
+        <v>8.540481642896024</v>
       </c>
     </row>
     <row r="574">
@@ -19297,7 +19297,7 @@
         </is>
       </c>
       <c r="G574">
-        <v>11.06845948476775</v>
+        <v>10.89973863501913</v>
       </c>
     </row>
     <row r="575">
@@ -19330,7 +19330,7 @@
         </is>
       </c>
       <c r="G575">
-        <v>11.06845948476775</v>
+        <v>10.89973863501913</v>
       </c>
     </row>
     <row r="576">
@@ -19363,7 +19363,7 @@
         </is>
       </c>
       <c r="G576">
-        <v>12.41390364723981</v>
+        <v>12.43844093000253</v>
       </c>
     </row>
     <row r="577">
@@ -19396,7 +19396,7 @@
         </is>
       </c>
       <c r="G577">
-        <v>13.78703967126381</v>
+        <v>13.56896921187864</v>
       </c>
     </row>
     <row r="578">
@@ -19429,7 +19429,7 @@
         </is>
       </c>
       <c r="G578">
-        <v>11.98227576904086</v>
+        <v>12.01829464294685</v>
       </c>
     </row>
     <row r="579">
@@ -19462,7 +19462,7 @@
         </is>
       </c>
       <c r="G579">
-        <v>17.85468016265829</v>
+        <v>17.19691984282917</v>
       </c>
     </row>
     <row r="580">
@@ -19495,7 +19495,7 @@
         </is>
       </c>
       <c r="G580">
-        <v>11.50567935893408</v>
+        <v>11.54166152224279</v>
       </c>
     </row>
     <row r="581">
@@ -19528,7 +19528,7 @@
         </is>
       </c>
       <c r="G581">
-        <v>20.85994810825926</v>
+        <v>20.11483247609937</v>
       </c>
     </row>
     <row r="582">
@@ -19561,7 +19561,7 @@
         </is>
       </c>
       <c r="G582">
-        <v>11.10569546765755</v>
+        <v>11.13773064137501</v>
       </c>
     </row>
     <row r="583">
@@ -19594,7 +19594,7 @@
         </is>
       </c>
       <c r="G583">
-        <v>23.83984040391564</v>
+        <v>23.0772669579675</v>
       </c>
     </row>
     <row r="584">
@@ -19627,7 +19627,7 @@
         </is>
       </c>
       <c r="G584">
-        <v>10.62378269131182</v>
+        <v>10.64867554114332</v>
       </c>
     </row>
     <row r="585">
@@ -19660,7 +19660,7 @@
         </is>
       </c>
       <c r="G585">
-        <v>26.44572977504299</v>
+        <v>25.75939243828449</v>
       </c>
     </row>
     <row r="586">
@@ -19693,7 +19693,7 @@
         </is>
       </c>
       <c r="G586">
-        <v>10.12114310518843</v>
+        <v>10.13842297504483</v>
       </c>
     </row>
     <row r="587">
@@ -19726,7 +19726,7 @@
         </is>
       </c>
       <c r="G587">
-        <v>29.01892306413349</v>
+        <v>28.47152711229374</v>
       </c>
     </row>
     <row r="588">
@@ -19759,7 +19759,7 @@
         </is>
       </c>
       <c r="G588">
-        <v>9.655134687487585</v>
+        <v>9.66652927249061</v>
       </c>
     </row>
     <row r="589">
@@ -19792,7 +19792,7 @@
         </is>
       </c>
       <c r="G589">
-        <v>31.72501738291064</v>
+        <v>31.33134310938874</v>
       </c>
     </row>
     <row r="590">
@@ -19825,7 +19825,7 @@
         </is>
       </c>
       <c r="G590">
-        <v>9.237855764807552</v>
+        <v>9.245614083741835</v>
       </c>
     </row>
     <row r="591">
@@ -19858,7 +19858,7 @@
         </is>
       </c>
       <c r="G591">
-        <v>34.70862830840605</v>
+        <v>34.44344725442415</v>
       </c>
     </row>
     <row r="592">
@@ -19891,7 +19891,7 @@
         </is>
       </c>
       <c r="G592">
-        <v>8.847267626914967</v>
+        <v>8.853331709531192</v>
       </c>
     </row>
     <row r="593">
@@ -19924,7 +19924,7 @@
         </is>
       </c>
       <c r="G593">
-        <v>37.86873890834722</v>
+        <v>37.69348820862896</v>
       </c>
     </row>
     <row r="594">
@@ -19957,7 +19957,7 @@
         </is>
       </c>
       <c r="G594">
-        <v>8.505553703186614</v>
+        <v>8.511299319092002</v>
       </c>
     </row>
     <row r="595">
@@ -19990,7 +19990,7 @@
         </is>
       </c>
       <c r="G595">
-        <v>41.37599734701016</v>
+        <v>41.25772472894341</v>
       </c>
     </row>
     <row r="596">
@@ -20023,7 +20023,7 @@
         </is>
       </c>
       <c r="G596">
-        <v>8.206666337630903</v>
+        <v>8.212987851824808</v>
       </c>
     </row>
     <row r="597">
@@ -20056,7 +20056,7 @@
         </is>
       </c>
       <c r="G597">
-        <v>44.87206722589833</v>
+        <v>44.79088898476692</v>
       </c>
     </row>
     <row r="598">
@@ -20089,7 +20089,7 @@
         </is>
       </c>
       <c r="G598">
-        <v>7.949509448639318</v>
+        <v>7.956904732968773</v>
       </c>
     </row>
     <row r="599">
@@ -20122,7 +20122,7 @@
         </is>
       </c>
       <c r="G599">
-        <v>48.2883177111107</v>
+        <v>48.23261837512648</v>
       </c>
     </row>
     <row r="600">
@@ -20155,7 +20155,7 @@
         </is>
       </c>
       <c r="G600">
-        <v>7.734496842313922</v>
+        <v>7.743138888216208</v>
       </c>
     </row>
     <row r="601">
@@ -20188,7 +20188,7 @@
         </is>
       </c>
       <c r="G601">
-        <v>51.55783213912353</v>
+        <v>51.51944371111156</v>
       </c>
     </row>
     <row r="602">
@@ -20254,7 +20254,7 @@
         </is>
       </c>
       <c r="G603">
-        <v>0.3266782400431036</v>
+        <v>0.3264375821806573</v>
       </c>
     </row>
     <row r="604">
@@ -20320,7 +20320,7 @@
         </is>
       </c>
       <c r="G605">
-        <v>0.4737550781643196</v>
+        <v>0.4676416481723078</v>
       </c>
     </row>
     <row r="606">
@@ -20386,7 +20386,7 @@
         </is>
       </c>
       <c r="G607">
-        <v>0.7050766326327981</v>
+        <v>0.6978575261484044</v>
       </c>
     </row>
     <row r="608">
@@ -20452,7 +20452,7 @@
         </is>
       </c>
       <c r="G609">
-        <v>0.9679828248639585</v>
+        <v>0.9588507115510964</v>
       </c>
     </row>
     <row r="610">
@@ -20518,7 +20518,7 @@
         </is>
       </c>
       <c r="G611">
-        <v>1.281272583447477</v>
+        <v>1.269664775089933</v>
       </c>
     </row>
     <row r="612">
@@ -20584,7 +20584,7 @@
         </is>
       </c>
       <c r="G613">
-        <v>1.647553186301527</v>
+        <v>1.632458224428927</v>
       </c>
     </row>
     <row r="614">
@@ -20650,7 +20650,7 @@
         </is>
       </c>
       <c r="G615">
-        <v>2.117792686943006</v>
+        <v>2.098108116787043</v>
       </c>
     </row>
     <row r="616">
@@ -20716,7 +20716,7 @@
         </is>
       </c>
       <c r="G617">
-        <v>2.551145493166899</v>
+        <v>2.525933337068802</v>
       </c>
     </row>
     <row r="618">
@@ -20782,7 +20782,7 @@
         </is>
       </c>
       <c r="G619">
-        <v>3.177726449741448</v>
+        <v>3.144008238033766</v>
       </c>
     </row>
     <row r="620">
@@ -20848,7 +20848,7 @@
         </is>
       </c>
       <c r="G621">
-        <v>3.950060511306395</v>
+        <v>3.904533344383338</v>
       </c>
     </row>
     <row r="622">
@@ -20881,7 +20881,7 @@
         </is>
       </c>
       <c r="G622">
-        <v>5.089561355806054</v>
+        <v>5.02567018404279</v>
       </c>
     </row>
     <row r="623">
@@ -20914,7 +20914,7 @@
         </is>
       </c>
       <c r="G623">
-        <v>5.089561355806054</v>
+        <v>5.02567018404279</v>
       </c>
     </row>
     <row r="624">
@@ -20947,7 +20947,7 @@
         </is>
       </c>
       <c r="G624">
-        <v>5.218323921265565</v>
+        <v>5.224522190378893</v>
       </c>
     </row>
     <row r="625">
@@ -20980,7 +20980,7 @@
         </is>
       </c>
       <c r="G625">
-        <v>6.517131097432545</v>
+        <v>6.425387627615025</v>
       </c>
     </row>
     <row r="626">
@@ -21013,7 +21013,7 @@
         </is>
       </c>
       <c r="G626">
-        <v>4.932281912442078</v>
+        <v>4.942323079325287</v>
       </c>
     </row>
     <row r="627">
@@ -21046,7 +21046,7 @@
         </is>
       </c>
       <c r="G627">
-        <v>8.1437538557515</v>
+        <v>8.026765074049564</v>
       </c>
     </row>
     <row r="628">
@@ -21079,7 +21079,7 @@
         </is>
       </c>
       <c r="G628">
-        <v>4.69874249407445</v>
+        <v>4.706237024740037</v>
       </c>
     </row>
     <row r="629">
@@ -21112,7 +21112,7 @@
         </is>
       </c>
       <c r="G629">
-        <v>10.55188479629232</v>
+        <v>10.20010279388132</v>
       </c>
     </row>
     <row r="630">
@@ -21145,7 +21145,7 @@
         </is>
       </c>
       <c r="G630">
-        <v>4.464194669058784</v>
+        <v>4.472073087894154</v>
       </c>
     </row>
     <row r="631">
@@ -21178,7 +21178,7 @@
         </is>
       </c>
       <c r="G631">
-        <v>12.44354397414312</v>
+        <v>12.04988794808799</v>
       </c>
     </row>
     <row r="632">
@@ -21211,7 +21211,7 @@
         </is>
       </c>
       <c r="G632">
-        <v>4.312613978038978</v>
+        <v>4.320055631762743</v>
       </c>
     </row>
     <row r="633">
@@ -21244,7 +21244,7 @@
         </is>
       </c>
       <c r="G633">
-        <v>14.58793961894159</v>
+        <v>14.18559571617904</v>
       </c>
     </row>
     <row r="634">
@@ -21277,7 +21277,7 @@
         </is>
       </c>
       <c r="G634">
-        <v>4.147778618696937</v>
+        <v>4.153982081035119</v>
       </c>
     </row>
     <row r="635">
@@ -21310,7 +21310,7 @@
         </is>
       </c>
       <c r="G635">
-        <v>16.68055587998272</v>
+        <v>16.31879240244259</v>
       </c>
     </row>
     <row r="636">
@@ -21343,7 +21343,7 @@
         </is>
       </c>
       <c r="G636">
-        <v>3.98217880782509</v>
+        <v>3.986856579568076</v>
       </c>
     </row>
     <row r="637">
@@ -21376,7 +21376,7 @@
         </is>
       </c>
       <c r="G637">
-        <v>18.92923934310248</v>
+        <v>18.64069523123329</v>
       </c>
     </row>
     <row r="638">
@@ -21409,7 +21409,7 @@
         </is>
       </c>
       <c r="G638">
-        <v>3.829882117356997</v>
+        <v>3.833263910256667</v>
       </c>
     </row>
     <row r="639">
@@ -21442,7 +21442,7 @@
         </is>
       </c>
       <c r="G639">
-        <v>21.42307540833528</v>
+        <v>21.21512629809423</v>
       </c>
     </row>
     <row r="640">
@@ -21475,7 +21475,7 @@
         </is>
       </c>
       <c r="G640">
-        <v>3.693912331955126</v>
+        <v>3.696429272636624</v>
       </c>
     </row>
     <row r="641">
@@ -21508,7 +21508,7 @@
         </is>
       </c>
       <c r="G641">
-        <v>24.2404505233078</v>
+        <v>24.09975040946069</v>
       </c>
     </row>
     <row r="642">
@@ -21541,7 +21541,7 @@
         </is>
       </c>
       <c r="G642">
-        <v>3.564114349401397</v>
+        <v>3.56623208584699</v>
       </c>
     </row>
     <row r="643">
@@ -21574,7 +21574,7 @@
         </is>
       </c>
       <c r="G643">
-        <v>27.3086792354496</v>
+        <v>27.21507766358426</v>
       </c>
     </row>
     <row r="644">
@@ -21607,7 +21607,7 @@
         </is>
       </c>
       <c r="G644">
-        <v>3.451638083511075</v>
+        <v>3.45373868816519</v>
       </c>
     </row>
     <row r="645">
@@ -21640,7 +21640,7 @@
         </is>
       </c>
       <c r="G645">
-        <v>30.77346272864444</v>
+        <v>30.70975398019001</v>
       </c>
     </row>
     <row r="646">
@@ -21673,7 +21673,7 @@
         </is>
       </c>
       <c r="G646">
-        <v>3.351891883006883</v>
+        <v>3.354250960603643</v>
       </c>
     </row>
     <row r="647">
@@ -21706,7 +21706,7 @@
         </is>
       </c>
       <c r="G647">
-        <v>34.37202858712014</v>
+        <v>34.32793808251957</v>
       </c>
     </row>
     <row r="648">
@@ -21739,7 +21739,7 @@
         </is>
       </c>
       <c r="G648">
-        <v>3.265446506877136</v>
+        <v>3.268222414771421</v>
       </c>
     </row>
     <row r="649">
@@ -21772,7 +21772,7 @@
         </is>
       </c>
       <c r="G649">
-        <v>38.03619382440959</v>
+        <v>38.00558825832622</v>
       </c>
     </row>
     <row r="650">
@@ -21805,7 +21805,7 @@
         </is>
       </c>
       <c r="G650">
-        <v>3.192293449667918</v>
+        <v>3.195537107222501</v>
       </c>
     </row>
     <row r="651">
@@ -21838,7 +21838,7 @@
         </is>
       </c>
       <c r="G651">
-        <v>41.6036377472896</v>
+        <v>41.58192149704127</v>
       </c>
     </row>
     <row r="652">
@@ -21904,7 +21904,7 @@
         </is>
       </c>
       <c r="G653">
-        <v>0.327749433109089</v>
+        <v>0.327507964601965</v>
       </c>
     </row>
     <row r="654">
@@ -21970,7 +21970,7 @@
         </is>
       </c>
       <c r="G655">
-        <v>0.477274325422213</v>
+        <v>0.4711149476096478</v>
       </c>
     </row>
     <row r="656">
@@ -22036,7 +22036,7 @@
         </is>
       </c>
       <c r="G657">
-        <v>0.7122860469593082</v>
+        <v>0.7049910903217469</v>
       </c>
     </row>
     <row r="658">
@@ -22102,7 +22102,7 @@
         </is>
       </c>
       <c r="G659">
-        <v>0.9798648714441077</v>
+        <v>0.9706163767752072</v>
       </c>
     </row>
     <row r="660">
@@ -22168,7 +22168,7 @@
         </is>
       </c>
       <c r="G661">
-        <v>1.299106297960721</v>
+        <v>1.287328920148375</v>
       </c>
     </row>
     <row r="662">
@@ -22234,7 +22234,7 @@
         </is>
       </c>
       <c r="G663">
-        <v>1.67212126296742</v>
+        <v>1.656786558526619</v>
       </c>
     </row>
     <row r="664">
@@ -22300,7 +22300,7 @@
         </is>
       </c>
       <c r="G665">
-        <v>2.152332043830701</v>
+        <v>2.132302588272915</v>
       </c>
     </row>
     <row r="666">
@@ -22366,7 +22366,7 @@
         </is>
       </c>
       <c r="G667">
-        <v>2.597837116821446</v>
+        <v>2.572124477433326</v>
       </c>
     </row>
     <row r="668">
@@ -22432,7 +22432,7 @@
         </is>
       </c>
       <c r="G669">
-        <v>3.240967361951049</v>
+        <v>3.206511549484838</v>
       </c>
     </row>
     <row r="670">
@@ -22498,7 +22498,7 @@
         </is>
       </c>
       <c r="G671">
-        <v>4.03342793592663</v>
+        <v>3.98682728101156</v>
       </c>
     </row>
     <row r="672">
@@ -22531,7 +22531,7 @@
         </is>
       </c>
       <c r="G672">
-        <v>5.200531471688967</v>
+        <v>5.135056270087005</v>
       </c>
     </row>
     <row r="673">
@@ -22564,7 +22564,7 @@
         </is>
       </c>
       <c r="G673">
-        <v>5.200531471688967</v>
+        <v>5.135056270087005</v>
       </c>
     </row>
     <row r="674">
@@ -22597,7 +22597,7 @@
         </is>
       </c>
       <c r="G674">
-        <v>5.308127113862587</v>
+        <v>5.313851537357758</v>
       </c>
     </row>
     <row r="675">
@@ -22630,7 +22630,7 @@
         </is>
       </c>
       <c r="G675">
-        <v>6.660813923560551</v>
+        <v>6.566758735254876</v>
       </c>
     </row>
     <row r="676">
@@ -22663,7 +22663,7 @@
         </is>
       </c>
       <c r="G676">
-        <v>5.011571901632912</v>
+        <v>5.02107278035733</v>
       </c>
     </row>
     <row r="677">
@@ -22696,7 +22696,7 @@
         </is>
       </c>
       <c r="G677">
-        <v>8.322726599965193</v>
+        <v>8.202693587217141</v>
       </c>
     </row>
     <row r="678">
@@ -22729,7 +22729,7 @@
         </is>
       </c>
       <c r="G678">
-        <v>4.767990768681672</v>
+        <v>4.77385882581943</v>
       </c>
     </row>
     <row r="679">
@@ -22762,7 +22762,7 @@
         </is>
       </c>
       <c r="G679">
-        <v>10.77914133744827</v>
+        <v>10.41833255750328</v>
       </c>
     </row>
     <row r="680">
@@ -22795,7 +22795,7 @@
         </is>
       </c>
       <c r="G680">
-        <v>4.523815063091353</v>
+        <v>4.529800976178029</v>
       </c>
     </row>
     <row r="681">
@@ -22828,7 +22828,7 @@
         </is>
       </c>
       <c r="G681">
-        <v>12.71812119875387</v>
+        <v>12.31370118108848</v>
       </c>
     </row>
     <row r="682">
@@ -22861,7 +22861,7 @@
         </is>
       </c>
       <c r="G682">
-        <v>4.352405221810782</v>
+        <v>4.357744888619835</v>
       </c>
     </row>
     <row r="683">
@@ -22894,7 +22894,7 @@
         </is>
       </c>
       <c r="G683">
-        <v>14.88869238551429</v>
+        <v>14.4752992094801</v>
       </c>
     </row>
     <row r="684">
@@ -22927,7 +22927,7 @@
         </is>
       </c>
       <c r="G684">
-        <v>4.164795477186288</v>
+        <v>4.168942439732448</v>
       </c>
     </row>
     <row r="685">
@@ -22960,7 +22960,7 @@
         </is>
       </c>
       <c r="G685">
-        <v>16.99497958077229</v>
+        <v>16.62323482334566</v>
       </c>
     </row>
     <row r="686">
@@ -22993,7 +22993,7 @@
         </is>
       </c>
       <c r="G686">
-        <v>3.975369672034759</v>
+        <v>3.978316739643479</v>
       </c>
     </row>
     <row r="687">
@@ -23026,7 +23026,7 @@
         </is>
       </c>
       <c r="G687">
-        <v>19.24862901886852</v>
+        <v>18.95210771294231</v>
       </c>
     </row>
     <row r="688">
@@ -23059,7 +23059,7 @@
         </is>
       </c>
       <c r="G688">
-        <v>3.800283948133555</v>
+        <v>3.802402008610526</v>
       </c>
     </row>
     <row r="689">
@@ -23092,7 +23092,7 @@
         </is>
       </c>
       <c r="G689">
-        <v>21.74152944608946</v>
+        <v>21.52785060171162</v>
       </c>
     </row>
     <row r="690">
@@ -23125,7 +23125,7 @@
         </is>
       </c>
       <c r="G690">
-        <v>3.644081223595924</v>
+        <v>3.645762518015846</v>
       </c>
     </row>
     <row r="691">
@@ -23158,7 +23158,7 @@
         </is>
       </c>
       <c r="G691">
-        <v>24.55523590999356</v>
+        <v>24.41069582999205</v>
       </c>
     </row>
     <row r="692">
@@ -23191,7 +23191,7 @@
         </is>
       </c>
       <c r="G692">
-        <v>3.496797378793112</v>
+        <v>3.498380175887261</v>
       </c>
     </row>
     <row r="693">
@@ -23224,7 +23224,7 @@
         </is>
       </c>
       <c r="G693">
-        <v>27.616260680403</v>
+        <v>27.52014295795949</v>
       </c>
     </row>
     <row r="694">
@@ -23257,7 +23257,7 @@
         </is>
       </c>
       <c r="G694">
-        <v>3.368610392834678</v>
+        <v>3.370355764750244</v>
       </c>
     </row>
     <row r="695">
@@ -23290,7 +23290,7 @@
         </is>
       </c>
       <c r="G695">
-        <v>31.06985202166565</v>
+        <v>31.00446439196638</v>
       </c>
     </row>
     <row r="696">
@@ -23323,7 +23323,7 @@
         </is>
       </c>
       <c r="G696">
-        <v>3.254930940455515</v>
+        <v>3.257033969346025</v>
       </c>
     </row>
     <row r="697">
@@ -23356,7 +23356,7 @@
         </is>
       </c>
       <c r="G697">
-        <v>34.65054257572541</v>
+        <v>34.60531114566987</v>
       </c>
     </row>
     <row r="698">
@@ -23389,7 +23389,7 @@
         </is>
       </c>
       <c r="G698">
-        <v>3.156091421867872</v>
+        <v>3.158663606651765</v>
       </c>
     </row>
     <row r="699">
@@ -23422,7 +23422,7 @@
         </is>
       </c>
       <c r="G699">
-        <v>38.29080008992099</v>
+        <v>38.25942156561601</v>
       </c>
     </row>
     <row r="700">
@@ -23455,7 +23455,7 @@
         </is>
       </c>
       <c r="G700">
-        <v>3.072208805663395</v>
+        <v>3.07527333749599</v>
       </c>
     </row>
     <row r="701">
@@ -23488,7 +23488,7 @@
         </is>
       </c>
       <c r="G701">
-        <v>41.82962960713979</v>
+        <v>41.80740299853766</v>
       </c>
     </row>
     <row r="702">
@@ -23554,7 +23554,7 @@
         </is>
       </c>
       <c r="G703">
-        <v>0.3648294655477402</v>
+        <v>0.3645431509830761</v>
       </c>
     </row>
     <row r="704">
@@ -23620,7 +23620,7 @@
         </is>
       </c>
       <c r="G705">
-        <v>0.5528824689641286</v>
+        <v>0.5458903907624296</v>
       </c>
     </row>
     <row r="706">
@@ -23686,7 +23686,7 @@
         </is>
       </c>
       <c r="G707">
-        <v>0.85457989169819</v>
+        <v>0.8458860854147439</v>
       </c>
     </row>
     <row r="708">
@@ -23752,7 +23752,7 @@
         </is>
       </c>
       <c r="G709">
-        <v>1.219867458582113</v>
+        <v>1.20830032719261</v>
       </c>
     </row>
     <row r="710">
@@ -23818,7 +23818,7 @@
         </is>
       </c>
       <c r="G711">
-        <v>1.676179421343994</v>
+        <v>1.660737349817923</v>
       </c>
     </row>
     <row r="712">
@@ -23884,7 +23884,7 @@
         </is>
       </c>
       <c r="G713">
-        <v>2.231216771435883</v>
+        <v>2.210158126593366</v>
       </c>
     </row>
     <row r="714">
@@ -23950,7 +23950,7 @@
         </is>
       </c>
       <c r="G715">
-        <v>2.973024503538114</v>
+        <v>2.944250007946625</v>
       </c>
     </row>
     <row r="716">
@@ -24016,7 +24016,7 @@
         </is>
       </c>
       <c r="G717">
-        <v>3.709582353872328</v>
+        <v>3.67088913237996</v>
       </c>
     </row>
     <row r="718">
@@ -24082,7 +24082,7 @@
         </is>
       </c>
       <c r="G719">
-        <v>4.768978448748397</v>
+        <v>4.714734076191863</v>
       </c>
     </row>
     <row r="720">
@@ -24148,7 +24148,7 @@
         </is>
       </c>
       <c r="G721">
-        <v>6.113719816931444</v>
+        <v>6.03702035645325</v>
       </c>
     </row>
     <row r="722">
@@ -24181,7 +24181,7 @@
         </is>
       </c>
       <c r="G722">
-        <v>7.881197834774792</v>
+        <v>7.772026754418067</v>
       </c>
     </row>
     <row r="723">
@@ -24214,7 +24214,7 @@
         </is>
       </c>
       <c r="G723">
-        <v>7.881197834774792</v>
+        <v>7.772026754418067</v>
       </c>
     </row>
     <row r="724">
@@ -24247,7 +24247,7 @@
         </is>
       </c>
       <c r="G724">
-        <v>10.10502717085204</v>
+        <v>9.946981560352857</v>
       </c>
     </row>
     <row r="725">
@@ -24280,7 +24280,7 @@
         </is>
       </c>
       <c r="G725">
-        <v>10.10502717085204</v>
+        <v>9.946981560352857</v>
       </c>
     </row>
     <row r="726">
@@ -24313,7 +24313,7 @@
         </is>
       </c>
       <c r="G726">
-        <v>11.42267933234186</v>
+        <v>11.44131192619684</v>
       </c>
     </row>
     <row r="727">
@@ -24346,7 +24346,7 @@
         </is>
       </c>
       <c r="G727">
-        <v>12.62422612834652</v>
+        <v>12.41928609843706</v>
       </c>
     </row>
     <row r="728">
@@ -24379,7 +24379,7 @@
         </is>
       </c>
       <c r="G728">
-        <v>11.07659451256047</v>
+        <v>11.10147443390585</v>
       </c>
     </row>
     <row r="729">
@@ -24412,7 +24412,7 @@
         </is>
       </c>
       <c r="G729">
-        <v>16.41194807119122</v>
+        <v>15.79196780427636</v>
       </c>
     </row>
     <row r="730">
@@ -24445,7 +24445,7 @@
         </is>
       </c>
       <c r="G730">
-        <v>10.63415029017034</v>
+        <v>10.6591975677272</v>
       </c>
     </row>
     <row r="731">
@@ -24478,7 +24478,7 @@
         </is>
       </c>
       <c r="G731">
-        <v>19.13751464286052</v>
+        <v>18.43468183262262</v>
       </c>
     </row>
     <row r="732">
@@ -24511,7 +24511,7 @@
         </is>
       </c>
       <c r="G732">
-        <v>10.26401571264743</v>
+        <v>10.28648045874101</v>
       </c>
     </row>
     <row r="733">
@@ -24544,7 +24544,7 @@
         </is>
       </c>
       <c r="G733">
-        <v>21.81449150260796</v>
+        <v>21.09513901727017</v>
       </c>
     </row>
     <row r="734">
@@ -24577,7 +24577,7 @@
         </is>
       </c>
       <c r="G734">
-        <v>9.824213648298031</v>
+        <v>9.841874293967825</v>
       </c>
     </row>
     <row r="735">
@@ -24610,7 +24610,7 @@
         </is>
       </c>
       <c r="G735">
-        <v>24.13301496826976</v>
+        <v>23.48570242323219</v>
       </c>
     </row>
     <row r="736">
@@ -24643,7 +24643,7 @@
         </is>
       </c>
       <c r="G736">
-        <v>9.370939501416901</v>
+        <v>9.383465345760623</v>
       </c>
     </row>
     <row r="737">
@@ -24676,7 +24676,7 @@
         </is>
       </c>
       <c r="G737">
-        <v>26.41141932538863</v>
+        <v>25.89527857000833</v>
       </c>
     </row>
     <row r="738">
@@ -24709,7 +24709,7 @@
         </is>
       </c>
       <c r="G738">
-        <v>8.955792380508914</v>
+        <v>8.964383090059695</v>
       </c>
     </row>
     <row r="739">
@@ -24742,7 +24742,7 @@
         </is>
       </c>
       <c r="G739">
-        <v>28.80806361677483</v>
+        <v>28.43700475215142</v>
       </c>
     </row>
     <row r="740">
@@ -24775,7 +24775,7 @@
         </is>
       </c>
       <c r="G740">
-        <v>8.586660704088109</v>
+        <v>8.592829629067769</v>
       </c>
     </row>
     <row r="741">
@@ -24808,7 +24808,7 @@
         </is>
       </c>
       <c r="G741">
-        <v>31.45629154815038</v>
+        <v>31.20646142516348</v>
       </c>
     </row>
     <row r="742">
@@ -24841,7 +24841,7 @@
         </is>
       </c>
       <c r="G742">
-        <v>8.2416237485237</v>
+        <v>8.246731093852175</v>
       </c>
     </row>
     <row r="743">
@@ -24874,7 +24874,7 @@
         </is>
       </c>
       <c r="G743">
-        <v>34.26454620124359</v>
+        <v>34.09952226285932</v>
       </c>
     </row>
     <row r="744">
@@ -24907,7 +24907,7 @@
         </is>
       </c>
       <c r="G744">
-        <v>7.941644024890068</v>
+        <v>7.946715092120275</v>
       </c>
     </row>
     <row r="745">
@@ -24940,7 +24940,7 @@
         </is>
       </c>
       <c r="G745">
-        <v>37.3874921720065</v>
+        <v>37.27616370951942</v>
       </c>
     </row>
     <row r="746">
@@ -24973,7 +24973,7 @@
         </is>
       </c>
       <c r="G746">
-        <v>7.679434323155017</v>
+        <v>7.685173840829488</v>
       </c>
     </row>
     <row r="747">
@@ -25006,7 +25006,7 @@
         </is>
       </c>
       <c r="G747">
-        <v>40.49516881514666</v>
+        <v>40.41875885958666</v>
       </c>
     </row>
     <row r="748">
@@ -25039,7 +25039,7 @@
         </is>
       </c>
       <c r="G748">
-        <v>7.453216452703105</v>
+        <v>7.460028017034853</v>
       </c>
     </row>
     <row r="749">
@@ -25072,7 +25072,7 @@
         </is>
       </c>
       <c r="G749">
-        <v>43.51978264991087</v>
+        <v>43.46734595352364</v>
       </c>
     </row>
     <row r="750">
@@ -25105,7 +25105,7 @@
         </is>
       </c>
       <c r="G750">
-        <v>7.263336964614192</v>
+        <v>7.271349961985369</v>
       </c>
     </row>
     <row r="751">
@@ -25138,7 +25138,7 @@
         </is>
       </c>
       <c r="G751">
-        <v>46.40063620698364</v>
+        <v>46.36451493608293</v>
       </c>
     </row>
     <row r="752">
@@ -25204,7 +25204,7 @@
         </is>
       </c>
       <c r="G753">
-        <v>0.3660202468519353</v>
+        <v>0.3657329733637678</v>
       </c>
     </row>
     <row r="754">
@@ -25270,7 +25270,7 @@
         </is>
       </c>
       <c r="G755">
-        <v>0.5569635858182473</v>
+        <v>0.5499192934968797</v>
       </c>
     </row>
     <row r="756">
@@ -25336,7 +25336,7 @@
         </is>
       </c>
       <c r="G757">
-        <v>0.863259557185306</v>
+        <v>0.8544751448352865</v>
       </c>
     </row>
     <row r="758">
@@ -25402,7 +25402,7 @@
         </is>
       </c>
       <c r="G759">
-        <v>1.234738118775065</v>
+        <v>1.223024966114898</v>
       </c>
     </row>
     <row r="760">
@@ -25468,7 +25468,7 @@
         </is>
       </c>
       <c r="G761">
-        <v>1.699343699638027</v>
+        <v>1.683678566474893</v>
       </c>
     </row>
     <row r="762">
@@ -25534,7 +25534,7 @@
         </is>
       </c>
       <c r="G763">
-        <v>2.264225661215784</v>
+        <v>2.242837216362634</v>
       </c>
     </row>
     <row r="764">
@@ -25600,7 +25600,7 @@
         </is>
       </c>
       <c r="G765">
-        <v>3.021116281011842</v>
+        <v>2.991845364991507</v>
       </c>
     </row>
     <row r="766">
@@ -25666,7 +25666,7 @@
         </is>
       </c>
       <c r="G767">
-        <v>3.777027620991242</v>
+        <v>3.737578313253703</v>
       </c>
     </row>
     <row r="768">
@@ -25732,7 +25732,7 @@
         </is>
       </c>
       <c r="G769">
-        <v>4.863367954980139</v>
+        <v>4.807956531836126</v>
       </c>
     </row>
     <row r="770">
@@ -25798,7 +25798,7 @@
         </is>
       </c>
       <c r="G771">
-        <v>6.242164971378641</v>
+        <v>6.163688834866161</v>
       </c>
     </row>
     <row r="772">
@@ -25831,7 +25831,7 @@
         </is>
       </c>
       <c r="G772">
-        <v>8.052745358955729</v>
+        <v>7.940914312825475</v>
       </c>
     </row>
     <row r="773">
@@ -25864,7 +25864,7 @@
         </is>
       </c>
       <c r="G773">
-        <v>8.052745358955729</v>
+        <v>7.940914312825475</v>
       </c>
     </row>
     <row r="774">
@@ -25897,7 +25897,7 @@
         </is>
       </c>
       <c r="G774">
-        <v>10.32822829319831</v>
+        <v>10.16626027988851</v>
       </c>
     </row>
     <row r="775">
@@ -25930,7 +25930,7 @@
         </is>
       </c>
       <c r="G775">
-        <v>10.32822829319831</v>
+        <v>10.16626027988851</v>
       </c>
     </row>
     <row r="776">
@@ -25963,7 +25963,7 @@
         </is>
       </c>
       <c r="G776">
-        <v>11.61842164571339</v>
+        <v>11.63576030162667</v>
       </c>
     </row>
     <row r="777">
@@ -25996,7 +25996,7 @@
         </is>
       </c>
       <c r="G777">
-        <v>12.90333847153985</v>
+        <v>12.69314461409191</v>
       </c>
     </row>
     <row r="778">
@@ -26029,7 +26029,7 @@
         </is>
       </c>
       <c r="G778">
-        <v>11.25441568540099</v>
+        <v>11.27569558070753</v>
       </c>
     </row>
     <row r="779">
@@ -26062,7 +26062,7 @@
         </is>
       </c>
       <c r="G779">
-        <v>16.76909640018523</v>
+        <v>16.13345345902711</v>
       </c>
     </row>
     <row r="780">
@@ -26095,7 +26095,7 @@
         </is>
       </c>
       <c r="G780">
-        <v>10.79261527869924</v>
+        <v>10.81319846704967</v>
       </c>
     </row>
     <row r="781">
@@ -26128,7 +26128,7 @@
         </is>
       </c>
       <c r="G781">
-        <v>19.56547728332855</v>
+        <v>18.84373347576339</v>
       </c>
     </row>
     <row r="782">
@@ -26161,7 +26161,7 @@
         </is>
       </c>
       <c r="G782">
-        <v>10.37654509440861</v>
+        <v>10.3937217207264</v>
       </c>
     </row>
     <row r="783">
@@ -26194,7 +26194,7 @@
         </is>
       </c>
       <c r="G783">
-        <v>22.27225785544881</v>
+        <v>21.53347647688959</v>
       </c>
     </row>
     <row r="784">
@@ -26227,7 +26227,7 @@
         </is>
       </c>
       <c r="G784">
-        <v>9.882674260730063</v>
+        <v>9.894850440145488</v>
       </c>
     </row>
     <row r="785">
@@ -26260,7 +26260,7 @@
         </is>
       </c>
       <c r="G785">
-        <v>24.59786046075974</v>
+        <v>23.93298369626843</v>
       </c>
     </row>
     <row r="786">
@@ -26293,7 +26293,7 @@
         </is>
       </c>
       <c r="G786">
-        <v>9.37224893793884</v>
+        <v>9.379913668039517</v>
       </c>
     </row>
     <row r="787">
@@ -26326,7 +26326,7 @@
         </is>
       </c>
       <c r="G787">
-        <v>26.86794262339012</v>
+        <v>26.33775869816953</v>
       </c>
     </row>
     <row r="788">
@@ -26359,7 +26359,7 @@
         </is>
       </c>
       <c r="G788">
-        <v>8.902444978902686</v>
+        <v>8.907319664382758</v>
       </c>
     </row>
     <row r="789">
@@ -26392,7 +26392,7 @@
         </is>
       </c>
       <c r="G789">
-        <v>29.24721570627817</v>
+        <v>28.86606833667539</v>
       </c>
     </row>
     <row r="790">
@@ -26425,7 +26425,7 @@
         </is>
       </c>
       <c r="G790">
-        <v>8.485252380215799</v>
+        <v>8.488867606126856</v>
       </c>
     </row>
     <row r="791">
@@ -26458,7 +26458,7 @@
         </is>
       </c>
       <c r="G791">
-        <v>31.87541786560274</v>
+        <v>31.61882490358279</v>
       </c>
     </row>
     <row r="792">
@@ -26491,7 +26491,7 @@
         </is>
       </c>
       <c r="G792">
-        <v>8.099402352905063</v>
+        <v>8.102823860726598</v>
       </c>
     </row>
     <row r="793">
@@ -26524,7 +26524,7 @@
         </is>
       </c>
       <c r="G793">
-        <v>34.66116556717549</v>
+        <v>34.49170499658455</v>
       </c>
     </row>
     <row r="794">
@@ -26557,7 +26557,7 @@
         </is>
       </c>
       <c r="G794">
-        <v>7.763559582938126</v>
+        <v>7.767488785306555</v>
       </c>
     </row>
     <row r="795">
@@ -26590,7 +26590,7 @@
         </is>
       </c>
       <c r="G795">
-        <v>37.75891003015704</v>
+        <v>37.64461226509167</v>
       </c>
     </row>
     <row r="796">
@@ -26623,7 +26623,7 @@
         </is>
       </c>
       <c r="G796">
-        <v>7.470026208069627</v>
+        <v>7.474941524408266</v>
       </c>
     </row>
     <row r="797">
@@ -26656,7 +26656,7 @@
         </is>
       </c>
       <c r="G797">
-        <v>40.83558125638596</v>
+        <v>40.75714045621523</v>
       </c>
     </row>
     <row r="798">
@@ -26689,7 +26689,7 @@
         </is>
       </c>
       <c r="G798">
-        <v>7.216250682224834</v>
+        <v>7.222421416659078</v>
       </c>
     </row>
     <row r="799">
@@ -26722,7 +26722,7 @@
         </is>
       </c>
       <c r="G799">
-        <v>43.82444556290292</v>
+        <v>43.77061689314131</v>
       </c>
     </row>
     <row r="800">
@@ -26755,7 +26755,7 @@
         </is>
       </c>
       <c r="G800">
-        <v>7.002316025147608</v>
+        <v>7.009791069092973</v>
       </c>
     </row>
     <row r="801">
@@ -26788,7 +26788,7 @@
         </is>
       </c>
       <c r="G801">
-        <v>46.66627801689442</v>
+        <v>46.62922128694105</v>
       </c>
     </row>
     <row r="802">
@@ -26854,7 +26854,7 @@
         </is>
       </c>
       <c r="G803">
-        <v>0.5703608693233001</v>
+        <v>0.5694714034249472</v>
       </c>
     </row>
     <row r="804">
@@ -26920,7 +26920,7 @@
         </is>
       </c>
       <c r="G805">
-        <v>0.6656696714976819</v>
+        <v>0.658646951834774</v>
       </c>
     </row>
     <row r="806">
@@ -26986,7 +26986,7 @@
         </is>
       </c>
       <c r="G807">
-        <v>0.9508779576034019</v>
+        <v>0.9427682632159262</v>
       </c>
     </row>
     <row r="808">
@@ -27052,7 +27052,7 @@
         </is>
       </c>
       <c r="G809">
-        <v>1.119020687600724</v>
+        <v>1.109507953766206</v>
       </c>
     </row>
     <row r="810">
@@ -27118,7 +27118,7 @@
         </is>
       </c>
       <c r="G811">
-        <v>1.387068758389044</v>
+        <v>1.374752029832324</v>
       </c>
     </row>
     <row r="812">
@@ -27184,7 +27184,7 @@
         </is>
       </c>
       <c r="G813">
-        <v>1.726870298973492</v>
+        <v>1.710432264250312</v>
       </c>
     </row>
     <row r="814">
@@ -27250,7 +27250,7 @@
         </is>
       </c>
       <c r="G815">
-        <v>2.055290757815838</v>
+        <v>2.03359551479599</v>
       </c>
     </row>
     <row r="816">
@@ -27316,7 +27316,7 @@
         </is>
       </c>
       <c r="G817">
-        <v>2.314691805577342</v>
+        <v>2.287252788758761</v>
       </c>
     </row>
     <row r="818">
@@ -27382,7 +27382,7 @@
         </is>
       </c>
       <c r="G819">
-        <v>2.761508002646158</v>
+        <v>2.727161938021399</v>
       </c>
     </row>
     <row r="820">
@@ -27448,7 +27448,7 @@
         </is>
       </c>
       <c r="G821">
-        <v>3.421088536020937</v>
+        <v>3.374485677857863</v>
       </c>
     </row>
     <row r="822">
@@ -27481,7 +27481,7 @@
         </is>
       </c>
       <c r="G822">
-        <v>4.461871678252254</v>
+        <v>4.393245496081137</v>
       </c>
     </row>
     <row r="823">
@@ -27514,7 +27514,7 @@
         </is>
       </c>
       <c r="G823">
-        <v>4.461871678252254</v>
+        <v>4.393245496081137</v>
       </c>
     </row>
     <row r="824">
@@ -27547,7 +27547,7 @@
         </is>
       </c>
       <c r="G824">
-        <v>4.731342968694988</v>
+        <v>4.724748506507632</v>
       </c>
     </row>
     <row r="825">
@@ -27580,7 +27580,7 @@
         </is>
       </c>
       <c r="G825">
-        <v>5.90805143028917</v>
+        <v>5.809914358005648</v>
       </c>
     </row>
     <row r="826">
@@ -27613,7 +27613,7 @@
         </is>
       </c>
       <c r="G826">
-        <v>4.580181457698951</v>
+        <v>4.579156308575969</v>
       </c>
     </row>
     <row r="827">
@@ -27646,7 +27646,7 @@
         </is>
       </c>
       <c r="G827">
-        <v>7.560135350193645</v>
+        <v>7.434776202690989</v>
       </c>
     </row>
     <row r="828">
@@ -27679,7 +27679,7 @@
         </is>
       </c>
       <c r="G828">
-        <v>4.504471563927308</v>
+        <v>4.494092467248828</v>
       </c>
     </row>
     <row r="829">
@@ -27712,7 +27712,7 @@
         </is>
       </c>
       <c r="G829">
-        <v>10.11140387390569</v>
+        <v>9.736347700201387</v>
       </c>
     </row>
     <row r="830">
@@ -27745,7 +27745,7 @@
         </is>
       </c>
       <c r="G830">
-        <v>4.374171537670446</v>
+        <v>4.369740922322678</v>
       </c>
     </row>
     <row r="831">
@@ -27778,7 +27778,7 @@
         </is>
       </c>
       <c r="G831">
-        <v>12.18676322128931</v>
+        <v>11.76859065819083</v>
       </c>
     </row>
     <row r="832">
@@ -27811,7 +27811,7 @@
         </is>
       </c>
       <c r="G832">
-        <v>4.340006965677755</v>
+        <v>4.340886774891696</v>
       </c>
     </row>
     <row r="833">
@@ -27844,7 +27844,7 @@
         </is>
       </c>
       <c r="G833">
-        <v>14.67296671698746</v>
+        <v>14.24666082471968</v>
       </c>
     </row>
     <row r="834">
@@ -27877,7 +27877,7 @@
         </is>
       </c>
       <c r="G834">
-        <v>4.289458909123144</v>
+        <v>4.293824292082127</v>
       </c>
     </row>
     <row r="835">
@@ -27910,7 +27910,7 @@
         </is>
       </c>
       <c r="G835">
-        <v>17.24103297296988</v>
+        <v>16.85912844493954</v>
       </c>
     </row>
     <row r="836">
@@ -27943,7 +27943,7 @@
         </is>
       </c>
       <c r="G836">
-        <v>4.252256254188438</v>
+        <v>4.258163117853477</v>
       </c>
     </row>
     <row r="837">
@@ -27976,7 +27976,7 @@
         </is>
       </c>
       <c r="G837">
-        <v>20.20194574453886</v>
+        <v>19.89831479130038</v>
       </c>
     </row>
     <row r="838">
@@ -28009,7 +28009,7 @@
         </is>
       </c>
       <c r="G838">
-        <v>4.206071034539235</v>
+        <v>4.211530273677495</v>
       </c>
     </row>
     <row r="839">
@@ -28042,7 +28042,7 @@
         </is>
       </c>
       <c r="G839">
-        <v>23.51428035441188</v>
+        <v>23.29572612582088</v>
       </c>
     </row>
     <row r="840">
@@ -28075,7 +28075,7 @@
         </is>
       </c>
       <c r="G840">
-        <v>4.147170672765159</v>
+        <v>4.151503777016604</v>
       </c>
     </row>
     <row r="841">
@@ -28108,7 +28108,7 @@
         </is>
       </c>
       <c r="G841">
-        <v>27.19957073465268</v>
+        <v>27.05154514662044</v>
       </c>
     </row>
     <row r="842">
@@ -28141,7 +28141,7 @@
         </is>
       </c>
       <c r="G842">
-        <v>4.068418116113106</v>
+        <v>4.071885024521499</v>
       </c>
     </row>
     <row r="843">
@@ -28174,7 +28174,7 @@
         </is>
       </c>
       <c r="G843">
-        <v>31.15502173367867</v>
+        <v>31.05626134362443</v>
       </c>
     </row>
     <row r="844">
@@ -28207,7 +28207,7 @@
         </is>
       </c>
       <c r="G844">
-        <v>3.990193949475658</v>
+        <v>3.993308653446623</v>
       </c>
     </row>
     <row r="845">
@@ -28240,7 +28240,7 @@
         </is>
       </c>
       <c r="G845">
-        <v>35.55572706679992</v>
+        <v>35.48823146217516</v>
       </c>
     </row>
     <row r="846">
@@ -28273,7 +28273,7 @@
         </is>
       </c>
       <c r="G846">
-        <v>3.911465945320838</v>
+        <v>3.914662949502028</v>
       </c>
     </row>
     <row r="847">
@@ -28306,7 +28306,7 @@
         </is>
       </c>
       <c r="G847">
-        <v>40.08818576223657</v>
+        <v>40.04131706760658</v>
       </c>
     </row>
     <row r="848">
@@ -28339,7 +28339,7 @@
         </is>
       </c>
       <c r="G848">
-        <v>3.836769583856737</v>
+        <v>3.840313646274449</v>
       </c>
     </row>
     <row r="849">
@@ -28372,7 +28372,7 @@
         </is>
       </c>
       <c r="G849">
-        <v>44.66749076080276</v>
+        <v>44.63484303667589</v>
       </c>
     </row>
     <row r="850">
@@ -28405,7 +28405,7 @@
         </is>
       </c>
       <c r="G850">
-        <v>3.770414394348197</v>
+        <v>3.774412543072853</v>
       </c>
     </row>
     <row r="851">
@@ -28438,7 +28438,7 @@
         </is>
       </c>
       <c r="G851">
-        <v>49.11186269183869</v>
+        <v>49.08841096220874</v>
       </c>
     </row>
     <row r="852">
@@ -28504,7 +28504,7 @@
         </is>
       </c>
       <c r="G853">
-        <v>0.5916150958759666</v>
+        <v>0.5906923543487028</v>
       </c>
     </row>
     <row r="854">
@@ -28570,7 +28570,7 @@
         </is>
       </c>
       <c r="G855">
-        <v>0.7231722830006543</v>
+        <v>0.7155366321687654</v>
       </c>
     </row>
     <row r="856">
@@ -28636,7 +28636,7 @@
         </is>
       </c>
       <c r="G857">
-        <v>1.068169719969611</v>
+        <v>1.059036926692418</v>
       </c>
     </row>
     <row r="858">
@@ -28702,7 +28702,7 @@
         </is>
       </c>
       <c r="G859">
-        <v>1.295473075495233</v>
+        <v>1.284411939690919</v>
       </c>
     </row>
     <row r="860">
@@ -28768,7 +28768,7 @@
         </is>
       </c>
       <c r="G861">
-        <v>1.645856182266099</v>
+        <v>1.631140944903938</v>
       </c>
     </row>
     <row r="862">
@@ -28834,7 +28834,7 @@
         </is>
       </c>
       <c r="G863">
-        <v>2.087246225105328</v>
+        <v>2.06717149321894</v>
       </c>
     </row>
     <row r="864">
@@ -28900,7 +28900,7 @@
         </is>
       </c>
       <c r="G865">
-        <v>2.535713995443018</v>
+        <v>2.50857789775934</v>
       </c>
     </row>
     <row r="866">
@@ -28966,7 +28966,7 @@
         </is>
       </c>
       <c r="G867">
-        <v>2.927210586376981</v>
+        <v>2.891861419042022</v>
       </c>
     </row>
     <row r="868">
@@ -29032,7 +29032,7 @@
         </is>
       </c>
       <c r="G869">
-        <v>3.571701717305721</v>
+        <v>3.526173087706316</v>
       </c>
     </row>
     <row r="870">
@@ -29098,7 +29098,7 @@
         </is>
       </c>
       <c r="G871">
-        <v>4.517630715373263</v>
+        <v>4.454173115818838</v>
       </c>
     </row>
     <row r="872">
@@ -29131,7 +29131,7 @@
         </is>
       </c>
       <c r="G872">
-        <v>5.988326576395144</v>
+        <v>5.892798681876573</v>
       </c>
     </row>
     <row r="873">
@@ -29164,7 +29164,7 @@
         </is>
       </c>
       <c r="G873">
-        <v>5.988326576395144</v>
+        <v>5.892798681876573</v>
       </c>
     </row>
     <row r="874">
@@ -29197,7 +29197,7 @@
         </is>
       </c>
       <c r="G874">
-        <v>6.404373256971073</v>
+        <v>6.390643151232648</v>
       </c>
     </row>
     <row r="875">
@@ -29230,7 +29230,7 @@
         </is>
       </c>
       <c r="G875">
-        <v>8.035112750601128</v>
+        <v>7.896225578050083</v>
       </c>
     </row>
     <row r="876">
@@ -29263,7 +29263,7 @@
         </is>
       </c>
       <c r="G876">
-        <v>6.264367043174126</v>
+        <v>6.257146747911581</v>
       </c>
     </row>
     <row r="877">
@@ -29296,7 +29296,7 @@
         </is>
       </c>
       <c r="G877">
-        <v>10.39989136525616</v>
+        <v>10.21878188442399</v>
       </c>
     </row>
     <row r="878">
@@ -29329,7 +29329,7 @@
         </is>
       </c>
       <c r="G878">
-        <v>6.21907275423948</v>
+        <v>6.190380451821791</v>
       </c>
     </row>
     <row r="879">
@@ -29362,7 +29362,7 @@
         </is>
       </c>
       <c r="G879">
-        <v>14.05330101427607</v>
+        <v>13.5037291796474</v>
       </c>
     </row>
     <row r="880">
@@ -29395,7 +29395,7 @@
         </is>
       </c>
       <c r="G880">
-        <v>6.114555403918723</v>
+        <v>6.091653320640718</v>
       </c>
     </row>
     <row r="881">
@@ -29428,7 +29428,7 @@
         </is>
       </c>
       <c r="G881">
-        <v>17.18115673644985</v>
+        <v>16.55070684461684</v>
       </c>
     </row>
     <row r="882">
@@ -29461,7 +29461,7 @@
         </is>
       </c>
       <c r="G882">
-        <v>5.942222836011644</v>
+        <v>5.92556325661934</v>
       </c>
     </row>
     <row r="883">
@@ -29494,7 +29494,7 @@
         </is>
       </c>
       <c r="G883">
-        <v>20.31509354176909</v>
+        <v>19.67159254315228</v>
       </c>
     </row>
     <row r="884">
@@ -29527,7 +29527,7 @@
         </is>
       </c>
       <c r="G884">
-        <v>5.725496667085848</v>
+        <v>5.714529520158093</v>
       </c>
     </row>
     <row r="885">
@@ -29560,7 +29560,7 @@
         </is>
       </c>
       <c r="G885">
-        <v>23.34873472818676</v>
+        <v>22.77163021593276</v>
       </c>
     </row>
     <row r="886">
@@ -29593,7 +29593,7 @@
         </is>
       </c>
       <c r="G886">
-        <v>5.51529624261449</v>
+        <v>5.509323063757325</v>
       </c>
     </row>
     <row r="887">
@@ -29626,7 +29626,7 @@
         </is>
       </c>
       <c r="G887">
-        <v>26.68682947008944</v>
+        <v>26.227846291536</v>
       </c>
     </row>
     <row r="888">
@@ -29659,7 +29659,7 @@
         </is>
       </c>
       <c r="G888">
-        <v>5.297912056899124</v>
+        <v>5.295176014949456</v>
       </c>
     </row>
     <row r="889">
@@ -29692,7 +29692,7 @@
         </is>
       </c>
       <c r="G889">
-        <v>30.28783441879583</v>
+        <v>29.95798691184903</v>
       </c>
     </row>
     <row r="890">
@@ -29725,7 +29725,7 @@
         </is>
       </c>
       <c r="G890">
-        <v>5.07974828599767</v>
+        <v>5.078923401930465</v>
       </c>
     </row>
     <row r="891">
@@ -29758,7 +29758,7 @@
         </is>
       </c>
       <c r="G891">
-        <v>34.20354408556591</v>
+        <v>33.98101501228963</v>
       </c>
     </row>
     <row r="892">
@@ -29791,7 +29791,7 @@
         </is>
       </c>
       <c r="G892">
-        <v>4.85335537675451</v>
+        <v>4.853740413351755</v>
       </c>
     </row>
     <row r="893">
@@ -29824,7 +29824,7 @@
         </is>
       </c>
       <c r="G893">
-        <v>38.29947062617033</v>
+        <v>38.15192977419795</v>
       </c>
     </row>
     <row r="894">
@@ -29857,7 +29857,7 @@
         </is>
       </c>
       <c r="G894">
-        <v>4.639176977205588</v>
+        <v>4.64049156889147</v>
       </c>
     </row>
     <row r="895">
@@ -29890,7 +29890,7 @@
         </is>
       </c>
       <c r="G895">
-        <v>42.75496457771523</v>
+        <v>42.65497499117023</v>
       </c>
     </row>
     <row r="896">
@@ -29923,7 +29923,7 @@
         </is>
       </c>
       <c r="G896">
-        <v>4.435420160932137</v>
+        <v>4.437603965691483</v>
       </c>
     </row>
     <row r="897">
@@ -29956,7 +29956,7 @@
         </is>
       </c>
       <c r="G897">
-        <v>47.17842207291496</v>
+        <v>47.1096006987087</v>
       </c>
     </row>
     <row r="898">
@@ -29989,7 +29989,7 @@
         </is>
       </c>
       <c r="G898">
-        <v>4.246268069535186</v>
+        <v>4.249303399428875</v>
       </c>
     </row>
     <row r="899">
@@ -30022,7 +30022,7 @@
         </is>
       </c>
       <c r="G899">
-        <v>51.47458186432148</v>
+        <v>51.42725869479746</v>
       </c>
     </row>
     <row r="900">
@@ -30055,7 +30055,7 @@
         </is>
       </c>
       <c r="G900">
-        <v>4.077510646381013</v>
+        <v>4.081319168776033</v>
       </c>
     </row>
     <row r="901">
@@ -30088,7 +30088,7 @@
         </is>
       </c>
       <c r="G901">
-        <v>55.46930398172532</v>
+        <v>55.43632696380546</v>
       </c>
     </row>
     <row r="902">
@@ -30154,7 +30154,7 @@
         </is>
       </c>
       <c r="G903">
-        <v>0.6388568151638385</v>
+        <v>0.6377986119188879</v>
       </c>
     </row>
     <row r="904">
@@ -30220,7 +30220,7 @@
         </is>
       </c>
       <c r="G905">
-        <v>0.7841187228387703</v>
+        <v>0.7760713108404202</v>
       </c>
     </row>
     <row r="906">
@@ -30286,7 +30286,7 @@
         </is>
       </c>
       <c r="G907">
-        <v>1.17411489965137</v>
+        <v>1.164320653037545</v>
       </c>
     </row>
     <row r="908">
@@ -30352,7 +30352,7 @@
         </is>
       </c>
       <c r="G909">
-        <v>1.446108910560339</v>
+        <v>1.434015315511224</v>
       </c>
     </row>
     <row r="910">
@@ -30418,7 +30418,7 @@
         </is>
       </c>
       <c r="G911">
-        <v>1.870883241495057</v>
+        <v>1.854421107688058</v>
       </c>
     </row>
     <row r="912">
@@ -30484,7 +30484,7 @@
         </is>
       </c>
       <c r="G913">
-        <v>2.424452534381555</v>
+        <v>2.401380205530547</v>
       </c>
     </row>
     <row r="914">
@@ -30550,7 +30550,7 @@
         </is>
       </c>
       <c r="G915">
-        <v>2.997287386372906</v>
+        <v>2.965355683680624</v>
       </c>
     </row>
     <row r="916">
@@ -30616,7 +30616,7 @@
         </is>
       </c>
       <c r="G917">
-        <v>3.498580359338521</v>
+        <v>3.456211453860596</v>
       </c>
     </row>
     <row r="918">
@@ -30682,7 +30682,7 @@
         </is>
       </c>
       <c r="G919">
-        <v>4.311567240895448</v>
+        <v>4.256124099274597</v>
       </c>
     </row>
     <row r="920">
@@ -30748,7 +30748,7 @@
         </is>
       </c>
       <c r="G921">
-        <v>5.519093073345463</v>
+        <v>5.440352803102569</v>
       </c>
     </row>
     <row r="922">
@@ -30781,7 +30781,7 @@
         </is>
       </c>
       <c r="G922">
-        <v>7.202995838777872</v>
+        <v>7.08542852899884</v>
       </c>
     </row>
     <row r="923">
@@ -30814,7 +30814,7 @@
         </is>
       </c>
       <c r="G923">
-        <v>7.202995838777872</v>
+        <v>7.08542852899884</v>
       </c>
     </row>
     <row r="924">
@@ -30847,7 +30847,7 @@
         </is>
       </c>
       <c r="G924">
-        <v>9.557144020038349</v>
+        <v>9.387489130130675</v>
       </c>
     </row>
     <row r="925">
@@ -30880,7 +30880,7 @@
         </is>
       </c>
       <c r="G925">
-        <v>9.557144020038349</v>
+        <v>9.387489130130675</v>
       </c>
     </row>
     <row r="926">
@@ -30913,7 +30913,7 @@
         </is>
       </c>
       <c r="G926">
-        <v>11.05388487038097</v>
+        <v>11.05224751248501</v>
       </c>
     </row>
     <row r="927">
@@ -30946,7 +30946,7 @@
         </is>
       </c>
       <c r="G927">
-        <v>12.21618196856569</v>
+        <v>11.99659320116751</v>
       </c>
     </row>
     <row r="928">
@@ -30979,7 +30979,7 @@
         </is>
       </c>
       <c r="G928">
-        <v>11.02660996899664</v>
+        <v>11.01824010305678</v>
       </c>
     </row>
     <row r="929">
@@ -31012,7 +31012,7 @@
         </is>
       </c>
       <c r="G929">
-        <v>16.33582930260734</v>
+        <v>15.67175672059481</v>
       </c>
     </row>
     <row r="930">
@@ -31045,7 +31045,7 @@
         </is>
       </c>
       <c r="G930">
-        <v>10.79064330900814</v>
+        <v>10.79463352842793</v>
       </c>
     </row>
     <row r="931">
@@ -31078,7 +31078,7 @@
         </is>
       </c>
       <c r="G931">
-        <v>19.4157607247226</v>
+        <v>18.66582126162391</v>
       </c>
     </row>
     <row r="932">
@@ -31111,7 +31111,7 @@
         </is>
       </c>
       <c r="G932">
-        <v>10.6608444447629</v>
+        <v>10.67497577270605</v>
       </c>
     </row>
     <row r="933">
@@ -31144,7 +31144,7 @@
         </is>
       </c>
       <c r="G933">
-        <v>22.65318355978227</v>
+        <v>21.8874552823984</v>
       </c>
     </row>
     <row r="934">
@@ -31177,7 +31177,7 @@
         </is>
       </c>
       <c r="G934">
-        <v>10.44547502766843</v>
+        <v>10.46480504338188</v>
       </c>
     </row>
     <row r="935">
@@ -31210,7 +31210,7 @@
         </is>
       </c>
       <c r="G935">
-        <v>25.65321941835996</v>
+        <v>24.96657425031164</v>
       </c>
     </row>
     <row r="936">
@@ -31243,7 +31243,7 @@
         </is>
       </c>
       <c r="G936">
-        <v>10.24741687576185</v>
+        <v>10.26776201427168</v>
       </c>
     </row>
     <row r="937">
@@ -31276,7 +31276,7 @@
         </is>
       </c>
       <c r="G937">
-        <v>28.8745051608752</v>
+        <v>28.3286692822114</v>
       </c>
     </row>
     <row r="938">
@@ -31309,7 +31309,7 @@
         </is>
       </c>
       <c r="G938">
-        <v>10.03614939497385</v>
+        <v>10.05331050171525</v>
       </c>
     </row>
     <row r="939">
@@ -31342,7 +31342,7 @@
         </is>
       </c>
       <c r="G939">
-        <v>32.27465869689792</v>
+        <v>31.88291320424101</v>
       </c>
     </row>
     <row r="940">
@@ -31375,7 +31375,7 @@
         </is>
       </c>
       <c r="G940">
-        <v>9.804083986978577</v>
+        <v>9.817039373116616</v>
       </c>
     </row>
     <row r="941">
@@ -31408,7 +31408,7 @@
         </is>
       </c>
       <c r="G941">
-        <v>35.90608020281088</v>
+        <v>35.64242165143622</v>
       </c>
     </row>
     <row r="942">
@@ -31441,7 +31441,7 @@
         </is>
       </c>
       <c r="G942">
-        <v>9.535782497647656</v>
+        <v>9.545712508873166</v>
       </c>
     </row>
     <row r="943">
@@ -31474,7 +31474,7 @@
         </is>
       </c>
       <c r="G943">
-        <v>39.63327128744354</v>
+        <v>39.45904398701755</v>
       </c>
     </row>
     <row r="944">
@@ -31507,7 +31507,7 @@
         </is>
       </c>
       <c r="G944">
-        <v>9.275426004431758</v>
+        <v>9.283985295717425</v>
       </c>
     </row>
     <row r="945">
@@ -31540,7 +31540,7 @@
         </is>
       </c>
       <c r="G945">
-        <v>43.6538251426206</v>
+        <v>43.53622432082602</v>
       </c>
     </row>
     <row r="946">
@@ -31573,7 +31573,7 @@
         </is>
       </c>
       <c r="G946">
-        <v>9.026566510002732</v>
+        <v>9.035048371556801</v>
       </c>
     </row>
     <row r="947">
@@ -31606,7 +31606,7 @@
         </is>
       </c>
       <c r="G947">
-        <v>47.58428692092892</v>
+        <v>47.50364434592076</v>
       </c>
     </row>
     <row r="948">
@@ -31639,7 +31639,7 @@
         </is>
       </c>
       <c r="G948">
-        <v>8.796897283463286</v>
+        <v>8.80607741418245</v>
       </c>
     </row>
     <row r="949">
@@ -31672,7 +31672,7 @@
         </is>
       </c>
       <c r="G949">
-        <v>51.3501214805122</v>
+        <v>51.29491061738133</v>
       </c>
     </row>
     <row r="950">
@@ -31705,7 +31705,7 @@
         </is>
       </c>
       <c r="G950">
-        <v>8.599644418610122</v>
+        <v>8.609851949028887</v>
       </c>
     </row>
     <row r="951">
@@ -31738,7 +31738,7 @@
         </is>
       </c>
       <c r="G951">
-        <v>54.92029663827323</v>
+        <v>54.8821519415966</v>
       </c>
     </row>
     <row r="952">
@@ -31804,7 +31804,7 @@
         </is>
       </c>
       <c r="G953">
-        <v>0.6626299510982065</v>
+        <v>0.661532221015449</v>
       </c>
     </row>
     <row r="954">
@@ -31870,7 +31870,7 @@
         </is>
       </c>
       <c r="G955">
-        <v>0.851721792670033</v>
+        <v>0.842973500694864</v>
       </c>
     </row>
     <row r="956">
@@ -31936,7 +31936,7 @@
         </is>
       </c>
       <c r="G957">
-        <v>1.318781808126257</v>
+        <v>1.307755165160113</v>
       </c>
     </row>
     <row r="958">
@@ -32002,7 +32002,7 @@
         </is>
       </c>
       <c r="G959">
-        <v>1.674139806008509</v>
+        <v>1.660083471097086</v>
       </c>
     </row>
     <row r="960">
@@ -32068,7 +32068,7 @@
         </is>
       </c>
       <c r="G961">
-        <v>2.220426948996432</v>
+        <v>2.200770633871227</v>
       </c>
     </row>
     <row r="962">
@@ -32134,7 +32134,7 @@
         </is>
       </c>
       <c r="G963">
-        <v>2.931979822495829</v>
+        <v>2.90382832360328</v>
       </c>
     </row>
     <row r="964">
@@ -32200,7 +32200,7 @@
         </is>
       </c>
       <c r="G965">
-        <v>3.701607710663716</v>
+        <v>3.661710734139023</v>
       </c>
     </row>
     <row r="966">
@@ -32266,7 +32266,7 @@
         </is>
       </c>
       <c r="G967">
-        <v>4.432013553310912</v>
+        <v>4.377502099721085</v>
       </c>
     </row>
     <row r="968">
@@ -32332,7 +32332,7 @@
         </is>
       </c>
       <c r="G969">
-        <v>5.590890285063842</v>
+        <v>5.517513873219936</v>
       </c>
     </row>
     <row r="970">
@@ -32398,7 +32398,7 @@
         </is>
       </c>
       <c r="G971">
-        <v>7.313267418186851</v>
+        <v>7.206249782597888</v>
       </c>
     </row>
     <row r="972">
@@ -32431,7 +32431,7 @@
         </is>
       </c>
       <c r="G972">
-        <v>9.711153369594516</v>
+        <v>9.547809598718015</v>
       </c>
     </row>
     <row r="973">
@@ -32464,7 +32464,7 @@
         </is>
       </c>
       <c r="G973">
-        <v>9.711153369594516</v>
+        <v>9.547809598718015</v>
       </c>
     </row>
     <row r="974">
@@ -32497,7 +32497,7 @@
         </is>
       </c>
       <c r="G974">
-        <v>13.07211804123714</v>
+        <v>12.83234688933813</v>
       </c>
     </row>
     <row r="975">
@@ -32530,7 +32530,7 @@
         </is>
       </c>
       <c r="G975">
-        <v>13.07211804123714</v>
+        <v>12.83234688933813</v>
       </c>
     </row>
     <row r="976">
@@ -32563,7 +32563,7 @@
         </is>
       </c>
       <c r="G976">
-        <v>15.23878813370215</v>
+        <v>15.22371305526002</v>
       </c>
     </row>
     <row r="977">
@@ -32596,7 +32596,7 @@
         </is>
       </c>
       <c r="G977">
-        <v>16.92339398037289</v>
+        <v>16.60657167132343</v>
       </c>
     </row>
     <row r="978">
@@ -32629,7 +32629,7 @@
         </is>
       </c>
       <c r="G978">
-        <v>15.36297799236238</v>
+        <v>15.31936268275313</v>
       </c>
     </row>
     <row r="979">
@@ -32662,7 +32662,7 @@
         </is>
       </c>
       <c r="G979">
-        <v>22.88775875065148</v>
+        <v>21.91646456846297</v>
       </c>
     </row>
     <row r="980">
@@ -32695,7 +32695,7 @@
         </is>
       </c>
       <c r="G980">
-        <v>15.24455623385172</v>
+        <v>15.2109815400079</v>
       </c>
     </row>
     <row r="981">
@@ -32728,7 +32728,7 @@
         </is>
       </c>
       <c r="G981">
-        <v>27.63094911161344</v>
+        <v>26.50275383115291</v>
       </c>
     </row>
     <row r="982">
@@ -32761,7 +32761,7 @@
         </is>
       </c>
       <c r="G982">
-        <v>14.77208408400565</v>
+        <v>14.74734156165927</v>
       </c>
     </row>
     <row r="983">
@@ -32794,7 +32794,7 @@
         </is>
       </c>
       <c r="G983">
-        <v>31.69946714996414</v>
+        <v>30.54628100899921</v>
       </c>
     </row>
     <row r="984">
@@ -32827,7 +32827,7 @@
         </is>
       </c>
       <c r="G984">
-        <v>14.12266334139607</v>
+        <v>14.10472039778409</v>
       </c>
     </row>
     <row r="985">
@@ -32860,7 +32860,7 @@
         </is>
       </c>
       <c r="G985">
-        <v>35.14171178306996</v>
+        <v>34.10652853244198</v>
       </c>
     </row>
     <row r="986">
@@ -32893,7 +32893,7 @@
         </is>
       </c>
       <c r="G986">
-        <v>13.46423640055271</v>
+        <v>13.45314656865762</v>
       </c>
     </row>
     <row r="987">
@@ -32926,7 +32926,7 @@
         </is>
       </c>
       <c r="G987">
-        <v>38.58696471452114</v>
+        <v>37.76360138892296</v>
       </c>
     </row>
     <row r="988">
@@ -32959,7 +32959,7 @@
         </is>
       </c>
       <c r="G988">
-        <v>12.79902163270845</v>
+        <v>12.79281985645639</v>
       </c>
     </row>
     <row r="989">
@@ -32992,7 +32992,7 @@
         </is>
       </c>
       <c r="G989">
-        <v>42.03445541595869</v>
+        <v>41.44394049337895</v>
       </c>
     </row>
     <row r="990">
@@ -33025,7 +33025,7 @@
         </is>
       </c>
       <c r="G990">
-        <v>12.14837345733966</v>
+        <v>12.14564942570783</v>
       </c>
     </row>
     <row r="991">
@@ -33058,7 +33058,7 @@
         </is>
       </c>
       <c r="G991">
-        <v>45.61917696080436</v>
+        <v>45.2225762601656</v>
       </c>
     </row>
     <row r="992">
@@ -33091,7 +33091,7 @@
         </is>
       </c>
       <c r="G992">
-        <v>11.4986521812675</v>
+        <v>11.49863256039015</v>
       </c>
     </row>
     <row r="993">
@@ -33124,7 +33124,7 @@
         </is>
       </c>
       <c r="G993">
-        <v>49.18809557547522</v>
+        <v>48.92688510359845</v>
       </c>
     </row>
     <row r="994">
@@ -33157,7 +33157,7 @@
         </is>
       </c>
       <c r="G994">
-        <v>10.89323192772855</v>
+        <v>10.89558571704217</v>
       </c>
     </row>
     <row r="995">
@@ -33190,7 +33190,7 @@
         </is>
       </c>
       <c r="G995">
-        <v>52.95804925039045</v>
+        <v>52.78245438584526</v>
       </c>
     </row>
     <row r="996">
@@ -33223,7 +33223,7 @@
         </is>
       </c>
       <c r="G996">
-        <v>10.33300832116359</v>
+        <v>10.33768280693247</v>
       </c>
     </row>
     <row r="997">
@@ -33256,7 +33256,7 @@
         </is>
       </c>
       <c r="G997">
-        <v>56.46053429568111</v>
+        <v>56.34051507045154</v>
       </c>
     </row>
     <row r="998">
@@ -33289,7 +33289,7 @@
         </is>
       </c>
       <c r="G998">
-        <v>9.822412799723612</v>
+        <v>9.829388088624837</v>
       </c>
     </row>
     <row r="999">
@@ -33322,7 +33322,7 @@
         </is>
       </c>
       <c r="G999">
-        <v>59.62375743338233</v>
+        <v>59.54191361592631</v>
       </c>
     </row>
     <row r="1000">
@@ -33355,7 +33355,7 @@
         </is>
       </c>
       <c r="G1000">
-        <v>9.375231327202997</v>
+        <v>9.384308050105091</v>
       </c>
     </row>
     <row r="1001">
@@ -33388,7 +33388,7 @@
         </is>
       </c>
       <c r="G1001">
-        <v>62.44904977651971</v>
+        <v>62.39328979348726</v>
       </c>
     </row>
     <row r="1002">
@@ -33421,7 +33421,7 @@
         </is>
       </c>
       <c r="G1002">
-        <v>0.5615196672622997</v>
+        <v>0.5611285612114799</v>
       </c>
     </row>
     <row r="1003">
@@ -33454,7 +33454,7 @@
         </is>
       </c>
       <c r="G1003">
-        <v>0.5615196672622997</v>
+        <v>0.5611285612114799</v>
       </c>
     </row>
     <row r="1004">
@@ -33487,7 +33487,7 @@
         </is>
       </c>
       <c r="G1004">
-        <v>0.6855416328866193</v>
+        <v>0.6766693451435568</v>
       </c>
     </row>
     <row r="1005">
@@ -33520,7 +33520,7 @@
         </is>
       </c>
       <c r="G1005">
-        <v>0.6855416328866193</v>
+        <v>0.6766693451435568</v>
       </c>
     </row>
     <row r="1006">
@@ -33553,7 +33553,7 @@
         </is>
       </c>
       <c r="G1006">
-        <v>0.8960863582688703</v>
+        <v>0.88580699689514</v>
       </c>
     </row>
     <row r="1007">
@@ -33586,7 +33586,7 @@
         </is>
       </c>
       <c r="G1007">
-        <v>0.8960863582688703</v>
+        <v>0.88580699689514</v>
       </c>
     </row>
     <row r="1008">
@@ -33619,7 +33619,7 @@
         </is>
       </c>
       <c r="G1008">
-        <v>1.146082983797519</v>
+        <v>1.133304314656693</v>
       </c>
     </row>
     <row r="1009">
@@ -33652,7 +33652,7 @@
         </is>
       </c>
       <c r="G1009">
-        <v>1.146082983797519</v>
+        <v>1.133304314656693</v>
       </c>
     </row>
     <row r="1010">
@@ -33685,7 +33685,7 @@
         </is>
       </c>
       <c r="G1010">
-        <v>1.453753279602449</v>
+        <v>1.437692560548772</v>
       </c>
     </row>
     <row r="1011">
@@ -33718,7 +33718,7 @@
         </is>
       </c>
       <c r="G1011">
-        <v>1.453753279602449</v>
+        <v>1.437692560548772</v>
       </c>
     </row>
     <row r="1012">
@@ -33751,7 +33751,7 @@
         </is>
       </c>
       <c r="G1012">
-        <v>1.83131359258639</v>
+        <v>1.810287733491543</v>
       </c>
     </row>
     <row r="1013">
@@ -33784,7 +33784,7 @@
         </is>
       </c>
       <c r="G1013">
-        <v>1.83131359258639</v>
+        <v>1.810287733491543</v>
       </c>
     </row>
     <row r="1014">
@@ -33817,7 +33817,7 @@
         </is>
       </c>
       <c r="G1014">
-        <v>2.351636360014424</v>
+        <v>2.324299298159645</v>
       </c>
     </row>
     <row r="1015">
@@ -33850,7 +33850,7 @@
         </is>
       </c>
       <c r="G1015">
-        <v>2.351636360014424</v>
+        <v>2.324299298159645</v>
       </c>
     </row>
     <row r="1016">
@@ -33883,7 +33883,7 @@
         </is>
       </c>
       <c r="G1016">
-        <v>2.755390114769689</v>
+        <v>2.721145471160932</v>
       </c>
     </row>
     <row r="1017">
@@ -33916,7 +33916,7 @@
         </is>
       </c>
       <c r="G1017">
-        <v>2.755390114769689</v>
+        <v>2.721145471160932</v>
       </c>
     </row>
     <row r="1018">
@@ -33949,7 +33949,7 @@
         </is>
       </c>
       <c r="G1018">
-        <v>3.370549580350867</v>
+        <v>3.32504155862773</v>
       </c>
     </row>
     <row r="1019">
@@ -33982,7 +33982,7 @@
         </is>
       </c>
       <c r="G1019">
-        <v>3.370549580350867</v>
+        <v>3.32504155862773</v>
       </c>
     </row>
     <row r="1020">
@@ -34015,7 +34015,7 @@
         </is>
       </c>
       <c r="G1020">
-        <v>4.18825167537475</v>
+        <v>4.127076225717021</v>
       </c>
     </row>
     <row r="1021">
@@ -34048,7 +34048,7 @@
         </is>
       </c>
       <c r="G1021">
-        <v>4.18825167537475</v>
+        <v>4.127076225717021</v>
       </c>
     </row>
     <row r="1022">
@@ -34081,7 +34081,7 @@
         </is>
       </c>
       <c r="G1022">
-        <v>5.459169413453205</v>
+        <v>5.373799290169971</v>
       </c>
     </row>
     <row r="1023">
@@ -34114,7 +34114,7 @@
         </is>
       </c>
       <c r="G1023">
-        <v>5.459169413453205</v>
+        <v>5.373799290169971</v>
       </c>
     </row>
     <row r="1024">
@@ -34147,7 +34147,7 @@
         </is>
       </c>
       <c r="G1024">
-        <v>5.682859945331402</v>
+        <v>5.671601571415709</v>
       </c>
     </row>
     <row r="1025">
@@ -34180,7 +34180,7 @@
         </is>
       </c>
       <c r="G1025">
-        <v>7.097134866996495</v>
+        <v>6.975086837340597</v>
       </c>
     </row>
     <row r="1026">
@@ -34213,7 +34213,7 @@
         </is>
       </c>
       <c r="G1026">
-        <v>5.443579149445609</v>
+        <v>5.437893653479856</v>
       </c>
     </row>
     <row r="1027">
@@ -34246,7 +34246,7 @@
         </is>
       </c>
       <c r="G1027">
-        <v>8.987587462404244</v>
+        <v>8.831250277602805</v>
       </c>
     </row>
     <row r="1028">
@@ -34279,7 +34279,7 @@
         </is>
       </c>
       <c r="G1028">
-        <v>5.258945900749611</v>
+        <v>5.232585030200741</v>
       </c>
     </row>
     <row r="1029">
@@ -34312,7 +34312,7 @@
         </is>
       </c>
       <c r="G1029">
-        <v>11.80923734892612</v>
+        <v>11.3402283972588</v>
       </c>
     </row>
     <row r="1030">
@@ -34345,7 +34345,7 @@
         </is>
       </c>
       <c r="G1030">
-        <v>4.938231746818461</v>
+        <v>4.913902545044385</v>
       </c>
     </row>
     <row r="1031">
@@ -34378,7 +34378,7 @@
         </is>
       </c>
       <c r="G1031">
-        <v>13.76388628745463</v>
+        <v>13.23942158733598</v>
       </c>
     </row>
     <row r="1032">
@@ -34411,7 +34411,7 @@
         </is>
       </c>
       <c r="G1032">
-        <v>4.733766402451875</v>
+        <v>4.713132408316553</v>
       </c>
     </row>
     <row r="1033">
@@ -34444,7 +34444,7 @@
         </is>
       </c>
       <c r="G1033">
-        <v>16.0111969203938</v>
+        <v>15.47501294088635</v>
       </c>
     </row>
     <row r="1034">
@@ -34477,7 +34477,7 @@
         </is>
       </c>
       <c r="G1034">
-        <v>4.533134169108907</v>
+        <v>4.518041412945959</v>
       </c>
     </row>
     <row r="1035">
@@ -34510,7 +34510,7 @@
         </is>
       </c>
       <c r="G1035">
-        <v>18.2286187968524</v>
+        <v>17.74734395001456</v>
       </c>
     </row>
     <row r="1036">
@@ -34543,7 +34543,7 @@
         </is>
       </c>
       <c r="G1036">
-        <v>4.361055338105311</v>
+        <v>4.351829138119278</v>
       </c>
     </row>
     <row r="1037">
@@ -34576,7 +34576,7 @@
         </is>
       </c>
       <c r="G1037">
-        <v>20.72822127852497</v>
+        <v>20.34515372820592</v>
       </c>
     </row>
     <row r="1038">
@@ -34609,7 +34609,7 @@
         </is>
       </c>
       <c r="G1038">
-        <v>4.228263950981566</v>
+        <v>4.223712251516108</v>
       </c>
     </row>
     <row r="1039">
@@ -34642,7 +34642,7 @@
         </is>
       </c>
       <c r="G1039">
-        <v>23.64916751912906</v>
+        <v>23.37374631503381</v>
       </c>
     </row>
     <row r="1040">
@@ -34675,7 +34675,7 @@
         </is>
       </c>
       <c r="G1040">
-        <v>4.124934404901609</v>
+        <v>4.123318524446345</v>
       </c>
     </row>
     <row r="1041">
@@ -34708,7 +34708,7 @@
         </is>
       </c>
       <c r="G1041">
-        <v>27.06629926360776</v>
+        <v>26.88033069622519</v>
       </c>
     </row>
     <row r="1042">
@@ -34741,7 +34741,7 @@
         </is>
       </c>
       <c r="G1042">
-        <v>4.028949204709082</v>
+        <v>4.029015403949806</v>
       </c>
     </row>
     <row r="1043">
@@ -34774,7 +34774,7 @@
         </is>
       </c>
       <c r="G1043">
-        <v>30.86736675389889</v>
+        <v>30.74379949944706</v>
       </c>
     </row>
     <row r="1044">
@@ -34807,7 +34807,7 @@
         </is>
       </c>
       <c r="G1044">
-        <v>3.951142920556129</v>
+        <v>3.9522845637476</v>
       </c>
     </row>
     <row r="1045">
@@ -34840,7 +34840,7 @@
         </is>
       </c>
       <c r="G1045">
-        <v>35.22356671521197</v>
+        <v>35.13941227485613</v>
       </c>
     </row>
     <row r="1046">
@@ -34873,7 +34873,7 @@
         </is>
       </c>
       <c r="G1046">
-        <v>3.880616020567013</v>
+        <v>3.882626908053192</v>
       </c>
     </row>
     <row r="1047">
@@ -34906,7 +34906,7 @@
         </is>
       </c>
       <c r="G1047">
-        <v>39.79024137119809</v>
+        <v>39.73182678032752</v>
       </c>
     </row>
     <row r="1048">
@@ -34939,7 +34939,7 @@
         </is>
       </c>
       <c r="G1048">
-        <v>3.815733988333098</v>
+        <v>3.818547947815508</v>
       </c>
     </row>
     <row r="1049">
@@ -34972,7 +34972,7 @@
         </is>
       </c>
       <c r="G1049">
-        <v>44.44198015654725</v>
+        <v>44.40122133983871</v>
       </c>
     </row>
     <row r="1050">
@@ -35005,7 +35005,7 @@
         </is>
       </c>
       <c r="G1050">
-        <v>3.757406589366936</v>
+        <v>3.760951883962418</v>
       </c>
     </row>
     <row r="1051">
@@ -35038,7 +35038,7 @@
         </is>
       </c>
       <c r="G1051">
-        <v>48.96415311480317</v>
+        <v>48.93504690323518</v>
       </c>
     </row>
     <row r="1052">
@@ -35071,7 +35071,7 @@
         </is>
       </c>
       <c r="G1052">
-        <v>0.5825561098344016</v>
+        <v>0.582150233988922</v>
       </c>
     </row>
     <row r="1053">
@@ -35104,7 +35104,7 @@
         </is>
       </c>
       <c r="G1053">
-        <v>0.5825561098344016</v>
+        <v>0.582150233988922</v>
       </c>
     </row>
     <row r="1054">
@@ -35137,7 +35137,7 @@
         </is>
       </c>
       <c r="G1054">
-        <v>0.7450110646573965</v>
+        <v>0.7353626123402388</v>
       </c>
     </row>
     <row r="1055">
@@ -35170,7 +35170,7 @@
         </is>
       </c>
       <c r="G1055">
-        <v>0.7450110646573965</v>
+        <v>0.7353626123402388</v>
       </c>
     </row>
     <row r="1056">
@@ -35203,7 +35203,7 @@
         </is>
       </c>
       <c r="G1056">
-        <v>1.006988794962382</v>
+        <v>0.9954091194275585</v>
       </c>
     </row>
     <row r="1057">
@@ -35236,7 +35236,7 @@
         </is>
       </c>
       <c r="G1057">
-        <v>1.006988794962382</v>
+        <v>0.9954091194275585</v>
       </c>
     </row>
     <row r="1058">
@@ -35269,7 +35269,7 @@
         </is>
       </c>
       <c r="G1058">
-        <v>1.326897371999762</v>
+        <v>1.312039119442128</v>
       </c>
     </row>
     <row r="1059">
@@ -35302,7 +35302,7 @@
         </is>
       </c>
       <c r="G1059">
-        <v>1.326897371999762</v>
+        <v>1.312039119442128</v>
       </c>
     </row>
     <row r="1060">
@@ -35335,7 +35335,7 @@
         </is>
       </c>
       <c r="G1060">
-        <v>1.725863467673489</v>
+        <v>1.706671485562242</v>
       </c>
     </row>
     <row r="1061">
@@ -35368,7 +35368,7 @@
         </is>
       </c>
       <c r="G1061">
-        <v>1.725863467673489</v>
+        <v>1.706671485562242</v>
       </c>
     </row>
     <row r="1062">
@@ -35401,7 +35401,7 @@
         </is>
       </c>
       <c r="G1062">
-        <v>2.216154031025285</v>
+        <v>2.190467941808135</v>
       </c>
     </row>
     <row r="1063">
@@ -35434,7 +35434,7 @@
         </is>
       </c>
       <c r="G1063">
-        <v>2.216154031025285</v>
+        <v>2.190467941808135</v>
       </c>
     </row>
     <row r="1064">
@@ -35467,7 +35467,7 @@
         </is>
       </c>
       <c r="G1064">
-        <v>2.908402795797174</v>
+        <v>2.874191567474568</v>
       </c>
     </row>
     <row r="1065">
@@ -35500,7 +35500,7 @@
         </is>
       </c>
       <c r="G1065">
-        <v>2.908402795797174</v>
+        <v>2.874191567474568</v>
       </c>
     </row>
     <row r="1066">
@@ -35533,7 +35533,7 @@
         </is>
       </c>
       <c r="G1066">
-        <v>3.497540537818407</v>
+        <v>3.453400858951981</v>
       </c>
     </row>
     <row r="1067">
@@ -35566,7 +35566,7 @@
         </is>
       </c>
       <c r="G1067">
-        <v>3.497540537818407</v>
+        <v>3.453400858951981</v>
       </c>
     </row>
     <row r="1068">
@@ -35599,7 +35599,7 @@
         </is>
       </c>
       <c r="G1068">
-        <v>4.382415225200416</v>
+        <v>4.322072803825734</v>
       </c>
     </row>
     <row r="1069">
@@ -35632,7 +35632,7 @@
         </is>
       </c>
       <c r="G1069">
-        <v>4.382415225200416</v>
+        <v>4.322072803825734</v>
       </c>
     </row>
     <row r="1070">
@@ -35665,7 +35665,7 @@
         </is>
       </c>
       <c r="G1070">
-        <v>5.566777947515397</v>
+        <v>5.483455371827625</v>
       </c>
     </row>
     <row r="1071">
@@ -35698,7 +35698,7 @@
         </is>
       </c>
       <c r="G1071">
-        <v>5.566777947515397</v>
+        <v>5.483455371827625</v>
       </c>
     </row>
     <row r="1072">
@@ -35731,7 +35731,7 @@
         </is>
       </c>
       <c r="G1072">
-        <v>7.382760215412045</v>
+        <v>7.263869528794722</v>
       </c>
     </row>
     <row r="1073">
@@ -35764,7 +35764,7 @@
         </is>
       </c>
       <c r="G1073">
-        <v>7.382760215412045</v>
+        <v>7.263869528794722</v>
       </c>
     </row>
     <row r="1074">
@@ -35797,7 +35797,7 @@
         </is>
       </c>
       <c r="G1074">
-        <v>7.755024948832191</v>
+        <v>7.734679083091585</v>
       </c>
     </row>
     <row r="1075">
@@ -35830,7 +35830,7 @@
         </is>
       </c>
       <c r="G1075">
-        <v>9.731024696957681</v>
+        <v>9.558149875219522</v>
       </c>
     </row>
     <row r="1076">
@@ -35863,7 +35863,7 @@
         </is>
       </c>
       <c r="G1076">
-        <v>7.512546001034782</v>
+        <v>7.498596246843578</v>
       </c>
     </row>
     <row r="1077">
@@ -35896,7 +35896,7 @@
         </is>
       </c>
       <c r="G1077">
-        <v>12.47549486088523</v>
+        <v>12.24952186239325</v>
       </c>
     </row>
     <row r="1078">
@@ -35929,7 +35929,7 @@
         </is>
       </c>
       <c r="G1078">
-        <v>7.327939127826111</v>
+        <v>7.275900931123084</v>
       </c>
     </row>
     <row r="1079">
@@ -35962,7 +35962,7 @@
         </is>
       </c>
       <c r="G1079">
-        <v>16.56535721121575</v>
+        <v>15.87762327431706</v>
       </c>
     </row>
     <row r="1080">
@@ -35995,7 +35995,7 @@
         </is>
       </c>
       <c r="G1080">
-        <v>6.969210317837016</v>
+        <v>6.916585630503837</v>
       </c>
     </row>
     <row r="1081">
@@ -36028,7 +36028,7 @@
         </is>
       </c>
       <c r="G1081">
-        <v>19.59129458721262</v>
+        <v>18.80018636576446</v>
       </c>
     </row>
     <row r="1082">
@@ -36061,7 +36061,7 @@
         </is>
       </c>
       <c r="G1082">
-        <v>6.542547409106306</v>
+        <v>6.49392751974199</v>
       </c>
     </row>
     <row r="1083">
@@ -36094,7 +36094,7 @@
         </is>
       </c>
       <c r="G1083">
-        <v>22.37827846728794</v>
+        <v>21.56874575797473</v>
       </c>
     </row>
     <row r="1084">
@@ -36127,7 +36127,7 @@
         </is>
       </c>
       <c r="G1084">
-        <v>6.102344236159881</v>
+        <v>6.062626970571636</v>
       </c>
     </row>
     <row r="1085">
@@ -36160,7 +36160,7 @@
         </is>
       </c>
       <c r="G1085">
-        <v>24.89819462700846</v>
+        <v>24.17094958778427</v>
       </c>
     </row>
     <row r="1086">
@@ -36193,7 +36193,7 @@
         </is>
       </c>
       <c r="G1086">
-        <v>5.696113917126904</v>
+        <v>5.667982796871357</v>
       </c>
     </row>
     <row r="1087">
@@ -36226,7 +36226,7 @@
         </is>
       </c>
       <c r="G1087">
-        <v>27.57634639167134</v>
+        <v>26.99737769088576</v>
       </c>
     </row>
     <row r="1088">
@@ -36259,7 +36259,7 @@
         </is>
       </c>
       <c r="G1088">
-        <v>5.352828837718263</v>
+        <v>5.335538493080731</v>
       </c>
     </row>
     <row r="1089">
@@ -36292,7 +36292,7 @@
         </is>
       </c>
       <c r="G1089">
-        <v>30.61862893468469</v>
+        <v>30.20289468350611</v>
       </c>
     </row>
     <row r="1090">
@@ -36325,7 +36325,7 @@
         </is>
       </c>
       <c r="G1090">
-        <v>5.068899926045035</v>
+        <v>5.05947030573317</v>
       </c>
     </row>
     <row r="1091">
@@ -36358,7 +36358,7 @@
         </is>
       </c>
       <c r="G1091">
-        <v>34.15007867693712</v>
+        <v>33.87024299450746</v>
       </c>
     </row>
     <row r="1092">
@@ -36391,7 +36391,7 @@
         </is>
       </c>
       <c r="G1092">
-        <v>4.815419752299092</v>
+        <v>4.810906434573598</v>
       </c>
     </row>
     <row r="1093">
@@ -36424,7 +36424,7 @@
         </is>
       </c>
       <c r="G1093">
-        <v>38.0228703111535</v>
+        <v>37.83786687496604</v>
       </c>
     </row>
     <row r="1094">
@@ -36457,7 +36457,7 @@
         </is>
       </c>
       <c r="G1094">
-        <v>4.598521459437324</v>
+        <v>4.597003844736276</v>
       </c>
     </row>
     <row r="1095">
@@ -36490,7 +36490,7 @@
         </is>
       </c>
       <c r="G1095">
-        <v>42.40500583824194</v>
+        <v>42.2798733235104</v>
       </c>
     </row>
     <row r="1096">
@@ -36523,7 +36523,7 @@
         </is>
       </c>
       <c r="G1096">
-        <v>4.402608568569201</v>
+        <v>4.403095504282088</v>
       </c>
     </row>
     <row r="1097">
@@ -36556,7 +36556,7 @@
         </is>
       </c>
       <c r="G1097">
-        <v>46.85798801560743</v>
+        <v>46.77176505092615</v>
       </c>
     </row>
     <row r="1098">
@@ -36589,7 +36589,7 @@
         </is>
       </c>
       <c r="G1098">
-        <v>4.223785423250291</v>
+        <v>4.225780265099211</v>
       </c>
     </row>
     <row r="1099">
@@ -36622,7 +36622,7 @@
         </is>
       </c>
       <c r="G1099">
-        <v>51.23249878824127</v>
+        <v>51.17297774253461</v>
       </c>
     </row>
     <row r="1100">
@@ -36655,7 +36655,7 @@
         </is>
       </c>
       <c r="G1100">
-        <v>4.063521144359815</v>
+        <v>4.066687043406715</v>
       </c>
     </row>
     <row r="1101">
@@ -36688,7 +36688,7 @@
         </is>
       </c>
       <c r="G1101">
-        <v>55.31321727988703</v>
+        <v>55.27175990653901</v>
       </c>
     </row>
     <row r="1102">
@@ -36721,7 +36721,7 @@
         </is>
       </c>
       <c r="G1102">
-        <v>0.6292139936621831</v>
+        <v>0.6287465821278726</v>
       </c>
     </row>
     <row r="1103">
@@ -36754,7 +36754,7 @@
         </is>
       </c>
       <c r="G1103">
-        <v>0.6292139936621831</v>
+        <v>0.6287465821278726</v>
       </c>
     </row>
     <row r="1104">
@@ -36787,7 +36787,7 @@
         </is>
       </c>
       <c r="G1104">
-        <v>0.808082322998803</v>
+        <v>0.7978602355031996</v>
       </c>
     </row>
     <row r="1105">
@@ -36820,7 +36820,7 @@
         </is>
       </c>
       <c r="G1105">
-        <v>0.808082322998803</v>
+        <v>0.7978602355031996</v>
       </c>
     </row>
     <row r="1106">
@@ -36853,7 +36853,7 @@
         </is>
       </c>
       <c r="G1106">
-        <v>1.106124170743784</v>
+        <v>1.093639209056601</v>
       </c>
     </row>
     <row r="1107">
@@ -36886,7 +36886,7 @@
         </is>
       </c>
       <c r="G1107">
-        <v>1.106124170743784</v>
+        <v>1.093639209056601</v>
       </c>
     </row>
     <row r="1108">
@@ -36919,7 +36919,7 @@
         </is>
       </c>
       <c r="G1108">
-        <v>1.480989236487453</v>
+        <v>1.464651437049795</v>
       </c>
     </row>
     <row r="1109">
@@ -36952,7 +36952,7 @@
         </is>
       </c>
       <c r="G1109">
-        <v>1.480989236487453</v>
+        <v>1.464651437049795</v>
       </c>
     </row>
     <row r="1110">
@@ -36985,7 +36985,7 @@
         </is>
       </c>
       <c r="G1110">
-        <v>1.963001694681692</v>
+        <v>1.941416089401744</v>
       </c>
     </row>
     <row r="1111">
@@ -37018,7 +37018,7 @@
         </is>
       </c>
       <c r="G1111">
-        <v>1.963001694681692</v>
+        <v>1.941416089401744</v>
       </c>
     </row>
     <row r="1112">
@@ -37051,7 +37051,7 @@
         </is>
       </c>
       <c r="G1112">
-        <v>2.577925757731202</v>
+        <v>2.548254699786451</v>
       </c>
     </row>
     <row r="1113">
@@ -37084,7 +37084,7 @@
         </is>
       </c>
       <c r="G1113">
-        <v>2.577925757731202</v>
+        <v>2.548254699786451</v>
       </c>
     </row>
     <row r="1114">
@@ -37117,7 +37117,7 @@
         </is>
       </c>
       <c r="G1114">
-        <v>3.451556823458605</v>
+        <v>3.411115679795703</v>
       </c>
     </row>
     <row r="1115">
@@ -37150,7 +37150,7 @@
         </is>
       </c>
       <c r="G1115">
-        <v>3.451556823458605</v>
+        <v>3.411115679795703</v>
       </c>
     </row>
     <row r="1116">
@@ -37183,7 +37183,7 @@
         </is>
       </c>
       <c r="G1116">
-        <v>4.207937923412971</v>
+        <v>4.154801315446413</v>
       </c>
     </row>
     <row r="1117">
@@ -37216,7 +37216,7 @@
         </is>
       </c>
       <c r="G1117">
-        <v>4.207937923412971</v>
+        <v>4.154801315446413</v>
       </c>
     </row>
     <row r="1118">
@@ -37249,7 +37249,7 @@
         </is>
       </c>
       <c r="G1118">
-        <v>5.340270628846365</v>
+        <v>5.266315255282069</v>
       </c>
     </row>
     <row r="1119">
@@ -37282,7 +37282,7 @@
         </is>
       </c>
       <c r="G1119">
-        <v>5.340270628846365</v>
+        <v>5.266315255282069</v>
       </c>
     </row>
     <row r="1120">
@@ -37315,7 +37315,7 @@
         </is>
       </c>
       <c r="G1120">
-        <v>6.876402449825666</v>
+        <v>6.772403470321393</v>
       </c>
     </row>
     <row r="1121">
@@ -37348,7 +37348,7 @@
         </is>
       </c>
       <c r="G1121">
-        <v>6.876402449825666</v>
+        <v>6.772403470321393</v>
       </c>
     </row>
     <row r="1122">
@@ -37381,7 +37381,7 @@
         </is>
       </c>
       <c r="G1122">
-        <v>8.988894060653433</v>
+        <v>8.842028422239531</v>
       </c>
     </row>
     <row r="1123">
@@ -37414,7 +37414,7 @@
         </is>
       </c>
       <c r="G1123">
-        <v>8.988894060653433</v>
+        <v>8.842028422239531</v>
       </c>
     </row>
     <row r="1124">
@@ -37447,7 +37447,7 @@
         </is>
       </c>
       <c r="G1124">
-        <v>11.71400201119963</v>
+        <v>11.50199740876612</v>
       </c>
     </row>
     <row r="1125">
@@ -37480,7 +37480,7 @@
         </is>
       </c>
       <c r="G1125">
-        <v>11.71400201119963</v>
+        <v>11.50199740876612</v>
       </c>
     </row>
     <row r="1126">
@@ -37513,7 +37513,7 @@
         </is>
       </c>
       <c r="G1126">
-        <v>13.42460517817442</v>
+        <v>13.41507370930398</v>
       </c>
     </row>
     <row r="1127">
@@ -37546,7 +37546,7 @@
         </is>
       </c>
       <c r="G1127">
-        <v>14.8366692898838</v>
+        <v>14.56170697045139</v>
       </c>
     </row>
     <row r="1128">
@@ -37579,7 +37579,7 @@
         </is>
       </c>
       <c r="G1128">
-        <v>13.15328853987157</v>
+        <v>13.11388540181966</v>
       </c>
     </row>
     <row r="1129">
@@ -37612,7 +37612,7 @@
         </is>
       </c>
       <c r="G1129">
-        <v>19.48865402850653</v>
+        <v>18.65438733707286</v>
       </c>
     </row>
     <row r="1130">
@@ -37645,7 +37645,7 @@
         </is>
       </c>
       <c r="G1130">
-        <v>12.44499461462794</v>
+        <v>12.40370241928177</v>
       </c>
     </row>
     <row r="1131">
@@ -37678,7 +37678,7 @@
         </is>
       </c>
       <c r="G1131">
-        <v>22.39586243748221</v>
+        <v>21.45127213320188</v>
       </c>
     </row>
     <row r="1132">
@@ -37711,7 +37711,7 @@
         </is>
       </c>
       <c r="G1132">
-        <v>11.86464066410237</v>
+        <v>11.82458735688361</v>
       </c>
     </row>
     <row r="1133">
@@ -37744,7 +37744,7 @@
         </is>
       </c>
       <c r="G1133">
-        <v>25.21562774149085</v>
+        <v>24.24873521666922</v>
       </c>
     </row>
     <row r="1134">
@@ -37777,7 +37777,7 @@
         </is>
       </c>
       <c r="G1134">
-        <v>11.23409036787919</v>
+        <v>11.20049874965241</v>
       </c>
     </row>
     <row r="1135">
@@ -37810,7 +37810,7 @@
         </is>
       </c>
       <c r="G1135">
-        <v>27.59539436104713</v>
+        <v>26.72686438970929</v>
       </c>
     </row>
     <row r="1136">
@@ -37843,7 +37843,7 @@
         </is>
       </c>
       <c r="G1136">
-        <v>10.65673122376643</v>
+        <v>10.63321157630723</v>
       </c>
     </row>
     <row r="1137">
@@ -37876,7 +37876,7 @@
         </is>
       </c>
       <c r="G1137">
-        <v>30.03414307327262</v>
+        <v>29.34298974606449</v>
       </c>
     </row>
     <row r="1138">
@@ -37909,7 +37909,7 @@
         </is>
       </c>
       <c r="G1138">
-        <v>10.18871589436303</v>
+        <v>10.1752819274754</v>
       </c>
     </row>
     <row r="1139">
@@ -37942,7 +37942,7 @@
         </is>
       </c>
       <c r="G1139">
-        <v>32.77256606799768</v>
+        <v>32.27682277084261</v>
       </c>
     </row>
     <row r="1140">
@@ -37975,7 +37975,7 @@
         </is>
       </c>
       <c r="G1140">
-        <v>9.812924263152317</v>
+        <v>9.806883243892285</v>
       </c>
     </row>
     <row r="1141">
@@ -38008,7 +38008,7 @@
         </is>
       </c>
       <c r="G1141">
-        <v>35.94690065233301</v>
+        <v>35.61386155911249</v>
       </c>
     </row>
     <row r="1142">
@@ -38041,7 +38041,7 @@
         </is>
       </c>
       <c r="G1142">
-        <v>9.478644486355922</v>
+        <v>9.477313818118933</v>
       </c>
     </row>
     <row r="1143">
@@ -38074,7 +38074,7 @@
         </is>
       </c>
       <c r="G1143">
-        <v>39.40555921654304</v>
+        <v>39.18598328752641</v>
       </c>
     </row>
     <row r="1144">
@@ -38107,7 +38107,7 @@
         </is>
       </c>
       <c r="G1144">
-        <v>9.203794215920354</v>
+        <v>9.205617461383255</v>
       </c>
     </row>
     <row r="1145">
@@ -38140,7 +38140,7 @@
         </is>
       </c>
       <c r="G1145">
-        <v>43.32725032501606</v>
+        <v>43.17921872108922</v>
       </c>
     </row>
     <row r="1146">
@@ -38173,7 +38173,7 @@
         </is>
       </c>
       <c r="G1146">
-        <v>8.965142785981781</v>
+        <v>8.96946637426073</v>
       </c>
     </row>
     <row r="1147">
@@ -38206,7 +38206,7 @@
         </is>
       </c>
       <c r="G1147">
-        <v>47.27257000287574</v>
+        <v>47.17087051846497</v>
       </c>
     </row>
     <row r="1148">
@@ -38239,7 +38239,7 @@
         </is>
       </c>
       <c r="G1148">
-        <v>8.753130036985537</v>
+        <v>8.75968995022885</v>
       </c>
     </row>
     <row r="1149">
@@ -38272,7 +38272,7 @@
         </is>
       </c>
       <c r="G1149">
-        <v>51.1073758600709</v>
+        <v>51.03740836796182</v>
       </c>
     </row>
     <row r="1150">
@@ -38305,7 +38305,7 @@
         </is>
       </c>
       <c r="G1150">
-        <v>8.571859757426523</v>
+        <v>8.580410300892915</v>
       </c>
     </row>
     <row r="1151">
@@ -38338,7 +38338,7 @@
         </is>
       </c>
       <c r="G1151">
-        <v>54.75701175151472</v>
+        <v>54.70860855901072</v>
       </c>
     </row>
     <row r="1152">
@@ -38371,7 +38371,7 @@
         </is>
       </c>
       <c r="G1152">
-        <v>0.6527561656338596</v>
+        <v>0.6522711310075949</v>
       </c>
     </row>
     <row r="1153">
@@ -38404,7 +38404,7 @@
         </is>
       </c>
       <c r="G1153">
-        <v>0.6527561656338596</v>
+        <v>0.6522711310075949</v>
       </c>
     </row>
     <row r="1154">
@@ -38437,7 +38437,7 @@
         </is>
       </c>
       <c r="G1154">
-        <v>0.8780556507982142</v>
+        <v>0.866941094210138</v>
       </c>
     </row>
     <row r="1155">
@@ -38470,7 +38470,7 @@
         </is>
       </c>
       <c r="G1155">
-        <v>0.8780556507982142</v>
+        <v>0.866941094210138</v>
       </c>
     </row>
     <row r="1156">
@@ -38503,7 +38503,7 @@
         </is>
       </c>
       <c r="G1156">
-        <v>1.242908643050875</v>
+        <v>1.228848224962722</v>
       </c>
     </row>
     <row r="1157">
@@ -38536,7 +38536,7 @@
         </is>
       </c>
       <c r="G1157">
-        <v>1.242908643050875</v>
+        <v>1.228848224962722</v>
       </c>
     </row>
     <row r="1158">
@@ -38569,7 +38569,7 @@
         </is>
       </c>
       <c r="G1158">
-        <v>1.714683439292529</v>
+        <v>1.695694475209276</v>
       </c>
     </row>
     <row r="1159">
@@ -38602,7 +38602,7 @@
         </is>
       </c>
       <c r="G1159">
-        <v>1.714683439292529</v>
+        <v>1.695694475209276</v>
       </c>
     </row>
     <row r="1160">
@@ -38635,7 +38635,7 @@
         </is>
       </c>
       <c r="G1160">
-        <v>2.330995212686652</v>
+        <v>2.305215695942038</v>
       </c>
     </row>
     <row r="1161">
@@ -38668,7 +38668,7 @@
         </is>
       </c>
       <c r="G1161">
-        <v>2.330995212686652</v>
+        <v>2.305215695942038</v>
       </c>
     </row>
     <row r="1162">
@@ -38701,7 +38701,7 @@
         </is>
       </c>
       <c r="G1162">
-        <v>3.121280559307742</v>
+        <v>3.085063198006216</v>
       </c>
     </row>
     <row r="1163">
@@ -38734,7 +38734,7 @@
         </is>
       </c>
       <c r="G1163">
-        <v>3.121280559307742</v>
+        <v>3.085063198006216</v>
       </c>
     </row>
     <row r="1164">
@@ -38767,7 +38767,7 @@
         </is>
       </c>
       <c r="G1164">
-        <v>4.272330115642292</v>
+        <v>4.221769800643385</v>
       </c>
     </row>
     <row r="1165">
@@ -38800,7 +38800,7 @@
         </is>
       </c>
       <c r="G1165">
-        <v>4.272330115642292</v>
+        <v>4.221769800643385</v>
       </c>
     </row>
     <row r="1166">
@@ -38833,7 +38833,7 @@
         </is>
       </c>
       <c r="G1166">
-        <v>5.348844595615752</v>
+        <v>5.280435206947412</v>
       </c>
     </row>
     <row r="1167">
@@ -38866,7 +38866,7 @@
         </is>
       </c>
       <c r="G1167">
-        <v>5.348844595615752</v>
+        <v>5.280435206947412</v>
       </c>
     </row>
     <row r="1168">
@@ -38899,7 +38899,7 @@
         </is>
       </c>
       <c r="G1168">
-        <v>6.957966671910541</v>
+        <v>6.860042586643282</v>
       </c>
     </row>
     <row r="1169">
@@ -38932,7 +38932,7 @@
         </is>
       </c>
       <c r="G1169">
-        <v>6.957966671910541</v>
+        <v>6.860042586643282</v>
       </c>
     </row>
     <row r="1170">
@@ -38965,7 +38965,7 @@
         </is>
       </c>
       <c r="G1170">
-        <v>9.165720222536439</v>
+        <v>9.024302928918509</v>
       </c>
     </row>
     <row r="1171">
@@ -38998,7 +38998,7 @@
         </is>
       </c>
       <c r="G1171">
-        <v>9.165720222536439</v>
+        <v>9.024302928918509</v>
       </c>
     </row>
     <row r="1172">
@@ -39031,7 +39031,7 @@
         </is>
       </c>
       <c r="G1172">
-        <v>12.20263793176156</v>
+        <v>11.99844608440924</v>
       </c>
     </row>
     <row r="1173">
@@ -39064,7 +39064,7 @@
         </is>
       </c>
       <c r="G1173">
-        <v>12.20263793176156</v>
+        <v>11.99844608440924</v>
       </c>
     </row>
     <row r="1174">
@@ -39097,7 +39097,7 @@
         </is>
       </c>
       <c r="G1174">
-        <v>16.14071304354429</v>
+        <v>15.84079897475479</v>
       </c>
     </row>
     <row r="1175">
@@ -39130,7 +39130,7 @@
         </is>
       </c>
       <c r="G1175">
-        <v>16.14071304354429</v>
+        <v>15.84079897475479</v>
       </c>
     </row>
     <row r="1176">
@@ -39163,7 +39163,7 @@
         </is>
       </c>
       <c r="G1176">
-        <v>18.65990568474966</v>
+        <v>18.63331103369905</v>
       </c>
     </row>
     <row r="1177">
@@ -39196,7 +39196,7 @@
         </is>
       </c>
       <c r="G1177">
-        <v>20.72345486431179</v>
+        <v>20.32649942491151</v>
       </c>
     </row>
     <row r="1178">
@@ -39229,7 +39229,7 @@
         </is>
       </c>
       <c r="G1178">
-        <v>18.482420455632</v>
+        <v>18.39332071337445</v>
       </c>
     </row>
     <row r="1179">
@@ -39262,7 +39262,7 @@
         </is>
       </c>
       <c r="G1179">
-        <v>27.53836007663358</v>
+        <v>26.31704269329788</v>
       </c>
     </row>
     <row r="1180">
@@ -39295,7 +39295,7 @@
         </is>
       </c>
       <c r="G1180">
-        <v>17.74376386204495</v>
+        <v>17.64243646494804</v>
       </c>
     </row>
     <row r="1181">
@@ -39328,7 +39328,7 @@
         </is>
       </c>
       <c r="G1181">
-        <v>32.16605054649083</v>
+        <v>30.74396026731244</v>
       </c>
     </row>
     <row r="1182">
@@ -39361,7 +39361,7 @@
         </is>
       </c>
       <c r="G1182">
-        <v>16.59808964348393</v>
+        <v>16.49275216548459</v>
       </c>
     </row>
     <row r="1183">
@@ -39394,7 +39394,7 @@
         </is>
       </c>
       <c r="G1183">
-        <v>35.62487585486448</v>
+        <v>34.1680358055216</v>
       </c>
     </row>
     <row r="1184">
@@ -39427,7 +39427,7 @@
         </is>
       </c>
       <c r="G1184">
-        <v>15.32994899597573</v>
+        <v>15.23372544025476</v>
       </c>
     </row>
     <row r="1185">
@@ -39460,7 +39460,7 @@
         </is>
       </c>
       <c r="G1185">
-        <v>38.15422619115542</v>
+        <v>36.8445018833713</v>
       </c>
     </row>
     <row r="1186">
@@ -39493,7 +39493,7 @@
         </is>
       </c>
       <c r="G1186">
-        <v>14.11793642794886</v>
+        <v>14.04256200100373</v>
       </c>
     </row>
     <row r="1187">
@@ -39526,7 +39526,7 @@
         </is>
       </c>
       <c r="G1187">
-        <v>40.4702216843406</v>
+        <v>39.4275562016216</v>
       </c>
     </row>
     <row r="1188">
@@ -39559,7 +39559,7 @@
         </is>
       </c>
       <c r="G1188">
-        <v>13.0781543373216</v>
+        <v>13.02743786873872</v>
       </c>
     </row>
     <row r="1189">
@@ -39592,7 +39592,7 @@
         </is>
       </c>
       <c r="G1189">
-        <v>42.96255513655577</v>
+        <v>42.21509600323621</v>
       </c>
     </row>
     <row r="1190">
@@ -39625,7 +39625,7 @@
         </is>
       </c>
       <c r="G1190">
-        <v>12.21528686580186</v>
+        <v>12.18506727198879</v>
       </c>
     </row>
     <row r="1191">
@@ -39658,7 +39658,7 @@
         </is>
       </c>
       <c r="G1191">
-        <v>45.88365627032303</v>
+        <v>45.38234353310833</v>
       </c>
     </row>
     <row r="1192">
@@ -39691,7 +39691,7 @@
         </is>
       </c>
       <c r="G1192">
-        <v>11.46462015700688</v>
+        <v>11.44836792207179</v>
       </c>
     </row>
     <row r="1193">
@@ -39724,7 +39724,7 @@
         </is>
       </c>
       <c r="G1193">
-        <v>49.05781202769403</v>
+        <v>48.72815932788409</v>
       </c>
     </row>
     <row r="1194">
@@ -39757,7 +39757,7 @@
         </is>
       </c>
       <c r="G1194">
-        <v>10.83009955761019</v>
+        <v>10.8227729522228</v>
       </c>
     </row>
     <row r="1195">
@@ -39790,7 +39790,7 @@
         </is>
       </c>
       <c r="G1195">
-        <v>52.66767669888429</v>
+        <v>52.44617099793633</v>
       </c>
     </row>
     <row r="1196">
@@ -39823,7 +39823,7 @@
         </is>
       </c>
       <c r="G1196">
-        <v>10.27492167130409</v>
+        <v>10.27363646194503</v>
       </c>
     </row>
     <row r="1197">
@@ -39856,7 +39856,7 @@
         </is>
       </c>
       <c r="G1197">
-        <v>56.16212733074103</v>
+        <v>56.0103701286335</v>
       </c>
     </row>
     <row r="1198">
@@ -39889,7 +39889,7 @@
         </is>
       </c>
       <c r="G1198">
-        <v>9.780459829652353</v>
+        <v>9.783690842249467</v>
       </c>
     </row>
     <row r="1199">
@@ -39922,7 +39922,7 @@
         </is>
       </c>
       <c r="G1199">
-        <v>59.3891495382618</v>
+        <v>59.28509738439703</v>
       </c>
     </row>
     <row r="1200">
@@ -39955,7 +39955,7 @@
         </is>
       </c>
       <c r="G1200">
-        <v>9.348676117657776</v>
+        <v>9.355393107709267</v>
       </c>
     </row>
     <row r="1201">
@@ -39988,7 +39988,7 @@
         </is>
       </c>
       <c r="G1201">
-        <v>62.29450320617327</v>
+        <v>62.22333380520843</v>
       </c>
     </row>
   </sheetData>
